--- a/docs/examples/demo-control-1_FERG.xlsx
+++ b/docs/examples/demo-control-1_FERG.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C98"/>
+  <dimension ref="A1:C440"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -517,7 +517,7 @@
         <v>[R_01_闪光]</v>
       </c>
       <c r="C11" t="str">
-        <v>白色光: 0.01 cd·s/m²</v>
+        <v>b白色光:0.01cd.m-2,5ms</v>
       </c>
     </row>
     <row r="12">
@@ -528,7 +528,7 @@
         <v>[R_01_闪光背景]</v>
       </c>
       <c r="C12" t="str">
-        <v>无背景光</v>
+        <v>b背景光_关:0.0cd.m-2</v>
       </c>
     </row>
     <row r="13">
@@ -539,7 +539,7 @@
         <v>[R_01_采样]</v>
       </c>
       <c r="C13" t="str">
-        <v>刺激间隔: 15.0S</v>
+        <v>刺激间隔:10.0S</v>
       </c>
     </row>
     <row r="14">
@@ -550,7 +550,7 @@
         <v>[R_01_分析时间]</v>
       </c>
       <c r="C14" t="str">
-        <v>200 ms</v>
+        <v>200ms</v>
       </c>
     </row>
     <row r="15">
@@ -572,7 +572,7 @@
         <v>[R_01_详细数据(uv)]</v>
       </c>
       <c r="C16" t="str">
-        <v>2.88,-1.59,-2.01,2.7,0.52,-2.98,1.12,2.36,-2.43,-1.03,2.99,-0.62,-2.65,2.08,1.5,-2.91,0.1,2.85,-1.68,-1.93,2.74,0.42,-2.97,1.22,2.3,-2.49,-0.94,2.99,-0.73,-2.61,2.14,1.4,-2.95,0.18,2.79,-1.8,-1.9,2.72,0.25,-3.04,1.21,2.11,-2.69,-1.02,2.78,-1.09,-2.87,1.85,0.87,-3.48,-0.32,2.05,-2.7,-2.78,1.64,-1.15,-4.52,-0.42,0.06,-5,-3.49,-0.15,-4.5,-6.56,-2.31,-3.97,-8.82,-6.15,-4.6,-10.11,-10.8,-7.26,-11.07,-15.26,-12.09,-12.8,-18.93,-18.4,-16.32,-21.96,-25.08,-22.06,-25.1,-31.1,-29.54,-29.3,-35.99,-37.59,-35.11,-39.97,-44.82,-42.27,-43.68,-50.15,-49.66,-47.69,-53.2,-55.72,-52.01,-54.27,-58.97,-55.81,-53.95,-58.59,-57.67,-52.58,-54.6,-56.07,-49.91,-47.66,-50.01,-45.03,-38.59,-39.37,-36.73,-27.83,-24.91,-24.05,-15.2,-7.83,-6.8,0.02,10.76,14.31,18.61,30.38,37.92,40.92,51.22,62.54,66.5,73.92,87.2,94.13,99.02,111.65,122.3,126.49,136.38,149.71,155.53,162.11,175.79,184.79,189.21,200.76,212.84,217.36,225.34,238.77,245.5,250.2,262.43,272.2,275.44,284.34,296.23,300.35,305.28,317,323.62,325.67,334.72,343.83,345.22,350.1,360.03,362.92,363.83,372.04,377.35,376.08,380.44,387.36,386.29,386.11,392.45,393.34,389.71,393.03,396.03,391.25,390.09,393.7,390.08,384.68,386.52,385.2,377.44,375.48,375.86,368.28,361.9,362,356.55,346.92,344.44,341.51,331.05,324.58,322.89,314.05,303.89,301.18,295.28,283.35,277.62,274.24,263.15,253.77,251.03,242.82,230.93,226.53,221.69,209.67,202.13,199.43,189.74,179.26,176.42,170.4,158.76,153.69,150.94,140.68,132.59,131.18,124.31,114.16,111.69,108.68,98.71,93.55,93.13,85.73,77.87,77.69,74.17,65.25,63.08,63.02,55.46,50.35,51.79,47.57,40.31,40.76,40.38,33.11,30.81,33.01,28.07,22.9,25.29,24.04,17.51,17.79,19.86,14.38,11.5,14.96,12.53,7.21,9.56,10.75,5.07,4.5,8.12,4.46,0.75,4.46,4.25,-1.12,0.37,3.33,-1.31,-3.15,1.13,-0.7,-5.23,-2.11,-0.47,-5.62,-5.52,-1.49,-4.85,-8.04,-3.91,-3.97,-9.03,-7.14,-4.08,-8.6,-10.12,-5.7,-7.57,-11.91,-8.61,-7.06,-12.2,-11.91,-7.94,-11.43,-14.51,-10.37,-10.64,-15.72,-13.75,-10.87,-15.56,-17.01,-12.7,-14.83,-19.19,-15.91,-14.62,-19.9,-19.58,-15.81,-19.56,-22.64,-18.59,-19.17,-24.34,-22.38,-19.77,-24.68,-26.11,-21.96,-24.38,-28.78,-25.54,-24.55,-29.98,-29.64,-26.07,-30.08,-33.14,-29.18,-30.03,-35.28,-33.3,-30.92,-36,-37.37,-33.34,-36.01,-40.39,-37.14,-36.38,-41.89,-41.45,-38.03,-42.2,-45.17,-41.2,-42.25,-47.47,-45.37,-43.13,-48.29,-49.49,-45.47,-48.27,-52.52,-49.14,-48.49,-53.96,-53.3,-49.89,-54.09,-56.83,-52.74,-53.86,-58.91,-56.55,-54.32,-59.39,-60.29,-56.15,-58.92,-62.89,-59.25,-58.57,-63.83,-62.82,-59.28,-63.37,-65.74,-61.38,-62.42,-67.15,-64.42,-62.05,-66.9,-67.36,-62.97,-65.6,-69.15,-65.13,-64.3,-69.25,-67.76,-63.99,-67.86,-69.74,-65.04,-65.89,-70.22,-67.01,-64.44,-68.99,-68.93,-64.23,-66.65,-69.73,-65.28,-64.26,-68.83,-66.84,-62.82,-66.43,-67.81,-62.74,-63.41,-67.32,-63.65,-60.87,-65.13,-64.58,-59.6,-61.83,-64.47,-59.63,-58.46,-62.71,-60.27,-56.06,-59.48,-60.43,-55.07,-55.63,-59.2,-55.17,-52.28,-56.34,-55.4,-50.25,-52.39,-54.7,-49.6,-48.4,-52.44,-49.68,-45.41,-48.76,-49.4,-43.9,-44.49,-47.85,-43.59,-40.75,-44.74,-43.54,-38.37,-40.58,-42.69,-37.48,-36.39,-40.37,-37.42,-33.24,-36.67,-37.14,-31.65,-32.4,-35.69,-31.34,-28.68,-32.74,-31.42,-26.36,-28.75,-30.8,-25.6,-24.75,-28.77,-25.77,-21.8,-25.4,-25.81,-20.43,-21.45,-24.76,-20.43,-18.04,-22.24,-20.9,-16.04</v>
+        <v>-11.46,-22.79,-18.42,-10.41,-20.63,-22.03,-11.27,-17.68,-24.51,-13.9,-14.83,-25.31,-17.72,-12.96,-24.34,-21.84,-12.7,-21.98,-25.28,-14.25,-19,-27.25,-17.3,-16.3,-27.35,-21.17,-14.71,-25.64,-24.91,-14.74,-22.66,-27.59,-16.45,-19.25,-28.54,-19.4,-16.36,-27.54,-22.83,-14.76,-24.82,-25.8,-14.82,-21.07,-27.47,-16.51,-17.26,-27.32,-19.25,-14.22,-25.33,-22.24,-12.8,-21.79,-24.56,-13.33,-17.8,-25.73,-15.4,-14.21,-24.89,-18.3,-11.6,-22.53,-21.44,-11.55,-19.33,-24.59,-13.17,-16.61,-25.12,-16.15,-14.33,-25.06,-21.1,-13.04,-24.62,-24.91,-14.66,-22.72,-28.83,-18.33,-19.97,-30.82,-25.12,-24.34,-32.17,-33.78,-22.13,-33.43,-38.74,-30.12,-35.43,-48.52,-35.3,-42,-43.23,-47.78,-43.41,-47.09,-45.29,-34.9,-48.08,-60.22,-40.83,-49.37,-65.73,-52.59,-39.65,-51.77,-51.65,-49.86,-60.92,-61.54,-51.82,-41.9,-47.32,-47.98,-52.26,-61.38,-44.77,-27.48,-50.03,-43.92,-16.27,-24.11,-21.94,-27.41,-4.93,-26.25,7.08,-3.78,6.58,2.15,25.47,13.09,29.13,45.3,34.66,55.96,61.83,83.67,45.68,80.78,73.17,99.97,93.43,118.12,98.75,138,158.69,155.94,146.39,172.68,185.62,186.17,186.27,201.86,212.57,192.26,219.19,228.55,191.42,218.82,238.32,213.65,255.65,256.77,259.31,285.44,287.79,266.67,309.06,267.3,309.78,261.36,310.36,306.66,310.89,313.79,341.32,309.53,311.57,339.5,295.17,321.64,315.29,346.42,307.66,306.79,351.74,310.78,314.16,373.96,364.39,324.07,300.47,367.56,354.16,313.53,295.51,285.3,328.22,318.62,272.08,280.98,346.23,315.21,303.43,326.23,298.08,267.47,278.85,293.9,274.58,245.75,247.75,260.84,242.82,235.11,253.91,256.52,210.11,244.94,186.34,225.23,181.78,211.15,215.66,175,173.05,191.21,169.37,148.24,143.18,152.71,134.44,117.52,126.45,118.82,134.73,115.13,122.94,102.14,103.97,113.71,103.05,99.99,82.76,87.19,78.49,73.02,72.39,68.4,68.05,64.47,60.96,46.76,59.38,52.26,32.39,49.7,44.63,31.63,29.73,36.95,21.12,25.35,26.59,20.9,10.57,23.54,18.34,8.25,13.46,11.74,-2.28,8.12,8.56,-4.73,-3.31,4.62,-6.02,-9.65,1.71,-3.95,-14.17,-5.55,-4.44,-17.67,-10.96,-4.99,-17.21,-16.6,-9.07,-16.8,-22.07,-13.25,-14.47,-24.95,-17.05,-12.72,-25.4,-21.85,-11.56,-24.86,-26.49,-16.12,-21.26,-27.97,-17.79,-20.12,-28.15,-24.08,-15.84,-28.43,-26.24,-18.54,-28.43,-29.77,-21.49,-22.5,-31.65,-22.54,-21.4,-32,-22.18,-21.73,-30.94,-29.94,-22.41,-27.59,-33.63,-20.34,-26.21,-32.85,-25.41,-18.69,-29.24,-33.58,-18.21,-32.77,-29.01,-23.94,-29.97,-33.81,-30.9,-26.28,-35.88,-35.59,-26.2,-46.39,-34.15,-24.5,-35.84,-46.81,-26.36,-35.9,-41.1,-41.32,-28.97,-46.61,-45.46,-33.03,-44.32,-42.33,-33.62,-49,-63.55,-47.25,-58.27,-55.35,-40.38,-37.42,-56.59,-51.4,-49.99,-63.66,-49.63,-57.09,-51.38,-76.69,-45.42,-66.39,-76.5,-49.23,-51.3,-76.38,-77.53,-63.74,-75.03,-75.14,-45.54,-60.59,-60.28,-48.65,-54.96,-57.85,-76.18,-52.24,-55.98,-76.95,-55.58,-60.94,-66.21,-60.56,-59.55,-86.06,-69.03,-51.83,-62.16,-61.59,-72.26,-56.3,-81.75,-52.1,-67.23,-76.26,-46.32,-58.74,-85.31,-49.87,-66.71,-83.34,-69.3,-64.48,-53.43,-79.06,-47.24,-62.63,-86.63,-62.6,-57.59,-65.9,-78.16,-46.15,-75.67,-50.97,-40.24,-73.08,-55.64,-63.24,-48.66,-66.54,-57.51,-67.58,-71.37,-64.83,-50.47,-66.68,-58.68,-54.77,-65.42,-54.66,-53.9,-66.47,-60.01,-57.45,-39.36,-55.26,-66.33,-48.35,-61.87,-51.88,-55.01,-45.53,-65.46,-50.73,-38.78,-66.78,-49.11,-55.59,-44.03,-51.7,-46.42,-40.72,-47.85,-42.14,-49.63,-62.25,-52.64,-42,-56.74,-50.86,-31.84,-40.59,-52.5,-36.02,-46.79,-44,-26.38,-26.84,-42.33,-35.53,-32.76,-33.12,-42.58,-21.67,-32.15,-35.24</v>
       </c>
     </row>
     <row r="17">
@@ -583,7 +583,7 @@
         <v>[R_01_标记]</v>
       </c>
       <c r="C17" t="str">
-        <v>a: 15.2ms -88.0uv b: 34.2ms 403.6uv</v>
+        <v>a: 15.3ms -36.0uv b: 33.8ms 206.4uv</v>
       </c>
     </row>
     <row r="18">
@@ -616,7 +616,7 @@
         <v>[L_01_闪光]</v>
       </c>
       <c r="C20" t="str">
-        <v>白色光: 0.01 cd·s/m²</v>
+        <v>b白色光:0.01cd.m-2,5ms</v>
       </c>
     </row>
     <row r="21">
@@ -627,7 +627,7 @@
         <v>[L_01_闪光背景]</v>
       </c>
       <c r="C21" t="str">
-        <v>无背景光</v>
+        <v>b背景光_关:0.0cd.m-2</v>
       </c>
     </row>
     <row r="22">
@@ -638,7 +638,7 @@
         <v>[L_01_采样]</v>
       </c>
       <c r="C22" t="str">
-        <v>刺激间隔: 15.0S</v>
+        <v>刺激间隔:10.0S</v>
       </c>
     </row>
     <row r="23">
@@ -649,7 +649,7 @@
         <v>[L_01_分析时间]</v>
       </c>
       <c r="C23" t="str">
-        <v>200 ms</v>
+        <v>200ms</v>
       </c>
     </row>
     <row r="24">
@@ -671,7 +671,7 @@
         <v>[L_01_详细数据(uv)]</v>
       </c>
       <c r="C25" t="str">
-        <v>2.39,-2.89,1.1,1.55,-2.98,2.05,0.5,-2.66,2.71,-0.62,-1.96,2.99,-1.66,-0.99,2.85,-2.46,0.12,2.31,-2.92,1.22,1.45,-2.97,2.14,0.38,-2.6,2.76,-0.75,-1.87,2.99,-1.77,-0.88,2.8,-2.55,0.22,2.21,-2.98,1.28,1.29,-3.01,2.14,0.16,-2.66,2.67,-1.03,-1.98,2.75,-2.16,-1.11,2.35,-3.09,-0.22,1.46,-3.78,0.49,0.13,-4.2,0.82,-1.58,-4.44,0.58,-3.57,-4.63,-0.38,-5.78,-4.96,-2.17,-8.15,-5.68,-4.84,-10.68,-7.03,-8.39,-13.41,-9.22,-12.75,-16.4,-12.42,-17.79,-19.72,-16.7,-23.33,-23.46,-22,-29.14,-27.63,-28.11,-34.95,-32.19,-34.71,-40.44,-36.96,-41.32,-45.27,-41.7,-47.39,-49.1,-46,-52.28,-51.56,-49.39,-55.38,-52.3,-51.33,-56.13,-51.04,-51.27,-54.06,-47.5,-48.71,-48.87,-41.5,-43.24,-40.42,-32.93,-34.57,-28.76,-21.76,-22.59,-14.11,-8.03,-7.37,3.2,8.13,10.86,22.74,26.56,31.73,44.04,47.03,54.77,66.65,69.29,79.43,90.17,93.05,105.16,114.24,117.99,131.4,138.6,143.75,157.65,163.05,169.95,183.48,187.4,196.18,208.52,211.49,221.99,232.47,235.13,246.91,255.09,258.07,270.48,276.19,280.03,292.25,295.59,300.63,311.8,313.12,319.45,328.76,328.62,336.04,342.86,341.9,349.97,353.89,352.75,360.81,361.72,360.97,368.24,366.32,366.33,372.03,367.74,368.65,372.08,366.07,367.77,368.41,361.47,363.61,361.21,354.11,356.14,350.78,344.19,345.48,337.51,331.93,331.84,321.87,317.55,315.52,304.36,301.29,296.95,285.49,283.4,276.64,265.74,264.15,255.13,245.53,243.85,233.01,225.21,222.83,210.84,205.07,201.45,189.12,185.33,180.12,168.3,166.14,159.2,148.71,147.64,139.11,130.57,129.92,120.17,113.99,113.06,102.7,98.99,97.17,86.92,85.49,82.35,72.97,73.36,68.7,60.9,62.45,56.33,50.64,52.6,45.36,42.06,43.65,35.85,34.95,35.53,27.82,29.06,28.15,21.27,24.12,21.52,16.11,19.86,15.65,12.18,16.05,10.57,9.31,12.53,6.34,7.25,9.18,2.96,5.75,5.96,0.42,4.56,2.87,-1.32,3.45,-0.01,-2.39,2.24,-2.6,-2.93,0.82,-4.82,-3.13,-0.86,-6.58,-3.18,-2.79,-7.86,-3.3,-4.9,-8.67,-3.65,-7.08,-9.07,-4.35,-9.19,-9.18,-5.48,-11.1,-9.15,-7.04,-12.71,-9.16,-8.99,-13.97,-9.36,-11.21,-14.86,-9.9,-13.58,-15.43,-10.88,-15.92,-15.8,-12.35,-18.12,-16.09,-14.3,-20.04,-16.46,-16.64,-21.63,-17.07,-19.28,-22.87,-18.05,-22.04,-23.82,-19.49,-24.78,-24.57,-21.41,-27.34,-25.25,-23.78,-29.61,-26.01,-26.54,-31.52,-27.01,-29.54,-33.06,-28.36,-32.62,-34.29,-30.14,-35.62,-35.28,-32.36,-38.4,-36.19,-35,-40.82,-37.15,-37.95,-42.84,-38.31,-41.07,-44.43,-39.77,-44.2,-45.65,-41.6,-47.17,-46.6,-43.82,-49.83,-47.4,-46.37,-52.07,-48.21,-49.15,-53.82,-49.15,-52.01,-55.08,-50.34,-54.8,-55.9,-51.83,-57.34,-56.4,-53.63,-59.48,-56.69,-55.68,-61.12,-56.94,-57.89,-62.2,-57.27,-60.1,-62.73,-57.79,-62.15,-62.78,-58.56,-63.88,-62.46,-59.59,-65.15,-61.9,-60.81,-65.86,-61.27,-62.13,-65.97,-60.7,-63.4,-65.52,-60.3,-64.47,-64.56,-60.13,-65.19,-63.23,-60.21,-65.42,-61.68,-60.47,-65.09,-60.06,-60.81,-64.17,-58.54,-61.11,-62.69,-57.21,-61.2,-60.75,-56.14,-60.95,-58.48,-55.35,-60.24,-56.05,-54.77,-59.01,-53.61,-54.3,-57.23,-51.33,-53.83,-54.96,-49.31,-53.2,-52.3,-47.62,-52.26,-49.39,-46.26,-50.93,-46.4,-45.17,-49.14,-43.5,-44.26,-46.87,-40.83,-43.39,-44.19,-38.51,-42.41,-41.21,-36.59,-41.2,-38.07,-35.07,-39.65,-34.93,-33.88,-37.7,-31.97,-32.92,-35.35,-29.32,-32.05,-32.66,-27.09,-31.13,-29.74,-25.31,-30.01,-26.73,-23.99,-28.59,-23.8,-23.05,-26.82,-21.11,-22.36,-24.7,-18.78,-21.79,-22.29,-16.92,-21.18,-19.69,-15.55,-20.39</v>
+        <v>-4.72,-10.74,-3.89,-0.96,-9.24,-8.81,-0.94,-4.99,-11.4,-4.89,-1.59,-9.85,-9.95,-2.01,-5.69,-12.44,-6.25,-2.56,-10.74,-11.33,-3.31,-6.57,-13.6,-7.73,-3.63,-11.65,-12.69,-4.59,-7.38,-14.63,-9.05,-4.51,-12.33,-13.8,-5.61,-7.93,-15.32,-10.07,-5.07,-12.71,-14.56,-6.37,-8.1,-15.66,-10.87,-5.39,-12.97,-15.2,-7.04,-8.47,-16.01,-11.92,-6.01,-13.71,-16.53,-8.43,-10.06,-17.41,-14.77,-8.23,-16.21,-18.61,-11.69,-14.2,-23.31,-18.88,-13.37,-21.77,-23.61,-18.84,-19.94,-29.9,-26.01,-20.25,-32.83,-37.08,-27.32,-25.67,-40.58,-42.56,-32.76,-40.9,-47.47,-45.87,-35.1,-47.17,-44.15,-39.87,-43.6,-51.76,-43.56,-52.51,-64.4,-56.01,-44.38,-63.24,-71.82,-62.73,-55.86,-58.09,-54.34,-35.78,-52.81,-52.15,-41.32,-36.55,-41.08,-32.74,-11.8,-16.34,-15.44,-8.16,2.25,-7.86,-4.15,16.08,20.57,15.13,21.74,39.54,31.44,39.33,55.93,53.77,53.92,76.2,96.93,77.71,106.93,118.33,100.52,106.23,125.57,155.59,146.34,143.17,170.11,183.61,166.01,210.57,198.51,178.47,182.16,234.15,200.88,221.23,246.96,238.14,265.11,234.89,249.25,295.48,246.51,300.04,298.06,261.34,319.58,285.29,305.32,346.61,355.38,300.25,338.8,358.29,361.95,303.43,304.95,364.43,330.83,375.48,331.21,368.3,373.28,368.51,366.1,332.6,361.72,337.63,357.54,314.81,294.45,338.7,333.38,279.68,285.52,304.41,323.4,288.18,254.04,298.32,307.02,255.48,256.5,265.61,222.61,221.19,248,243.65,215.48,204.62,199.15,178.31,181.96,187.51,180.04,155.59,165.22,169.31,138.43,151.74,139.5,143.25,136.55,118.08,116.92,112.15,92.79,109.14,94.1,83.05,81.39,74.3,68.86,67.1,68.29,58.54,46.86,53.38,57.67,44.28,43.06,41.65,42.09,27.1,36.31,31.39,22.4,24.58,25.85,23.97,12.37,18.32,20.56,10.25,5.64,14.86,11.03,3.62,5.81,11.99,1.3,-0.85,6.23,3.8,-4.81,-0.06,3.96,-3.13,-4.87,2.6,-0.35,-9.04,-4.85,0.47,-6.46,-10.61,-0.77,-2.9,-13.04,-6.76,-2.84,-10.18,-12.18,-4.9,-7.1,-15.02,-10.16,-4.59,-12.34,-15.33,-9.47,-9.85,-16.97,-13.57,-10.34,-16.24,-20.97,-11.37,-14.66,-18.79,-15.76,-13.22,-17.34,-24.62,-18.16,-17.91,-23.1,-20.62,-17.81,-21.94,-28.82,-21.4,-20.55,-24.76,-23.55,-14.76,-23.75,-32.85,-26.23,-18.84,-32.54,-31.53,-25.23,-28.44,-27.57,-21.04,-27.4,-37.56,-35.94,-22.55,-26.64,-33.77,-22.06,-22.34,-37.05,-33.39,-24.52,-25.69,-41.59,-30.44,-35.88,-41.27,-34.72,-27.83,-30.89,-34.47,-41.99,-32.74,-47.43,-42.55,-41.53,-34.45,-36.22,-35.77,-25.96,-35.36,-35.33,-34.39,-41.36,-39.85,-38.04,-33.17,-44.22,-54.16,-36.08,-51.14,-62.15,-43.85,-33.94,-58.14,-51.09,-38.12,-44.38,-69.94,-46.4,-57.04,-57.65,-58.67,-55.71,-66.59,-51.37,-60.36,-43.33,-67.58,-62.66,-46.08,-45.35,-59.1,-68.6,-56.28,-51.53,-69.63,-67.91,-63.94,-58.2,-77.77,-67.85,-65.26,-71.94,-45.53,-59.13,-68.53,-66.11,-71.34,-61.44,-68.79,-58,-59.76,-84.95,-76.5,-66.74,-82.63,-72.26,-57.2,-62.13,-58.58,-76.63,-63.15,-67.48,-55.28,-60.01,-62.84,-77.39,-78.86,-65.21,-64.71,-61.28,-45.76,-62.52,-74.78,-76.46,-44.52,-74.1,-67.87,-59,-57.18,-56.4,-48.26,-49.27,-47.56,-55.33,-62.51,-44.77,-46.83,-49.08,-43.28,-50.08,-48.27,-36.53,-45.39,-44.78,-63.48,-45.25,-37.99,-51.66,-48.33,-48.63,-54.37,-41.53,-47.34,-32.38,-58.72,-46.16,-43.14,-52.08,-50.68,-44.27,-39.3,-45.55,-39.84,-40.63,-37.93,-38.26,-27.95,-43.98,-39.42,-42.6,-33.19,-41.96,-42.31,-32.87,-36.15,-34.75,-36.54,-25.82,-29.67,-37.36,-27.08,-34.49,-38.58,-27.55,-22.08,-36.9,-30.57,-24.27,-27.91,-35,-26.63,-19.3,-23.42,-31.54,-23.44,-23.07,-30.05,-26.88,-22.72,-26.96,-33.4,-24.73,-23.05</v>
       </c>
     </row>
     <row r="26">
@@ -682,7 +682,7 @@
         <v>[L_01_标记]</v>
       </c>
       <c r="C26" t="str">
-        <v>a: 15.2ms -82.7uv b: 34.2ms 379.4uv</v>
+        <v>a: 15.3ms -35.3uv b: 33.6ms 245.5uv</v>
       </c>
     </row>
     <row r="27">
@@ -693,7 +693,7 @@
         <v>[R_02_名字]</v>
       </c>
       <c r="C27" t="str">
-        <v>FERG(2)_dMax</v>
+        <v>FERG(2)_dRod</v>
       </c>
     </row>
     <row r="28">
@@ -715,7 +715,7 @@
         <v>[R_02_闪光]</v>
       </c>
       <c r="C29" t="str">
-        <v>白色光: 5.00 cd·s/m²</v>
+        <v>b白色光:0.03cd.m-2,5ms</v>
       </c>
     </row>
     <row r="30">
@@ -726,7 +726,7 @@
         <v>[R_02_闪光背景]</v>
       </c>
       <c r="C30" t="str">
-        <v>无背景光</v>
+        <v>b背景光_关:0.0cd.m-2</v>
       </c>
     </row>
     <row r="31">
@@ -737,7 +737,7 @@
         <v>[R_02_采样]</v>
       </c>
       <c r="C31" t="str">
-        <v>刺激间隔: 15.0S</v>
+        <v>刺激间隔:10.0S</v>
       </c>
     </row>
     <row r="32">
@@ -748,7 +748,7 @@
         <v>[R_02_分析时间]</v>
       </c>
       <c r="C32" t="str">
-        <v>200 ms</v>
+        <v>200ms</v>
       </c>
     </row>
     <row r="33">
@@ -770,7 +770,7 @@
         <v>[R_02_详细数据(uv)]</v>
       </c>
       <c r="C34" t="str">
-        <v>2.39,-2.89,1.1,1.55,-2.98,2.05,0.5,-2.66,2.71,-0.62,-1.96,2.99,-1.66,-1,2.85,-2.47,0.11,2.29,-2.95,1.18,1.4,-3.03,2.07,0.29,-2.72,2.62,-0.93,-2.1,2.71,-2.11,-1.3,2.29,-3.17,-0.53,1.3,-4.07,-0.01,-0.26,-4.85,-0.03,-2.4,-5.66,-0.85,-5.13,-6.74,-2.76,-8.51,-8.41,-6.01,-12.63,-11.06,-10.82,-17.64,-15.1,-17.34,-23.71,-20.88,-25.63,-31.01,-28.65,-35.62,-39.64,-38.46,-47.06,-49.54,-50.12,-59.52,-60.49,-63.08,-72.31,-71.95,-76.49,-84.52,-83.12,-89.18,-95.05,-92.93,-99.73,-102.63,-100.06,-106.57,-105.96,-103.1,-108.15,-103.8,-100.67,-103.09,-95.1,-91.55,-90.34,-79.08,-74.8,-69.26,-55.36,-49.92,-39.71,-23.94,-16.83,-2.05,14.81,24.08,42.94,60.17,72.03,94.13,111.19,125.94,150.2,166.8,184.51,209.75,225.82,246.35,271.39,287.1,310.02,333.85,349.52,374.15,395.97,411.96,437.42,456.74,473.36,498.59,515.21,532.61,556.55,570.54,588.64,610.22,621.87,640.33,658.66,668.4,686.6,701.01,709.29,726.43,736.55,743.77,758.91,764.69,771.12,783.31,785.03,790.75,799.16,797.35,802.22,806.24,801.62,805.33,804.67,798.05,800.15,794.86,787.04,786.99,777.5,769.17,766.49,753.53,745.19,739.5,724.07,715.98,707.11,690.34,682.53,670.55,653.56,645.86,631.14,614.95,607.03,590.19,575.6,567.07,548.95,536.46,526.95,508.5,498.28,487.53,469.76,461.65,449.58,433.39,426.94,413.69,399.8,394.39,380.29,369.16,364.08,349.66,341.42,335.98,321.89,316.36,309.99,296.92,293.6,285.98,274.56,272.74,263.78,254.48,253.33,243.21,236.3,234.96,224.12,219.6,217.3,206.34,203.94,200.13,189.72,188.93,183.32,174.11,174.25,166.84,159.36,159.66,150.76,145.32,145.03,135.18,131.88,130.35,120.27,118.89,115.69,106.15,106.26,101.21,92.93,93.92,87.14,80.7,81.83,73.7,69.44,70.02,61.14,59.13,58.55,49.65,49.67,47.52,39.37,40.93,37.05,30.34,32.8,27.3,22.56,25.15,18.41,15.91,17.9,10.5,10.23,11,3.64,5.32,4.44,-2.15,0.95,-1.74,-6.92,-3.1,-7.48,-10.76,-7.01,-12.7,-13.86,-10.91,-17.33,-16.4,-14.88,-21.32,-18.62,-18.92,-24.65,-20.74,-22.98,-27.36,-22.95,-26.98,-29.55,-25.4,-30.8,-31.35,-28.19,-34.34,-32.92,-31.33,-37.5,-34.45,-34.78,-40.24,-36.11,-38.44,-42.55,-38.05,-42.19,-44.5,-40.38,-45.87,-46.17,-43.15,-49.34,-47.72,-46.33,-52.48,-49.29,-49.86,-55.23,-51.04,-53.61,-57.56,-53.09,-57.41,-59.53,-55.51,-61.12,-61.22,-58.35,-64.56,-62.75,-61.55,-67.63,-64.28,-65.04,-70.24,-65.95,-68.67,-72.39,-67.86,-72.29,-74.1,-70.1,-75.71,-75.49,-72.67,-78.79,-76.66,-75.54,-81.41,-77.78,-78.6,-83.5,-78.97,-81.71,-85.05,-80.35,-84.72,-86.11,-81.98,-87.45,-86.77,-83.88,-89.76,-87.18,-85.99,-91.52,-87.48,-88.23,-92.69,-87.81,-90.45,-93.27,-88.28,-92.48,-93.32,-88.96,-94.18,-92.94,-89.86,-95.39,-92.28,-90.93,-96.02,-91.49,-92.08,-96.02,-90.72,-93.17,-95.42,-90.08,-94.04,-94.27,-89.64,-94.55,-92.71,-89.42,-94.56,-90.88,-89.36,-93.98,-88.96,-89.38,-92.79,-87.08,-89.34,-91.02,-85.36,-89.1,-88.75,-83.88,-88.5,-86.11,-82.66,-87.44,-83.26,-81.63,-85.83,-80.38,-80.72,-83.66,-77.62,-79.78,-80.97,-75.09,-78.69,-77.85,-72.86,-77.29,-74.45,-70.95,-75.48,-70.93,-69.3,-73.19,-67.46,-67.82,-70.41,-64.19,-66.37,-67.2,-61.24,-64.83,-63.64,-58.67,-63.04,-59.89,-56.49,-60.91,-56.12,-54.64,-58.36,-52.49,-53.01,-55.4,-49.14,-51.48,-52.08,-46.2,-49.9,-48.5,-43.7,-48.13,-44.81,-41.64,-46.06,-41.18,-39.97,-43.64,-37.75,-38.57,-40.86,-34.69,-37.29,-37.77,-32.07,-35.99,-34.49,-29.95,-34.53,-31.15,-28.31,-32.81,-27.92,-27.07,-30.75,-24.95,-26.11,-28.37,-22.37,-25.3,-25.72,-20.27,-24.46,-22.9,-18.69,-23.47</v>
+        <v>-7.45,-20.55,-11.19,-11.19,-21.3,-8.72,-15.91,-19.71,-8.18,-20.22,-16.5,-9.95,-22.85,-12.9,-13.58,-23.05,-10.26,-17.97,-20.88,-9.56,-21.75,-17.12,-11.1,-23.68,-13.09,-14.38,-23.12,-10.11,-18.27,-20.23,-9.14,-21.41,-15.9,-10.42,-22.64,-11.47,-13.39,-21.41,-8.27,-16.91,-17.99,-7.24,-19.62,-13.33,-8.52,-20.44,-8.83,-11.5,-18.9,-5.81,-15.02,-15.35,-5.11,-17.74,-10.86,-6.84,-18.63,-6.85,-10.38,-17.37,-4.42,-14.49,-14.23,-4.87,-17.75,-10.41,-7.68,-19.52,-7.57,-12.22,-19.43,-7.27,-17.85,-17.42,-9.54,-22.44,-15.79,-13.16,-25.28,-15.78,-21.37,-29.14,-17.94,-30.68,-29.56,-19.37,-34.8,-26.34,-26.96,-44.14,-33.36,-41.92,-47.7,-35.69,-44.49,-44.01,-41.49,-51.75,-50.23,-47.65,-68.45,-53.01,-54.66,-63.23,-63.59,-66.83,-64.59,-62.17,-81.14,-60.32,-67.96,-81.08,-62.73,-62.46,-60.08,-51.16,-70.62,-52.81,-40.9,-65.84,-37.83,-46.37,-55.84,-39.65,-33.02,-40.63,-25.89,-24.11,-8.6,-12.77,-19.81,6.41,8.1,13.37,34.14,35.36,37.81,39.91,36.64,49.1,63.8,68.17,75.51,95.52,90.76,92.58,115.13,99.9,128.41,111.11,133.78,141.38,161.71,164.51,182.82,153.45,198.12,185.37,178.02,208,206.43,195.95,219.19,229.43,217.23,247.04,225.47,237.51,248.45,291.25,278.62,279.51,309.82,321.2,246.98,265.26,275.31,275.21,280.59,277.96,294.74,274.01,333.26,346.23,313.91,296.01,326.25,272.08,329.32,283.44,316.11,305.16,285.67,320.09,271.79,309.68,242.53,268.66,291.69,270.33,284.91,245.44,240.33,269.67,210.83,265.48,221.95,197.14,240.67,202.53,207.52,231.92,216.43,190.56,204.5,192.49,176.44,179.59,152.32,162.7,161.11,144.82,158.47,115.56,132.54,126.06,104.14,120.22,110.77,83.82,97.32,90.12,72.15,84.59,64.33,66.18,61.5,57.25,58.13,50.08,37.57,51.79,36.51,27.93,35.74,26.9,25.84,33.64,12.67,20.84,16.7,9.94,21.93,10.46,3.48,14.9,-2.31,3.37,6.34,-5.97,4.24,0,-9.83,2.29,-9.62,-10.32,-2.52,-15.44,-10.87,-6.95,-19.65,-8.2,-14.22,-20.3,-9.47,-20.01,-19.27,-9.97,-23.41,-16.11,-14.72,-25.75,-14.78,-19.17,-25.87,-12.89,-24.48,-23.99,-15.21,-27.42,-20.17,-18.26,-29.9,-18.09,-21.9,-26.79,-15.21,-28.03,-26.69,-18.32,-28.1,-23.11,-21.17,-31.37,-16.83,-25.23,-28.53,-18.49,-30.92,-27.9,-15.95,-28.91,-18.93,-22.79,-32.6,-21.06,-24.12,-28.37,-15.95,-27.97,-24.46,-21.08,-36.23,-20.9,-27.52,-32.53,-23.68,-30.04,-29.51,-22.02,-31.04,-31.79,-25.27,-42.23,-23.94,-25.54,-36.99,-25.21,-39.39,-40.89,-23.94,-44.61,-34.95,-36.95,-38.05,-38.05,-35.14,-41.85,-27.68,-47.52,-40.71,-32.31,-42.74,-51.66,-38.65,-49.84,-44.94,-48.28,-54.56,-50.05,-44.18,-51.61,-39.94,-52.73,-50.27,-39.42,-57.89,-42.76,-64.74,-70.38,-47.42,-54.19,-71.55,-48.44,-54.1,-64.22,-55.11,-75.94,-51.71,-52.63,-58.58,-53.22,-59.38,-74.74,-62.06,-69.61,-49.58,-70.94,-64.78,-56.94,-58.78,-60.34,-68.3,-71.95,-57.22,-53.46,-66.01,-71.85,-68.36,-82.1,-55.35,-60.75,-75.99,-52.83,-58.28,-64,-51.88,-86.02,-60.21,-50.22,-75.88,-60.17,-52.45,-62.1,-67.32,-69.88,-69.36,-53.55,-63.54,-75.86,-60.37,-78.32,-57.95,-79.11,-72.38,-53.18,-79.33,-57.92,-44.39,-59.64,-51.77,-70.78,-76.93,-65.33,-66.45,-59.04,-63.36,-63.95,-67.34,-44.16,-73.27,-71.18,-47.92,-72.06,-54.44,-72.54,-59.71,-67,-71.13,-69.55,-46.95,-71.85,-51.75,-69.93,-69.93,-44.6,-51.59,-62.46,-40.97,-71.16,-53.73,-54.3,-59.46,-52.73,-60.32,-64.05,-42.66,-52.86,-55.04,-50.99,-56.6,-58.32,-47.26,-61.54,-42.75,-41.14,-58.68,-42.4,-48.42,-41.06,-39.45,-57.36,-44.13,-42.18,-54.1,-39.29,-37.63,-47.58,-36.64,-45.24,-36.89,-25.05,-45.78,-30.67,-31.07,-39.2,-31.91,-31.06,-36.7,-28.22</v>
       </c>
     </row>
     <row r="35">
@@ -781,7 +781,7 @@
         <v>[R_02_标记]</v>
       </c>
       <c r="C35" t="str">
-        <v>a: 17.2ms -175.9uv b: 38.2ms 786.6uv</v>
+        <v>a: 16.2ms -47.6uv b: 37.8ms 138.0uv</v>
       </c>
     </row>
     <row r="36">
@@ -792,7 +792,7 @@
         <v>[L_02_名字]</v>
       </c>
       <c r="C36" t="str">
-        <v>FERG(2)_dMax</v>
+        <v>FERG(2)_dRod</v>
       </c>
     </row>
     <row r="37">
@@ -814,7 +814,7 @@
         <v>[L_02_闪光]</v>
       </c>
       <c r="C38" t="str">
-        <v>白色光: 5.00 cd·s/m²</v>
+        <v>b白色光:0.03cd.m-2,5ms</v>
       </c>
     </row>
     <row r="39">
@@ -825,7 +825,7 @@
         <v>[L_02_闪光背景]</v>
       </c>
       <c r="C39" t="str">
-        <v>无背景光</v>
+        <v>b背景光_关:0.0cd.m-2</v>
       </c>
     </row>
     <row r="40">
@@ -836,7 +836,7 @@
         <v>[L_02_采样]</v>
       </c>
       <c r="C40" t="str">
-        <v>刺激间隔: 15.0S</v>
+        <v>刺激间隔:10.0S</v>
       </c>
     </row>
     <row r="41">
@@ -847,7 +847,7 @@
         <v>[L_02_分析时间]</v>
       </c>
       <c r="C41" t="str">
-        <v>200 ms</v>
+        <v>200ms</v>
       </c>
     </row>
     <row r="42">
@@ -869,7 +869,7 @@
         <v>[L_02_详细数据(uv)]</v>
       </c>
       <c r="C43" t="str">
-        <v>1.57,-2.68,2.99,-2.41,1.12,0.5,-1.98,2.87,-2.91,2.08,-0.64,-0.99,2.32,-2.98,2.73,-1.7,0.13,1.43,-2.64,2.97,-2.54,1.2,0.29,-1.96,2.71,-3.08,2.01,-1,-1.12,1.9,-3.36,2.3,-2.41,-0.44,0.44,-3.59,1.74,-4.08,-0.41,-1.9,-4.25,-0.17,-6.41,-1.74,-5.59,-6.13,-4.12,-10.12,-5.41,-11.35,-10.32,-11,-16.25,-12.55,-20.1,-18.03,-21.72,-25.86,-24.12,-32.59,-30.2,-36.74,-39.55,-40.37,-48.86,-46.78,-55.48,-56.75,-60.17,-67.54,-66.1,-75.66,-75.1,-80.44,-85.36,-84.44,-93.06,-90.26,-96.19,-97.29,-96.33,-101.97,-96.5,-101.24,-97.44,-95.56,-96.38,-87.98,-89.76,-80.49,-76.86,-71.6,-60.35,-57.78,-43.26,-37.27,-25.58,-12,-4.35,14.42,23,40.53,55.58,68.34,89.78,100.87,122.89,138.47,155.75,178.05,191.4,216.12,231.39,252.19,273.66,288.93,314.4,328.86,351.89,371.19,387.98,412.34,425.75,449.53,465.75,483.5,505.1,517.38,540.32,552.92,570.85,588.3,599.37,619.8,628.56,645.61,657.87,667.57,683.89,688.84,703.79,710.25,718.26,729.13,730.54,742.11,742.67,748.62,753.19,751.5,758.6,753.74,757.25,755.27,751.11,753.05,743.73,744.51,736.46,730.55,727.12,714.74,712.65,699.63,692.72,684.26,670.39,665.49,649.08,641.83,629.16,615.38,607.88,589.93,582.79,567.11,554.73,544.98,527.3,520.48,503.2,493.1,481.55,465.72,459.16,441.7,434.22,421.4,408.52,401.96,385.62,380.58,367.05,357.68,350.73,336.52,333.29,319.65,313.77,306.07,294.68,292.34,279.19,276.28,267.58,259.32,256.87,244.81,244,234.28,229.08,225.64,215.2,215.41,204.92,202.4,197.37,188.98,189.13,178.37,177.91,171.04,164.99,164.15,153.79,154.59,146.06,142.42,139.92,130.72,131.93,122.25,120.85,116.38,109.02,109.81,99.77,100.21,93.83,88.79,88.49,78.99,80.66,72.75,70.24,68.37,60.28,62.43,53.66,53.55,49.91,43.93,45.79,36.96,38.82,33.48,30.05,30.9,22.87,26,19.32,18.51,17.83,11.37,14.93,7.49,9.05,6.56,2.24,5.35,-2.1,1.25,-3.01,-4.88,-3,-9.7,-5.34,-11.05,-10.49,-10.38,-15.63,-11.15,-17.74,-15.08,-17,-20.27,-16.56,-23.29,-19.13,-23.01,-24.02,-21.81,-27.89,-23.02,-28.48,-27.26,-27.05,-31.77,-27.06,-33.46,-30.35,-32.32,-35.13,-31.42,-37.97,-33.56,-37.56,-38.2,-36.15,-42.05,-37.11,-42.68,-41.18,-41.22,-45.72,-41.09,-47.56,-44.26,-46.51,-49.08,-45.56,-52.1,-47.59,-51.84,-52.23,-50.44,-56.21,-51.28,-57.02,-55.28,-55.6,-59.89,-55.36,-61.87,-58.37,-60.87,-63.15,-59.79,-66.24,-61.6,-66.02,-66.08,-64.48,-70.04,-65.04,-70.84,-68.76,-69.27,-73.22,-68.69,-75.12,-71.32,-73.94,-75.82,-72.5,-78.73,-73.84,-78.29,-77.9,-76.37,-81.57,-76.38,-82.1,-79.57,-80.12,-83.62,-78.96,-85.18,-80.95,-83.58,-84.91,-81.52,-87.4,-82.15,-86.52,-85.55,-83.98,-88.7,-83.23,-88.75,-85.67,-86.17,-89.09,-84.23,-90.13,-85.4,-87.93,-88.65,-85.12,-90.55,-84.88,-89.08,-87.5,-85.82,-90,-84.21,-89.47,-85.8,-86.21,-88.52,-83.44,-88.97,-83.74,-86.15,-86.23,-82.56,-87.53,-81.46,-85.49,-83.29,-81.53,-85.18,-79.11,-84.12,-79.91,-80.26,-81.99,-76.75,-81.95,-76.28,-78.62,-78.13,-74.4,-78.97,-72.58,-76.51,-73.78,-72.02,-75.22,-68.97,-73.81,-69.16,-69.55,-70.81,-65.52,-70.49,-64.49,-66.88,-65.93,-62.26,-66.53,-59.97,-63.9,-60.77,-59.15,-62.01,-55.72,-60.52,-55.57,-56.13,-57.04,-51.84,-56.7,-50.53,-53.09,-51.81,-48.33,-52.44,-45.83,-49.9,-46.51,-45.16,-47.8,-41.61,-46.48,-41.36,-42.22,-42.89,-37.92,-42.77,-36.55,-39.39,-37.9,-34.74,-38.78,-32.26,-36.55,-33,-32.02,-34.53,-28.56,-33.58,-28.39,-29.63,-30.16,-25.5,-30.42,-24.24,-27.42,-25.8,-23.04,-27.05,-20.69,-25.26,-21.62,-21.07,-23.51,-17.81,-23.01,-17.81</v>
+        <v>-5.71,2.03,0.21,-6,2.2,-1.16,-6.14,2.24,-2.54,-6.12,2.14,-3.89,-5.93,1.92,-5.15,-5.58,1.58,-6.27,-5.08,1.15,-7.21,-4.43,0.64,-7.94,-3.67,0.06,-8.42,-2.82,-0.55,-8.65,-1.91,-1.19,-8.61,-0.97,-1.82,-8.31,-0.04,-2.44,-7.76,0.85,-3.01,-6.98,1.65,-3.53,-6.01,2.35,-3.98,-4.89,2.9,-4.36,-3.66,3.28,-4.64,-2.37,3.48,-4.84,-1.07,3.46,-4.96,0.16,3.23,-5,1.29,2.79,-4.99,2.22,2.1,-4.92,2.92,1.21,-4.89,3.43,-0.12,-5.11,3.23,-1.6,-5.34,2.61,-3.46,-5.51,1.62,-5.31,-7.06,0.26,-8.86,-8.24,-1.79,-12.42,-9.53,-6.53,-17.73,-14.64,-11.05,-20.6,-19.39,-14.47,-28.75,-22.24,-25.53,-35.79,-31.53,-34.97,-42.73,-33.07,-42.69,-45.83,-44.31,-45.37,-55,-51.42,-46.21,-62.69,-51.04,-55.6,-64.5,-59,-65.9,-67.55,-43.68,-58.19,-66.28,-52.95,-61.65,-52.77,-54.28,-50.84,-40.35,-35.08,-41.71,-26.96,-33.1,-24.76,-29.94,-19.19,-26.37,-3.2,-3.7,0.98,4.45,14.66,13.08,19.61,30.9,28.84,50.32,44.66,48.25,73.9,64.88,78.54,91.64,96.53,88.9,120.85,109.08,127.19,147.31,134.08,132.53,145.07,150.61,159.42,160.59,172.12,170.47,177.43,177.45,200.42,232.52,241.37,253.94,212.48,257.83,258.97,238.23,289.16,295.62,245.08,247.06,307.41,259.06,315.23,320.14,298.78,337.26,328.32,314.1,321.15,331.47,339.86,300.02,281.59,280.59,283.24,313.79,328.09,343.21,339.94,298.21,265.42,274.72,263.53,286.56,293.83,290.54,265.77,279.05,236.89,236.25,272.3,211.99,235.73,203.62,198.51,220.62,194.18,218.03,193.92,197.4,169.29,165.82,148.69,178.57,148.66,158.22,155.19,136.45,124.72,124.85,128.65,114.67,108,109.68,81.21,87.41,90.9,76.85,80.86,75.65,58.88,63.66,53.87,49.26,52.29,38.14,40.99,42.48,34.04,28.22,37.24,25.94,26.33,27.98,19.28,19.45,19.29,9.47,12.25,14.67,7.75,10.24,12.14,1.75,7.34,8.24,-0.66,4.78,4.39,-3.9,4.21,0.96,-5.67,2.14,-2.31,-7.28,1.18,-4.49,-7.98,0.22,-6.73,-9.3,-1.19,-9.27,-8.55,-1.86,-11.18,-9.43,-3.98,-11.91,-8.51,-3.46,-12.25,-9.21,-6.63,-13.83,-8.44,-7.02,-14.52,-8.6,-8.83,-16.15,-7,-7.59,-15.68,-7.5,-9.63,-15.84,-7.53,-13.1,-13.92,-8.47,-12.24,-16.08,-9.64,-15.89,-12.78,-6.64,-14.97,-13.85,-10,-17.84,-17.36,-10.64,-15.44,-10.81,-13.7,-17.09,-11.26,-12.13,-16.94,-10.63,-12.47,-17.51,-14.39,-13.51,-23.1,-14.2,-13.42,-18.58,-14.28,-17.25,-28.55,-13.23,-18.66,-24.06,-21.77,-26.25,-29.55,-17.98,-22.26,-21.84,-18.9,-37.47,-29.73,-24.71,-29.89,-28.1,-24.98,-37.19,-26.69,-22.76,-46.87,-34.89,-34.12,-42.83,-26.25,-26.02,-52.15,-26.18,-37.58,-49.72,-33.89,-38,-37.59,-35.97,-53.45,-39.41,-31.99,-42.91,-60.14,-40.82,-54.05,-48.64,-35.68,-58.12,-48.18,-34.46,-64.52,-46.25,-52.37,-63.44,-42.86,-51.13,-56.08,-62.27,-57.91,-46.54,-43.32,-39.8,-64.5,-48.42,-48.87,-46.32,-57.53,-47.22,-58.07,-48.38,-57.36,-52.27,-60.7,-53.64,-64.46,-43.96,-48.38,-46.08,-38.88,-54.54,-61.98,-38.42,-65.74,-44.46,-52.74,-48.75,-67.28,-55.3,-61.71,-41.43,-37.46,-70.01,-63.55,-39.33,-61.11,-53.15,-59.15,-71.12,-61.42,-44.92,-43.11,-41.2,-59.76,-59.18,-56.01,-59.87,-49.93,-43.16,-58.8,-50.13,-43.58,-55.34,-50.19,-55.51,-50.17,-38.74,-34.07,-50.28,-47.15,-36.26,-47.2,-53.96,-41.21,-42.3,-37.46,-45.37,-53.78,-43.79,-48.85,-56.75,-44.51,-35.95,-37.74,-37.8,-37.67,-40.63,-30.18,-44.25,-40.83,-30.93,-41.43,-49.15,-26.64,-34.39,-41.19,-25.28,-34.11,-32.18,-30.8,-36.5,-34.32,-20.82,-34.16,-24.4,-27.5,-37.91,-26.61,-26.81,-27.75,-19.23,-17.93,-27.29,-16.74</v>
       </c>
     </row>
     <row r="44">
@@ -880,7 +880,7 @@
         <v>[L_02_标记]</v>
       </c>
       <c r="C44" t="str">
-        <v>a: 17.2ms -165.4uv b: 38.2ms 739.4uv</v>
+        <v>a: 16.3ms -43.3uv b: 37.8ms 221.4uv</v>
       </c>
     </row>
     <row r="45">
@@ -891,7 +891,7 @@
         <v>[R_03_名字]</v>
       </c>
       <c r="C45" t="str">
-        <v>FERG(3)_dOps</v>
+        <v>FERG(3)_dRod</v>
       </c>
     </row>
     <row r="46">
@@ -913,7 +913,7 @@
         <v>[R_03_闪光]</v>
       </c>
       <c r="C47" t="str">
-        <v>白色光: 5.00 cd·s/m²</v>
+        <v>b白色光:0.10cd.m-2,5ms</v>
       </c>
     </row>
     <row r="48">
@@ -924,7 +924,7 @@
         <v>[R_03_闪光背景]</v>
       </c>
       <c r="C48" t="str">
-        <v>无背景光</v>
+        <v>b背景光_关:0.0cd.m-2</v>
       </c>
     </row>
     <row r="49">
@@ -935,7 +935,7 @@
         <v>[R_03_采样]</v>
       </c>
       <c r="C49" t="str">
-        <v>刺激间隔: 15.0S</v>
+        <v>刺激间隔:10.0S</v>
       </c>
     </row>
     <row r="50">
@@ -946,7 +946,7 @@
         <v>[R_03_分析时间]</v>
       </c>
       <c r="C50" t="str">
-        <v>200 ms</v>
+        <v>200ms</v>
       </c>
     </row>
     <row r="51">
@@ -968,7 +968,7 @@
         <v>[R_03_详细数据(uv)]</v>
       </c>
       <c r="C52" t="str">
-        <v>-8.78,-12.86,-7.01,-12.22,-8.51,-8.97,-11.32,-6.4,-12.16,-7.23,-10.09,-10.65,-7.62,-13.27,-7.97,-12.84,-11.45,-10.57,-15.01,-9.69,-15.36,-11.65,-12.41,-14.34,-9.18,-14.3,-8.39,-10.46,-9.57,-5.51,-9.78,-3.23,-7.21,-4.74,-3.63,-7.74,-2.82,-9.36,-6.7,-9.45,-13.21,-10.6,-18.25,-14.82,-19.59,-20.59,-18.46,-23.68,-17.44,-21.06,-16.91,-13.75,-14.49,-5.77,-7.94,-0.33,1.47,2.55,9.02,4.61,10.24,6.01,4.54,4.11,-4.85,-3.94,-14.29,-17.41,-22.59,-31.29,-30.44,-39.56,-37.27,-39.43,-39.61,-32.44,-33.38,-21.74,-17.98,-9,1.95,5.65,19.23,20.82,28.68,31.88,29.36,32.82,22.82,20.74,10.13,-1.32,-8.69,-26.04,-32.02,-46.43,-54.32,-58.9,-67.48,-62.65,-65.52,-56.95,-48.56,-40.53,-22.42,-13.94,5.43,17.47,29.55,44.21,46.83,57.23,54.29,52.88,48.28,33.97,26.93,6.68,-6.3,-23.31,-42.13,-51.69,-69.59,-73.74,-81.48,-83.35,-76.9,-75.41,-59.26,-50.03,-32.79,-14.24,-1.24,20.96,30.41,46.24,54.68,57.48,63.57,54.97,53.24,40.37,27.05,15.39,-6.01,-16.56,-36.46,-48.45,-58.49,-70.86,-70.08,-76.71,-70.45,-65.38,-58.66,-42.61,-35.33,-16.3,-5.29,7.82,22.61,26.97,39.66,39.08,42.12,41.13,32.45,30.8,16.17,9.78,-2.33,-15.23,-20.95,-35.7,-37.79,-46.26,-49.11,-46.99,-50.55,-41.25,-40.74,-31.82,-23.58,-19.38,-6.15,-4.54,5.95,9.64,11.59,18.04,12.86,17.2,11.42,8.38,6.64,-3.19,-2.55,-12.5,-14.59,-18.15,-24.84,-21.8,-28.81,-24.81,-25.88,-25.89,-19.6,-22.62,-14.24,-14.81,-11.09,-5.98,-8.39,-0.74,-4.45,-0.86,-0.44,-4,0.45,-6.45,-3.38,-6.93,-9.78,-7.41,-14.45,-10.18,-15.02,-14.71,-12.99,-17.71,-11.79,-16.56,-12.9,-12.23,-14.42,-8.47,-13.44,-8.05,-9.65,-10.09,-5.98,-11.3,-5.64,-9.76,-8.67,-7.08,-11.85,-6.5,-12.15,-9.21,-9.85,-12.86,-8.07,-13.99,-9.24,-11.72,-12.33,-8.7,-14,-8.2,-12.29,-10.59,-8.85,-12.99,-7.21,-12.52,-8.94,-9.51,-12,-7.16,-12.96,-8.02,-10.78,-11.2,-7.93,-13.29,-7.63,-12.08,-10.3,-8.99,-13.08,-7.47,-12.95,-9.21,-10.07,-12.3,-7.58,-13.32,-8.19,-11.12,-11.2,-8.08,-13.27,-7.52,-12.11,-10.04,-8.99,-12.87,-7.33,-12.9,-8.97,-10.12,-12.11,-7.58,-13.32,-8.09,-11.27,-11.09,-8.22,-13.28,-7.52,-12.27,-9.94,-9.15,-12.82,-7.35,-12.99,-8.85,-10.26,-11.99,-7.63,-13.33,-7.99,-11.39,-10.94,-8.31,-13.24,-7.47,-12.37,-9.79,-9.28,-12.73,-7.37,-13.05,-8.73,-10.41,-11.87,-7.7,-13.34,-7.9,-11.53,-10.8,-8.42,-13.2,-7.43,-12.47,-9.65,-9.41,-12.64,-7.38,-13.11,-8.61,-10.55,-11.75,-7.77,-13.35,-7.82,-11.66,-10.65,-8.53,-13.15,-7.4,-12.57,-9.51,-9.55,-12.55,-7.41,-13.16,-8.5,-10.69,-11.62,-7.84,-13.35,-7.75,-11.78,-10.51,-8.64,-13.1,-7.38,-12.67,-9.38,-9.69,-12.45,-7.44,-13.21,-8.39,-10.83,-11.49,-7.93,-13.34,-7.68,-11.91,-10.37,-8.76,-13.04,-7.36,-12.75,-9.24,-9.83,-12.34,-7.48,-13.25,-8.28,-10.97,-11.36,-8.01,-13.33,-7.62,-12.03,-10.22,-8.89,-12.97,-7.35,-12.84,-9.11,-9.97,-12.23,-7.52,-13.28,-8.18,-11.11,-11.22,-8.1,-13.31,-7.56,-12.14,-10.08,-9.01,-12.9,-7.35,-12.91,-8.98,-10.11,-12.12,-7.57,-13.31,-8.08,-11.25,-11.08,-8.2,-13.28,-7.51,-12.26,-9.94,-9.14,-12.82,-7.35,-12.98,-8.86,-10.26,-12,-7.63,-13.33,-7.99,-11.39,-10.94,-8.3,-13.24,-7.47,-12.36,-9.8,-9.27,-12.73,-7.37,-13.05,-8.74,-10.4,-11.88,-7.7,-13.34,-7.91,-11.52,-10.8,-8.41,-13.2,-7.43,-12.47,-9.66,-9.41,-12.64,-7.38,-13.11,-8.62,-10.54,-11.75,-7.76,-13.35,-7.83,-11.65,-10.66,-8.52,-13.15,-7.4,-12.57,-9.52,-9.55,-12.55,-7.41,-13.16,-8.5</v>
+        <v>-3.98,-2.66,-15.41,5.28,-19.15,3.07,-12.18,-7.54,-0.59,-17.52,5.68,-18.28,1.34,-9.02,-9.71,2.53,-17.73,6.79,-15.49,0.5,-4.48,-10.48,6.37,-16.21,8.31,-11.19,0.29,0.9,-10.17,10.36,-13.44,9.74,-6.04,0.26,6.35,-9.29,13.77,-10.1,10.47,-0.87,-0.15,11.04,-8.47,15.89,-6.95,9.92,3.5,-1.47,14.13,-8.34,16.06,-4.7,7.54,6.35,-4.21,14.89,-9.39,13.52,-3.77,2.76,6.74,-8.84,12.64,-12.22,7.63,-6.21,-5.38,4.58,-15.33,6.7,-17.3,-2.99,-11.62,-17.43,-3.37,-28.64,-3.53,-25.63,-13.82,-17.29,-27.68,-13.74,-41.41,-22.09,-43.38,-33.6,-32.25,-52.69,-23.49,-57.75,-38.11,-47.67,-47.31,-38.16,-60.18,-34.67,-59.15,-42.38,-52.48,-56.24,-39.82,-71.36,-43.5,-56.2,-43.51,-54.88,-58.08,-43.6,-71.74,-47.26,-51.85,-52.01,-29.73,-39.34,-22.09,-37.47,-13.02,-24.5,-17.11,-7.9,-17.99,24.62,3.54,19.67,31.58,27.48,51.59,30.43,61.09,42.49,82.5,70.44,67.01,109.39,73.6,125.38,103.97,132.03,131.29,145.19,163.13,149.2,177.72,152.53,195.02,187.25,187.5,213.31,187.12,246.32,235.45,247.75,221.34,256.46,236.04,247.34,247.28,254.17,254.38,310.9,260.68,330.62,257.8,301.6,343.59,307.22,358.19,284.21,366.58,351.99,349.85,329.15,298.46,363.49,308.83,372.67,366.53,334.15,317.77,338.4,319.68,321.33,311.64,307.53,332.57,305.94,341.12,365.66,303.91,321.25,290.69,279.88,289.53,288.09,261.42,297.78,273.25,296.91,271.34,285.12,258.38,279.48,213.55,207.56,221.65,225.1,227.63,172.54,182.35,197.48,188.98,186.54,163.77,179.96,145.73,172.98,164.77,138.22,130.78,122.74,124.9,114.06,126.58,120.57,86.19,117.09,70.97,100.83,78.55,80.25,87.63,58.3,78.48,57.43,65.45,58.64,44.03,53.68,34.94,52.42,27.03,44.4,36.14,22.96,41.71,12.6,35.97,11.43,23.75,20.61,7.67,24.11,0.68,21.67,1.94,7.32,12.77,-6.26,15.54,-8.64,8.64,-2.37,-4,6.25,-14.51,9.69,-13.2,1.26,-4.88,-12.19,4.11,-19.95,5.1,-15.77,-5.07,-4.96,-16.39,3.78,-19.96,1.22,-15.34,-7.72,-2.48,-19.73,2.47,-19.17,-0.77,-12.06,-10.23,-2.14,-20.07,3.92,-20.32,-2.84,-8.43,-13.25,2.5,-20.89,3.07,-15.73,-3.09,-7.34,-16.41,2.08,-17.04,3.35,-15.79,-5.38,-3.64,-16.91,1.93,-16.58,2.37,-12.24,-12.12,-1.71,-18,4.07,-17.33,-7.56,-9.09,-18.31,-4.13,-27.14,0.93,-24.55,-7.3,-14.54,-22.15,-9.76,-26.52,-14.45,-27.47,-23.4,-19.68,-35.39,-5.19,-34.12,-20.92,-38.21,-36.39,-26.82,-39.23,-11.68,-48.02,-25.19,-35.21,-31.63,-20.95,-56.8,-25.28,-44.12,-30.32,-40.87,-41.37,-34.09,-60.3,-21.33,-40.82,-41.25,-48.41,-54.26,-24.54,-66.17,-35.04,-47.75,-52.93,-39.51,-47.98,-31.93,-57.99,-36.2,-54.62,-58.72,-51.87,-61.91,-34.12,-68.99,-55.86,-43.56,-57.52,-54.65,-72.5,-32.85,-69.36,-40.21,-41.2,-72,-44.47,-59.27,-46.22,-46.75,-35.95,-49.21,-56.98,-33.56,-55.36,-45.08,-68.08,-55.91,-32.42,-45.14,-37.94,-45.97,-58.91,-58.78,-68.72,-42.29,-72.7,-40.81,-71.75,-40.69,-34.47,-46.37,-29.82,-60.21,-30.92,-64.11,-49.54,-52.6,-56.91,-34.31,-54.39,-53.68,-48.6,-57.42,-31.1,-56.96,-23.82,-48.65,-42.76,-38.46,-61.91,-33.54,-70.97,-27.87,-57.65,-41.21,-61.13,-55.93,-27.51,-57.69,-29.91,-52.67,-49.04,-52.75,-56.55,-23.99,-52.44,-34.59,-59.79,-50.58,-45.72,-65.56,-39.05,-60.67,-46.04,-38.63,-47.76,-34.77,-46.76,-30.04,-53.21,-38.9,-28.05,-33.7,-29.42,-46.41,-15.27,-46.36,-30.63,-27.4,-31.33,-9.12,-41.18,-18.27,-22.3,-20.12,-10.88,-36.14,-7.16,-24.1,-7.18,-21.28,-23.32,-9.31,-21.1,-1.14,-27.65,-7.99,-11.6,-21.94,0.43,-20.17,0.61,-21.12,-4.55,-2.65,-19.26,5.35</v>
       </c>
     </row>
     <row r="53">
@@ -979,7 +979,7 @@
         <v>[R_03_标记]</v>
       </c>
       <c r="C53" t="str">
-        <v>100.3uv</v>
+        <v>a: 17.8ms -37.4uv b: 41.6ms 287.9uv</v>
       </c>
     </row>
     <row r="54">
@@ -990,7 +990,7 @@
         <v>[L_03_名字]</v>
       </c>
       <c r="C54" t="str">
-        <v>FERG(3)_dOps</v>
+        <v>FERG(3)_dRod</v>
       </c>
     </row>
     <row r="55">
@@ -1012,7 +1012,7 @@
         <v>[L_03_闪光]</v>
       </c>
       <c r="C56" t="str">
-        <v>白色光: 5.00 cd·s/m²</v>
+        <v>b白色光:0.10cd.m-2,5ms</v>
       </c>
     </row>
     <row r="57">
@@ -1023,7 +1023,7 @@
         <v>[L_03_闪光背景]</v>
       </c>
       <c r="C57" t="str">
-        <v>无背景光</v>
+        <v>b背景光_关:0.0cd.m-2</v>
       </c>
     </row>
     <row r="58">
@@ -1034,7 +1034,7 @@
         <v>[L_03_采样]</v>
       </c>
       <c r="C58" t="str">
-        <v>刺激间隔: 15.0S</v>
+        <v>刺激间隔:10.0S</v>
       </c>
     </row>
     <row r="59">
@@ -1045,7 +1045,7 @@
         <v>[L_03_分析时间]</v>
       </c>
       <c r="C59" t="str">
-        <v>200 ms</v>
+        <v>200ms</v>
       </c>
     </row>
     <row r="60">
@@ -1067,7 +1067,7 @@
         <v>[L_03_详细数据(uv)]</v>
       </c>
       <c r="C61" t="str">
-        <v>-9.19,-10.64,-7.84,-11.21,-6.69,-11.56,-5.92,-11.69,-5.71,-11.66,-6.15,-11.54,-7.24,-11.37,-8.85,-11.18,-10.74,-10.92,-12.56,-10.51,-13.96,-9.86,-14.59,-8.91,-14.24,-7.68,-12.89,-6.31,-10.75,-5.06,-8.24,-4.3,-5.94,-4.4,-4.43,-5.65,-4.2,-8.11,-5.45,-11.58,-8.02,-15.49,-11.38,-19.05,-14.7,-21.31,-17.03,-21.46,-17.55,-19,-15.81,-13.99,-11.91,-7.12,-6.58,0.3,-1.09,6.62,3.05,10.12,4.41,9.53,2.1,4.38,-3.92,-4.77,-12.69,-16.25,-22.34,-27.62,-30.46,-36.1,-34.66,-39.3,-33.21,-35.81,-25.6,-25.74,-12.85,-10.83,2.55,5.8,17.11,20.26,27.1,28.83,29.47,28.87,22.74,19.63,7.53,2.59,-13.37,-18.73,-35.48,-39.44,-53.62,-54.46,-63.1,-59.75,-60.96,-53.37,-46.82,-36.15,-23.19,-11.62,4.99,14.68,31.39,36.5,49.74,48.36,55.38,46.96,46.47,32.11,24.55,6.86,-5.72,-23.11,-37.59,-50.83,-63.74,-69.66,-78.08,-74.96,-77.19,-65.23,-61.19,-42.56,-33.74,-12.11,-1.14,19.05,29.12,43.69,50.17,56.11,57.39,53.54,49.45,36.72,28.59,9.73,-0.06,-21.09,-29.69,-48.62,-53.53,-66.73,-66.43,-71.63,-65.98,-62.71,-53,-42.55,-31.15,-16.16,-5.94,10.27,16.69,30.86,31.75,41.42,36.35,40.28,30.24,28.5,15.62,9.46,-3.46,-12.12,-22.3,-31.31,-36.59,-44.18,-43.5,-48.54,-42.11,-44.31,-33.52,-33.3,-20.38,-18.64,-6.13,-3.89,5.87,7.77,13.14,14.24,14.51,14.85,10.31,10.29,2.07,2.29,-7.92,-6.9,-17.24,-15.11,-23.91,-20.74,-26.77,-23.02,-25.64,-22.05,-21.24,-18.66,-14.93,-14.08,-8.28,-9.58,-2.72,-6.19,0.74,-4.46,1.68,-4.46,0.27,-5.8,-2.87,-7.83,-6.86,-9.88,-10.82,-11.35,-14,-11.94,-15.95,-11.62,-16.53,-10.59,-15.9,-9.25,-14.39,-8.02,-12.42,-7.24,-10.39,-7.12,-8.63,-7.69,-7.32,-8.79,-6.54,-10.16,-6.27,-11.51,-6.41,-12.54,-6.87,-13.06,-7.55,-12.98,-8.35,-12.34,-9.21,-11.26,-10.08,-9.95,-10.89,-8.63,-11.59,-7.5,-12.11,-6.73,-12.39,-6.42,-12.38,-6.59,-12.06,-7.19,-11.45,-8.13,-10.61,-9.26,-9.63,-10.42,-8.64,-11.47,-7.76,-12.27,-7.13,-12.72,-6.82,-12.78,-6.89,-12.44,-7.34,-11.76,-8.11,-10.82,-9.1,-9.75,-10.18,-8.68,-11.2,-7.75,-12.04,-7.08,-12.57,-6.75,-12.73,-6.81,-12.49,-7.24,-11.89,-8,-11.01,-8.98,-9.96,-10.06,-8.88,-11.09,-7.91,-11.95,-7.18,-12.52,-6.78,-12.73,-6.77,-12.54,-7.15,-11.99,-7.86,-11.14,-8.81,-10.11,-9.89,-9.03,-10.94,-8.04,-11.84,-7.27,-12.46,-6.82,-12.72,-6.75,-12.6,-7.07,-12.1,-7.73,-11.29,-8.66,-10.27,-9.73,-9.19,-10.79,-8.18,-11.72,-7.37,-12.39,-6.86,-12.71,-6.73,-12.64,-7,-12.19,-7.62,-11.42,-8.51,-10.43,-9.56,-9.35,-10.64,-8.32,-11.59,-7.47,-12.31,-6.92,-12.68,-6.73,-12.68,-6.93,-12.28,-7.5,-11.56,-8.36,-10.59,-9.4,-9.51,-10.48,-8.46,-11.46,-7.58,-12.22,-6.98,-12.65,-6.73,-12.7,-6.88,-12.36,-7.4,-11.68,-8.22,-10.75,-9.24,-9.68,-10.32,-8.62,-11.33,-7.7,-12.13,-7.05,-12.61,-6.74,-12.72,-6.83,-12.44,-7.3,-11.8,-8.08,-10.9,-9.08,-9.84,-10.16,-8.77,-11.19,-7.82,-12.02,-7.12,-12.56,-6.77,-12.73,-6.79,-12.5,-7.2,-11.92,-7.95,-11.05,-8.92,-10,-10,-8.92,-11.04,-7.95,-11.91,-7.21,-12.5,-6.79,-12.73,-6.76,-12.56,-7.12,-12.03,-7.82,-11.19,-8.76,-10.17,-9.83,-9.08,-10.89,-8.08,-11.8,-7.3,-12.44,-6.83,-12.72,-6.74,-12.61,-7.04,-12.13,-7.69,-11.33,-8.61,-10.33,-9.67,-9.24,-10.74,-8.22,-11.68,-7.4,-12.36,-6.88,-12.7,-6.73,-12.65,-6.97,-12.22,-7.58,-11.47,-8.46,-10.49,-9.51,-9.41,-10.59,-8.37,-11.55,-7.51,-12.28,-6.94,-12.67,-6.73,-12.69,-6.91,-12.31,-7.47,-11.6,-8.31,-10.64</v>
+        <v>-1.62,24.63,-2.14,14.05,13.15,-2.69,23.07,-4.1,13.74,11.07,-2.99,22.18,-5.24,14.18,9.76,-2.43,22.04,-5.51,15.4,9.26,-1.02,22.62,-4.93,17.35,9.48,1.13,23.8,-3.66,19.85,10.26,3.84,25.38,-1.9,22.67,11.35,6.84,27.1,0.06,25.53,12.47,9.82,28.64,1.91,28.1,13.31,12.49,29.7,3.39,30.04,13.51,14.41,29.94,4,31.08,12.84,15.56,29.09,3.84,31.01,11.05,15.35,26.88,1.56,28.89,7.72,13.53,22.69,-1.29,24.92,0.85,9.51,15.87,-6.45,19.33,-6.81,1.76,8.37,-17.84,10.49,-19.26,-8.99,-1.51,-26.23,-1.41,-27.37,-18.16,-23.33,-40.39,-18.14,-37.45,-34.48,-33.47,-55.89,-34.39,-54.94,-38.49,-33.15,-59.12,-39.57,-68.77,-35.53,-46.88,-66.05,-40.1,-53.33,-45.6,-52.86,-55.82,-33.98,-60.31,-33.35,-41.01,-39.18,-5.7,-32.8,-4.85,-15.78,-28.48,8.52,-10.9,17,16.81,15.54,43.48,12.51,54.15,55.1,38.35,90.98,46.56,96.35,85.42,83.34,114.47,94.9,124.78,126.36,122.09,150.25,149.59,152.91,179.32,184.91,197.18,182.41,225.04,223.55,194.3,243.9,209.19,269.41,227.47,276.78,288.09,234.1,302.87,286.56,286.79,283.07,257.29,325.37,281.08,319.97,311.55,302.62,305.08,297.08,348.87,373.96,354.3,325.67,356.52,312.25,367.15,364.21,348.52,342.63,357.33,349.35,296.04,383.41,306.23,359.59,360.13,314.51,329.96,285.16,288.43,315.43,323.91,305.07,271.43,261.83,298.6,267.55,277.05,226.12,243.26,253.06,249.21,233.09,200.85,242.37,194.44,217.49,239.06,205.43,204.54,183.07,178.86,185.93,131.41,182.13,148.4,149.04,163.28,105.71,150.09,120.99,111.52,126.18,81.08,102.32,92.43,92.77,97.69,73.51,88.04,66.58,64.38,80.02,53.55,75.17,51.09,54.64,66.04,36.83,58.07,36.42,40.4,45.15,22.15,47.21,25.93,26.29,35.76,9.53,35.85,13.05,18.46,27.81,3.53,28.86,5.24,14.19,19.97,-3.62,23.02,-1.3,7.76,13.54,-8.57,18.2,-6.02,5.23,7.91,-12.05,15.57,-11.28,2.03,4.86,-15.06,12.93,-14.29,0.45,1.14,-15.67,9.6,-16.2,0.11,-2.45,-15.38,8.97,-18.73,0.41,-2.51,-14.61,8.73,-17.46,-0.02,-5.79,-15.84,8.3,-18.67,4.26,-6.65,-12.46,9.83,-17.54,1.92,-3.93,-12.38,9.77,-18.59,7.73,-8.29,-8.29,5.91,-19.47,9.15,-3.95,-7.25,11.91,-19.29,9.97,-12.38,-9.36,7.46,-21.96,2.73,-16.3,-7.1,-0.38,-20.53,8.21,-19.34,-9.4,-1.37,-30.28,-3.17,-21.35,-10.12,-2.06,-32.39,-4.75,-23.52,-14.24,-7.91,-30.15,-11.53,-35.22,-18.84,-10.74,-44.62,-13.02,-44.45,-29.97,-23.82,-50.36,-12.07,-51.5,-36.03,-24.78,-50.26,-26.92,-39.6,-47.08,-31.35,-62.4,-18.36,-61.68,-43.8,-29.52,-48.74,-28.82,-66.85,-52.1,-42.32,-65.38,-34.52,-70.84,-50.74,-59.58,-57.88,-42.7,-68.09,-41.28,-55.05,-61.85,-35.16,-77.97,-40.61,-46.29,-51.35,-28.13,-55.86,-51.34,-39.33,-50.88,-37.1,-78.5,-55.95,-51.54,-62.43,-25.33,-70.4,-36.32,-61.77,-62.39,-41.71,-79.17,-49.17,-54.47,-49.9,-45.5,-77.05,-42.65,-47.93,-48.98,-24.86,-61.82,-21.9,-41.99,-62.74,-43.33,-77.4,-39.34,-42.05,-61.06,-46.77,-59.1,-38.8,-66.23,-51.4,-49.7,-66.09,-30.66,-68.07,-61.45,-25.37,-66.93,-37.6,-52.36,-58.13,-27.3,-76.2,-38.27,-64.1,-59.62,-29.47,-68.66,-27.45,-54.28,-50.52,-51.07,-56.66,-40.42,-60.36,-48.39,-49.05,-69.01,-31.92,-60.57,-42.73,-31.45,-60.09,-32.79,-55.46,-41.15,-40.97,-51.31,-34.63,-50.64,-41.65,-42.02,-56.24,-14.09,-41.15,-32.57,-32.14,-43.45,-20.49,-41.66,-22.79,-28.56,-40.68,-10.95,-45.49,-12.5,-25.44,-28.76,-11.75,-36.29,-13.13,-18.23,-22.94,-2.75,-27.62,-5,-21.13,-21.35,4.73,-27.43,3.46,-10.66,-13.35,0.83,-27,1.63,-13.45</v>
       </c>
     </row>
     <row r="62">
@@ -1078,7 +1078,7 @@
         <v>[L_03_标记]</v>
       </c>
       <c r="C62" t="str">
-        <v>94.4uv</v>
+        <v>a: 17.8ms -38.6uv b: 41.8ms 272.1uv</v>
       </c>
     </row>
     <row r="63">
@@ -1089,7 +1089,7 @@
         <v>[R_04_名字]</v>
       </c>
       <c r="C63" t="str">
-        <v>FERG(4)_lCone</v>
+        <v>FERG(4)_dRod</v>
       </c>
     </row>
     <row r="64">
@@ -1111,7 +1111,7 @@
         <v>[R_04_闪光]</v>
       </c>
       <c r="C65" t="str">
-        <v>白色光: 3.00 cd·s/m²</v>
+        <v>b白色光:0.30cd.m-2,5ms</v>
       </c>
     </row>
     <row r="66">
@@ -1122,7 +1122,7 @@
         <v>[R_04_闪光背景]</v>
       </c>
       <c r="C66" t="str">
-        <v>白色背景光</v>
+        <v>b背景光_关:0.0cd.m-2</v>
       </c>
     </row>
     <row r="67">
@@ -1133,7 +1133,7 @@
         <v>[R_04_采样]</v>
       </c>
       <c r="C67" t="str">
-        <v>刺激间隔: 15.0S</v>
+        <v>刺激间隔:10.0S</v>
       </c>
     </row>
     <row r="68">
@@ -1144,7 +1144,7 @@
         <v>[R_04_分析时间]</v>
       </c>
       <c r="C68" t="str">
-        <v>200 ms</v>
+        <v>200ms</v>
       </c>
     </row>
     <row r="69">
@@ -1166,7 +1166,7 @@
         <v>[R_04_详细数据(uv)]</v>
       </c>
       <c r="C70" t="str">
-        <v>0.54,-1.07,1.55,-1.99,2.36,-2.66,2.87,-2.98,2.99,-2.91,2.73,-2.46,2.11,-1.69,1.22,-0.7,0.16,0.38,-0.91,1.41,-1.87,2.26,-2.58,2.81,-2.96,3,-2.95,2.79,-2.55,2.22,-1.83,1.36,-0.86,0.32,0.21,-0.77,1.25,-1.76,2.12,-2.53,2.71,-2.98,2.92,-3.06,2.73,-2.78,2.15,-2.18,1.23,-1.36,0.07,-0.46,-1.22,0.36,-2.51,0.94,-3.7,1.14,-4.72,0.82,-5.53,-0.08,-6.17,-1.59,-6.72,-3.7,-7.29,-6.34,-8.06,-9.43,-9.18,-12.85,-10.82,-16.47,-13.12,-20.2,-16.13,-23.92,-19.88,-27.56,-24.28,-31.06,-29.18,-34.38,-34.35,-37.49,-39.51,-40.37,-44.33,-42.96,-48.5,-45.19,-51.7,-46.99,-53.68,-48.22,-54.24,-48.74,-53.27,-48.38,-50.75,-46.99,-46.72,-44.4,-41.33,-40.5,-34.74,-35.2,-27.16,-28.47,-18.79,-20.36,-9.83,-10.95,-0.43,-0.4,9.31,11.09,19.34,23.27,29.67,35.92,40.31,48.79,51.34,61.68,62.81,74.42,74.76,86.91,87.19,99.08,100.07,110.95,113.31,122.57,126.79,134.01,140.35,145.37,153.78,156.74,166.9,168.18,179.52,179.7,191.48,191.26,202.65,202.76,212.97,214.05,222.38,224.93,230.89,235.14,238.52,244.45,245.3,252.6,251.25,259.39,256.39,264.64,260.7,268.26,264.13,270.21,266.58,270.51,267.94,269.27,268.1,266.6,266.92,262.68,264.29,257.69,260.15,251.78,254.49,245.11,247.35,237.79,238.83,229.88,229.1,221.42,218.4,212.43,206.97,202.88,195.08,192.78,183.01,182.13,170.98,170.97,159.21,159.36,147.83,147.42,136.93,135.32,126.53,123.24,116.62,111.39,107.13,99.99,97.98,89.22,89.11,79.26,80.46,70.21,71.99,62.13,63.72,55.01,55.7,48.8,48.02,43.36,40.79,38.56,34.12,34.24,28.14,30.23,22.93,26.4,18.55,22.66,15.01,18.95,12.25,15.28,10.18,11.7,8.66,8.28,7.52,5.12,6.6,2.34,5.71,0.03,4.73,-1.76,3.55,-3,2.13,-3.72,0.47,-4,-1.37,-3.95,-3.31,-3.73,-5.21,-3.48,-6.95,-3.36,-8.43,-3.49,-9.55,-3.96,-10.27,-4.81,-10.59,-6.02,-10.57,-7.53,-10.3,-9.24,-9.91,-11.02,-9.55,-12.72,-9.36,-14.22,-9.45,-15.43,-9.92,-16.27,-10.79,-16.75,-12.06,-16.89,-13.66,-16.79,-15.5,-16.57,-17.43,-16.36,-19.32,-16.3,-21.03,-16.52,-22.46,-17.09,-23.53,-18.08,-24.23,-19.45,-24.58,-21.17,-24.66,-23.12,-24.59,-25.19,-24.5,-27.22,-24.53,-29.07,-24.8,-30.64,-25.41,-31.85,-26.4,-32.67,-27.77,-33.11,-29.47,-33.25,-31.41,-33.2,-33.46,-33.08,-35.47,-33.04,-37.31,-33.2,-38.85,-33.67,-40.02,-34.48,-40.77,-35.67,-41.11,-37.16,-41.12,-38.89,-40.89,-40.72,-40.55,-42.52,-40.25,-44.13,-40.11,-45.45,-40.23,-46.37,-40.68,-46.86,-41.47,-46.91,-42.57,-46.6,-43.9,-46.01,-45.33,-45.28,-46.72,-44.54,-47.95,-43.93,-48.87,-43.56,-49.4,-43.5,-49.48,-43.77,-49.13,-44.34,-48.38,-45.15,-47.33,-46.08,-46.12,-47,-44.87,-47.75,-43.74,-48.23,-42.83,-48.32,-42.22,-47.98,-41.95,-47.2,-42,-46.03,-42.3,-44.55,-42.75,-42.89,-43.22,-41.19,-43.57,-39.6,-43.67,-38.23,-43.42,-37.17,-42.75,-36.46,-41.66,-36.11,-40.19,-36.03,-38.41,-36.15,-36.46,-36.33,-34.47,-36.42,-32.59,-36.31,-30.93,-35.89,-29.61,-35.08,-28.65,-33.87,-28.07,-32.29,-27.82,-30.42,-27.79,-28.38,-27.87,-26.3,-27.92,-24.33,-27.79,-22.59,-27.39,-21.19,-26.64,-20.19,-25.5,-19.58,-24.01,-19.33,-22.23,-19.34,-20.28,-19.49,-18.29,-19.65,-16.4,-19.68,-14.74,-19.45,-13.43,-18.9,-12.51,-17.98,-12.01,-16.7,-11.88,-15.14,-12.04,-13.39,-12.38,-11.59,-12.74,-9.88,-13,-8.4,-13.04,-7.24,-12.75,-6.48,-12.1,-6.13,-11.1,-6.18,-9.8,-6.52,-8.29,-7.06,-6.72,-7.66,-5.21,-8.16,-3.9,-8.45,-2.9,-8.43,-2.29,-8.05,-2.1,-7.31,-2.29,-6.25,-2.8,-4.97</v>
+        <v>-18.9,-24.4,-17.9,-24.86,-17.04,-25.1,-16.35,-25.11,-15.84,-24.87,-15.55,-24.39,-15.46,-23.67,-15.58,-22.75,-15.88,-21.65,-16.34,-20.44,-16.93,-19.13,-17.6,-17.81,-18.31,-16.49,-19.05,-15.26,-19.73,-14.23,-20.36,-13.3,-20.83,-12.77,-21.27,-12.38,-21.38,-12.24,-21.54,-12.48,-21.3,-13.08,-21.41,-14.17,-21.02,-15.36,-20.81,-16.38,-20.92,-17.91,-20.26,-19.73,-20.28,-21.79,-19.42,-24.86,-20.17,-27.19,-20.84,-28.91,-20.67,-31.38,-22.2,-32,-24.56,-34.82,-24.36,-37.33,-31.68,-35.72,-28.97,-39.93,-32.02,-40.52,-41.74,-41.94,-36.29,-48.23,-38.23,-48.96,-52.86,-46.03,-45.7,-51.71,-49.61,-52.48,-54.32,-51.85,-54.93,-36.63,-46.58,-38.4,-51.57,-49.42,-62.61,-46.62,-47.78,-39.27,-55.33,-47.14,-28.52,-17.21,-30.57,-22.56,-29.14,-22.35,-14.74,-12.88,-7.35,-5.84,2.07,1.7,19.92,8.23,26.28,27.22,30,44.92,38.87,52.05,54.26,42.29,63.6,77.62,93.59,74.05,90.47,97.51,115.79,112.12,116.6,126.39,135.79,153.16,162.46,146.94,165.21,170.06,185.16,173,165.66,186.34,185.06,215.48,207.46,240.91,204.51,245.98,206.39,237.41,260,242.54,230.29,280.56,267.76,277.59,279.53,242.95,261.08,274.59,290.99,301.37,317.88,298.08,286.97,313.35,281.05,328.93,277.35,277.18,304.03,264.61,321.16,256.29,329.42,289.24,328.24,293.41,276.36,277.57,295.17,314.32,283.93,249.13,258.31,302.97,293.61,297.11,297.09,267.65,274.89,263.88,271.48,220.82,222.27,226.99,209.41,208.67,197.2,218.49,232.83,194.11,221.85,179.86,169.62,191.98,161.47,181.05,179.53,166.75,163.1,173.28,147.32,151.36,147.08,131.33,143.74,128.19,126.21,125.81,111.69,109.34,101.59,101.7,89.27,89.98,79.03,68.94,89.35,78.2,78.04,51.69,58.69,47,56.56,52.53,48.49,41.42,48.82,28.35,45.03,29.57,29.65,23.94,23.37,25.31,23.09,15.72,14.12,13.35,10.97,10.12,8.59,7.76,5.48,9.34,1.04,4.74,-2.65,3.93,-7.14,2.47,-7.29,0.7,-9.5,-0.34,-10.75,-3.89,-12.42,-4.63,-13.18,-7.36,-11.91,-8.94,-13.64,-9.67,-12.15,-12.24,-11.26,-12.24,-11.14,-14.85,-10,-17.48,-10.73,-18.65,-11.41,-19.09,-8.71,-20.36,-9.83,-21.15,-11.48,-19.21,-10.14,-22.65,-12.08,-20.28,-11.33,-18.48,-12.52,-18.97,-15.44,-17.26,-16.33,-15.88,-22.51,-21.66,-20.71,-19.89,-26.3,-20.54,-26.16,-23.45,-31.32,-24.1,-28.13,-20.31,-33.8,-18.06,-31.51,-27.93,-28.92,-19.77,-37.83,-21.52,-39.36,-22.88,-33.41,-26.87,-27.95,-34.03,-32.89,-28.49,-39.36,-33.08,-35.4,-46.14,-28.04,-38.35,-31.96,-47.85,-30.72,-36.47,-34.68,-42.41,-29.25,-46.21,-34.59,-55.39,-41,-45.43,-43.66,-43.4,-36.29,-38.92,-45.51,-57.74,-40.66,-47.11,-46.66,-49.66,-60.78,-37.89,-57.93,-58.63,-41.06,-38.25,-42.72,-52.02,-58.12,-41.64,-63.31,-39.37,-47.4,-49.4,-65.01,-59.07,-53.3,-44.59,-49.31,-47.45,-52.26,-47.38,-50.25,-41.25,-65.44,-50.22,-67.35,-58.62,-56.84,-59.85,-54.31,-54.53,-48.93,-63.31,-56.32,-55.43,-64.31,-51.65,-59.83,-62.51,-37.14,-50.23,-62.29,-62.08,-48.11,-55.58,-66.53,-52.93,-53.33,-46.52,-39.99,-71.98,-48.18,-53,-50.97,-50.89,-52.51,-47.36,-58.26,-51.82,-61.62,-57.5,-60.67,-57.68,-57.82,-46.62,-56.26,-59.55,-63.86,-37.61,-44.98,-45.84,-49.37,-57.4,-55.3,-46.09,-48.72,-51.48,-44.94,-35.92,-40.21,-47.51,-51.2,-53.13,-49.7,-48.13,-47.14,-50.63,-37.08,-33.7,-29.08,-46.94,-25.89,-48.49,-25.15,-45.86,-30.91,-37.4,-23.36,-42.15,-35.58,-28.45,-19.94,-41.02,-32.24,-24.89,-20.6,-27.76,-19.79,-21.71,-29.09,-27.22,-17.62,-19.71,-24.9,-16.09,-18.69,-19.16,-22.73,-17.26,-23.43,-13.9,-19.16,-9.69,-17.81,-8.85,-19.56,-10.35,-25.21,-13.8,-22.12,-12.13,-20.33,-9.67,-17.92,-13.42,-21.51,-18.31</v>
       </c>
     </row>
     <row r="71">
@@ -1177,7 +1177,7 @@
         <v>[R_04_标记]</v>
       </c>
       <c r="C71" t="str">
-        <v>a: 21.2ms -62.1uv b: 46.2ms 269.1uv</v>
+        <v>a: 19.8ms -33.5uv b: 44.4ms 241.5uv</v>
       </c>
     </row>
     <row r="72">
@@ -1188,7 +1188,7 @@
         <v>[L_04_名字]</v>
       </c>
       <c r="C72" t="str">
-        <v>FERG(4)_lCone</v>
+        <v>FERG(4)_dRod</v>
       </c>
     </row>
     <row r="73">
@@ -1210,7 +1210,7 @@
         <v>[L_04_闪光]</v>
       </c>
       <c r="C74" t="str">
-        <v>白色光: 3.00 cd·s/m²</v>
+        <v>b白色光:0.30cd.m-2,5ms</v>
       </c>
     </row>
     <row r="75">
@@ -1221,7 +1221,7 @@
         <v>[L_04_闪光背景]</v>
       </c>
       <c r="C75" t="str">
-        <v>白色背景光</v>
+        <v>b背景光_关:0.0cd.m-2</v>
       </c>
     </row>
     <row r="76">
@@ -1232,7 +1232,7 @@
         <v>[L_04_采样]</v>
       </c>
       <c r="C76" t="str">
-        <v>刺激间隔: 15.0S</v>
+        <v>刺激间隔:10.0S</v>
       </c>
     </row>
     <row r="77">
@@ -1243,7 +1243,7 @@
         <v>[L_04_分析时间]</v>
       </c>
       <c r="C77" t="str">
-        <v>200 ms</v>
+        <v>200ms</v>
       </c>
     </row>
     <row r="78">
@@ -1265,7 +1265,7 @@
         <v>[L_04_详细数据(uv)]</v>
       </c>
       <c r="C79" t="str">
-        <v>-0.56,1.1,-1.61,2.05,-2.43,2.71,-2.91,2.99,-2.98,2.85,-2.63,2.31,-1.91,1.45,-0.93,0.38,0.18,-0.74,1.27,-1.76,2.18,-2.53,2.79,-2.95,3,-2.95,2.79,-2.54,2.19,-1.77,1.28,-0.76,0.19,0.36,-0.93,1.43,-1.92,2.29,-2.65,2.82,-3.02,2.94,-2.98,2.63,-2.54,1.93,-1.79,0.9,-0.84,-0.31,0.15,-1.57,1.01,-2.75,1.56,-3.73,1.68,-4.45,1.25,-4.89,0.25,-5.12,-1.33,-5.24,-3.42,-5.42,-5.93,-5.84,-8.73,-6.71,-11.71,-8.18,-14.75,-10.39,-17.78,-13.37,-20.75,-17.12,-23.65,-21.51,-26.49,-26.37,-29.31,-31.43,-32.14,-36.41,-34.99,-41,-37.82,-44.9,-40.56,-47.85,-43.08,-49.65,-45.2,-50.18,-46.7,-49.39,-47.33,-47.3,-46.87,-44,-45.1,-39.61,-41.87,-34.27,-37.1,-28.15,-30.79,-21.36,-23.03,-13.99,-13.98,-6.11,-3.89,2.29,7,11.21,18.38,20.7,30,30.79,41.63,41.51,53.1,52.84,64.32,64.73,75.28,77.08,86.01,89.77,96.63,102.62,107.25,115.44,118.01,128.05,129.01,140.3,140.3,152.05,151.88,163.22,163.67,173.76,175.53,183.7,187.25,193.06,198.59,201.9,209.28,210.26,219.08,218.18,227.76,225.64,235.15,232.59,241.14,238.92,245.69,244.47,248.83,249.05,250.63,252.48,251.22,254.55,250.71,255.11,249.24,254.05,246.9,251.34,243.75,247,239.83,241.17,235.1,234.01,229.53,225.76,223.06,216.67,215.64,207,207.24,197,197.87,186.86,187.62,176.73,176.61,166.69,165.02,156.78,153.09,146.98,141.08,137.23,129.25,127.5,117.83,117.73,107.04,107.9,97.01,98.05,87.82,88.23,79.47,78.58,71.9,69.25,65.01,60.39,58.65,52.19,52.67,44.79,46.95,38.28,41.39,32.73,35.93,28.11,30.59,24.35,25.41,21.3,20.5,18.8,15.96,16.66,11.94,14.69,8.52,12.73,5.78,10.67,3.74,8.46,2.37,6.1,1.55,3.64,1.16,1.2,1.02,-1.1,0.94,-3.13,0.77,-4.77,0.36,-5.95,-0.38,-6.63,-1.48,-6.86,-2.9,-6.72,-4.56,-6.33,-6.34,-5.87,-8.08,-5.48,-9.64,-5.33,-10.9,-5.52,-11.77,-6.14,-12.24,-7.17,-12.31,-8.59,-12.09,-10.27,-11.69,-12.08,-11.28,-13.87,-11,-15.48,-11,-16.8,-11.38,-17.73,-12.2,-18.27,-13.45,-18.44,-15.07,-18.34,-16.94,-18.08,-18.91,-17.83,-20.84,-17.75,-22.56,-17.95,-23.96,-18.55,-24.98,-19.57,-25.58,-21.01,-25.81,-22.79,-25.78,-24.78,-25.61,-26.84,-25.45,-28.82,-25.46,-30.55,-25.77,-31.93,-26.46,-32.89,-27.57,-33.42,-29.05,-33.59,-30.85,-33.48,-32.81,-33.24,-34.8,-33.01,-36.64,-32.96,-38.21,-33.2,-39.39,-33.81,-40.12,-34.81,-40.41,-36.16,-40.31,-37.78,-39.95,-39.52,-39.45,-41.24,-38.98,-42.77,-38.68,-43.98,-38.67,-44.77,-39.02,-45.09,-39.73,-44.96,-40.78,-44.45,-42.05,-43.67,-43.41,-42.77,-44.7,-41.91,-45.78,-41.23,-46.5,-40.84,-46.78,-40.81,-46.58,-41.14,-45.94,-41.78,-44.92,-42.63,-43.66,-43.53,-42.3,-44.35,-41.01,-44.92,-39.92,-45.13,-39.15,-44.89,-38.74,-44.19,-38.69,-43.05,-38.95,-41.57,-39.41,-39.87,-39.91,-38.13,-40.32,-36.48,-40.47,-35.08,-40.25,-34.02,-39.6,-33.34,-38.51,-33.04,-37.01,-33.05,-35.2,-33.26,-33.23,-33.51,-31.25,-33.65,-29.42,-33.54,-27.87,-33.08,-26.7,-32.19,-25.93,-30.89,-25.56,-29.21,-25.51,-27.27,-25.64,-25.21,-25.82,-23.19,-25.89,-21.37,-25.71,-19.86,-25.18,-18.76,-24.24,-18.09,-22.9,-17.83,-21.23,-17.87,-19.33,-18.1,-17.35,-18.37,-15.46,-18.51,-13.79,-18.4,-12.47,-17.94,-11.58,-17.08,-11.13,-15.83,-11.08,-14.28,-11.33,-12.53,-11.75,-10.73,-12.19,-9.04,-12.49,-7.62,-12.52,-6.56,-12.19,-5.94,-11.46,-5.76,-10.36,-5.96,-8.97,-6.46,-7.4,-7.1,-5.81,-7.72,-4.36,-8.19,-3.19,-8.36,-2.39,-8.16,-2.04,-7.56,-2.11,-6.59,-2.56,-5.34,-3.27,-3.94</v>
+        <v>17.86,2.8,14.07,7.46,9.3,12.7,4.71,17.35,1.43,20.38,0.3,21.15,1.66,19.59,5.3,16.15,10.48,11.76,16.1,7.58,20.97,4.71,24.08,3.96,24.83,5.62,23.17,9.45,19.62,14.65,15.12,20.12,10.83,24.67,7.84,27.33,6.93,27.52,8.36,25.25,11.83,21.11,16.57,16.03,21.44,11.19,25.25,7.57,27.08,6.22,26.39,6.94,22.97,9.91,17.87,13.61,11.91,17.54,6.06,20.27,2,20.6,-0.34,19.43,-0.06,13.93,1.31,7.41,3.92,1.47,6.33,-6.13,7.05,-10.25,6.81,-15.11,3.2,-14.48,-4.46,-13.73,-9.69,-14.08,-15.79,-15.13,-24.62,-18.2,-37.77,-16.12,-33.19,-17.86,-42.48,-25.99,-37.99,-38.01,-34.11,-40.5,-35.91,-51.89,-33.41,-40.56,-18.07,-54.65,-28.14,-45.63,-28.67,-36.64,-29.68,-21.97,-30.08,-9.8,-17.61,-10.7,-28.53,-1.74,-9.71,4.15,-11.46,22,-1.59,23.03,21.71,21.1,31.98,35.14,58.61,47.25,68.81,59.15,79.76,72.52,88.98,88.35,92.24,118.51,111.78,141.72,117.96,138.11,128.5,148.33,150.69,191.17,165.17,189.93,193.45,198.42,197.04,216.42,239.31,224.76,233.06,208.45,252.33,237.53,244.8,242.11,247.44,285.58,303.86,278.77,274.6,296.24,318.27,293.92,288.2,338.37,313.33,305.43,329.75,316.25,338.99,324.89,333.85,288.97,316.1,340.84,343.78,293.38,313.44,338.75,367.39,307.65,292.26,337.32,336.67,327.82,310.71,332.37,267.68,318.1,273.17,305.5,306.39,312.62,256.26,282.69,278.71,246.9,284.8,236.35,261.38,213.6,265.26,218.1,227.1,198.23,234.2,222.59,228.3,213.65,175.69,169.21,177.22,168.4,171.1,169.46,158.23,153.91,132.08,159.19,124.7,132.04,122.13,121.79,117.82,109.55,102.25,94.78,106.11,82.21,95.64,74.29,76.52,63.07,67.68,61.8,52.68,58.02,42.17,58.83,35.56,54.54,26.63,48.93,25.35,38.7,24.71,32.46,24.32,21.44,28.6,13.92,29.18,9.34,28.23,4.27,24.36,3.48,18.24,5.69,11.4,8.43,5.66,13.17,-1.76,14.66,-4.18,15.07,-5.59,13.12,-3.98,9.91,-2.3,3.79,2.94,-2.07,7.9,-5.13,11.73,-8.63,11.28,-8.16,12.3,-6.74,8.53,-1.21,1.95,3.62,-1.72,8.18,-7.16,11.91,-9.76,10.63,-8.95,12.15,-4.3,6.15,-0.78,3.93,2.21,0.01,4.95,-4.97,9.28,-9.37,11.8,-11.92,7.53,-10.04,6.5,-7.65,0.65,0.06,-7.97,1.08,-13.69,0.78,-13.09,0.33,-14.29,2.95,-17.58,-3.17,-10.76,-11.57,-12.06,-17.2,-5.77,-23.75,-4.09,-30.61,-12.71,-25.88,-14.17,-30.44,-15.81,-27.07,-18.5,-23.78,-30.22,-12.65,-38.11,-19.52,-39.92,-18.1,-34.84,-15.95,-39.29,-21.67,-26.2,-39.77,-30.61,-41.39,-22.87,-45.95,-29.47,-38.91,-31.4,-44.87,-34.18,-41.15,-24.78,-33.53,-47.54,-43.99,-40.71,-35.65,-58.97,-23.01,-57.3,-35.74,-47.07,-23.76,-35.56,-24.24,-44.4,-44.91,-45.62,-48.19,-35.3,-37.16,-21.17,-56.48,-44.43,-41.12,-27.76,-45.48,-45.41,-38.86,-38.5,-42.23,-38.99,-32.74,-50.88,-41.38,-42.74,-40.1,-59.9,-29.11,-56.09,-53.26,-33.33,-49.55,-46.23,-60.46,-27.5,-56.38,-43.67,-45.31,-50.32,-66.33,-40.6,-50.44,-42.11,-59.29,-40.94,-55.39,-67.46,-38.11,-60.98,-45.95,-70.41,-42.43,-68.6,-45.82,-46.32,-59.67,-47.31,-52.26,-55.74,-49.16,-44.18,-51.18,-50.39,-47.11,-26.83,-66.22,-39.62,-62.78,-39.42,-31.94,-57.44,-48.24,-51.04,-45.32,-45.21,-39.99,-50.15,-25.02,-36.85,-40.79,-32.63,-44.58,-32.7,-44.26,-33.91,-41.47,-24.71,-42.88,-27.98,-42.14,-25.58,-41.24,-29.7,-36.55,-18,-18.77,-33.95,-22.83,-29.37,-19.96,-28.68,-5.82,-34.96,-8.16,-20.27,-8.89,-15.49,-16.88,-11.44,-20.3,-4.79,-28.39,-1.01,-19.01,0.13,-25.88,-8.18,-21.71,-9.86,-16.98,-10.57,-4.8,-15.86,-0.13,-15.81,-4.28,-23.16,3.47</v>
       </c>
     </row>
     <row r="80">
@@ -1276,7 +1276,7 @@
         <v>[L_04_标记]</v>
       </c>
       <c r="C80" t="str">
-        <v>a: 21.2ms -58.4uv b: 46.2ms 253.0uv</v>
+        <v>a: 19.8ms -34.4uv b: 44.5ms 266.9uv</v>
       </c>
     </row>
     <row r="81">
@@ -1287,7 +1287,7 @@
         <v>[R_05_名字]</v>
       </c>
       <c r="C81" t="str">
-        <v>FERG(5)_Flicker</v>
+        <v>FERG(5)_dRod</v>
       </c>
     </row>
     <row r="82">
@@ -1298,7 +1298,7 @@
         <v>[R_05_放大器]</v>
       </c>
       <c r="C82" t="str">
-        <v>1-300 Hz</v>
+        <v>1-75 Hz</v>
       </c>
     </row>
     <row r="83">
@@ -1309,7 +1309,7 @@
         <v>[R_05_闪光]</v>
       </c>
       <c r="C83" t="str">
-        <v>白色光: 3.00 cd·s/m²</v>
+        <v>b白色光:1.0cd.m-2,5ms</v>
       </c>
     </row>
     <row r="84">
@@ -1320,7 +1320,7 @@
         <v>[R_05_闪光背景]</v>
       </c>
       <c r="C84" t="str">
-        <v>白色背景光</v>
+        <v>b背景光_关:0.0cd.m-2</v>
       </c>
     </row>
     <row r="85">
@@ -1331,7 +1331,7 @@
         <v>[R_05_采样]</v>
       </c>
       <c r="C85" t="str">
-        <v>刺激间隔: 50.0S</v>
+        <v>刺激间隔:10.0S</v>
       </c>
     </row>
     <row r="86">
@@ -1342,7 +1342,7 @@
         <v>[R_05_分析时间]</v>
       </c>
       <c r="C86" t="str">
-        <v>500 ms</v>
+        <v>200ms</v>
       </c>
     </row>
     <row r="87">
@@ -1364,7 +1364,7 @@
         <v>[R_05_详细数据(uv)]</v>
       </c>
       <c r="C88" t="str">
-        <v>57.32,61.92,61.97,68.2,66.09,73.37,69.64,77.16,72.53,79.41,74.67,80.04,75.92,79.06,76.12,76.54,75.11,72.63,72.76,67.52,68.95,61.42,63.64,54.55,56.88,47.09,48.78,39.21,39.54,31.03,29.43,22.65,18.79,14.12,7.98,5.5,-2.63,-3.15,-12.71,-11.75,-21.96,-20.21,-30.16,-28.38,-37.17,-36.09,-42.95,-43.15,-47.52,-49.35,-50.97,-54.5,-53.44,-58.45,-55.09,-61.07,-56.08,-62.35,-56.53,-62.31,-56.56,-61.08,-56.22,-58.85,-55.55,-55.87,-54.52,-52.41,-53.12,-48.78,-51.33,-45.23,-49.12,-41.98,-46.51,-39.18,-43.57,-36.91,-40.37,-35.15,-37.04,-33.84,-33.72,-32.82,-30.55,-31.91,-27.65,-30.93,-25.11,-29.68,-22.95,-28,-21.15,-25.8,-19.6,-23.02,-18.14,-19.65,-16.58,-15.74,-14.68,-11.37,-12.22,-6.65,-9,-1.66,-4.89,3.51,0.18,8.8,6.2,14.2,13.07,19.7,20.59,25.34,28.53,31.14,36.6,37.11,44.49,43.24,51.9,49.47,58.58,55.67,64.32,61.69,68.97,67.28,72.46,72.19,74.75,76.14,75.88,78.85,75.9,80.1,74.89,79.7,72.91,77.57,70.01,73.69,66.23,68.17,61.56,61.18,56.01,52.98,49.57,43.88,42.23,34.2,34.05,24.27,25.1,14.39,15.52,4.82,5.51,-4.26,-4.68,-12.71,-14.74,-20.47,-24.38,-27.53,-33.27,-33.89,-41.13,-39.58,-47.73,-44.64,-52.93,-49.06,-56.65,-52.85,-58.92,-55.95,-59.86,-58.3,-59.65,-59.84,-58.52,-60.5,-56.75,-60.25,-54.57,-59.08,-52.23,-57.05,-49.91,-54.27,-47.73,-50.89,-45.74,-47.13,-43.95,-43.22,-42.3,-39.38,-40.69,-35.84,-39.03,-32.76,-37.22,-30.26,-35.19,-28.34,-32.91,-26.97,-30.36,-26.01,-27.59,-25.27,-24.64,-24.51,-21.6,-23.49,-18.51,-21.97,-15.42,-19.75,-12.33,-16.69,-9.2,-12.72,-5.94,-7.86,-2.45,-2.18,1.41,4.16,5.79,10.98,10.78,18.07,16.46,25.22,22.82,32.24,29.8,38.97,37.25,45.28,44.94,51.12,52.59,56.42,59.86,61.18,66.44,65.36,72,68.94,76.27,71.88,79.05,74.1,80.22,75.47,79.73,75.87,77.64,75.14,74.07,73.14,69.21,69.76,63.26,64.93,56.45,58.65,48.99,51,41.07,42.14,32.85,32.31,24.44,21.82,15.91,11.02,7.33,0.28,-1.25,-10.05,-9.77,-19.64,-18.15,-28.25,-26.27,-35.69,-34,-41.88,-41.16,-46.81,-47.55,-50.56,-52.98,-53.23,-57.29,-55,-60.35,-56.02,-62.08,-56.47,-62.49,-56.47,-61.67,-56.11,-59.76,-55.44,-57,-54.46,-53.65,-53.17,-50,-51.54,-46.32,-49.53,-42.87,-47.14,-39.82,-44.41,-37.29,-41.38,-35.3,-38.17,-33.81,-34.88,-32.71,-31.67,-31.81,-28.65,-30.93,-25.92,-29.86,-23.56,-28.43,-21.54,-26.5,-19.82,-23.98,-18.25,-20.84,-16.67,-17.11,-14.85,-12.84,-12.58,-8.15,-9.64,-3.12,-5.87,2.12,-1.17,7.52,4.5,13.02,11.05,18.59,18.35,24.25,26.18,30.02,34.25,35.91,42.27,41.93,49.93,48.03,56.94,54.12,63.06,60.08,68.11,65.69,71.98,70.72,74.63,74.91,76.05,77.98,76.3,79.67,75.45,79.8,73.59,78.23,70.79,74.91,67.1,69.91,62.55,63.35,57.16,55.47,50.92,46.56,43.83,36.94,35.92,26.96,27.26,16.92,17.95,7.12,8.15,-2.22,-1.9,-10.93,-11.95,-18.93,-21.68,-26.18,-30.79,-32.67,-38.99,-38.45,-46.03,-43.55,-51.71,-48.01,-55.93,-51.83,-58.68,-55,-60.03,-57.47,-60.14,-59.19,-59.22,-60.09,-57.54,-60.14,-55.35,-59.3,-52.92,-57.6,-50.45,-55.12,-48.1,-51.99,-45.96,-48.39,-44.06,-44.54,-42.35,-40.66,-40.77,-36.98,-39.2,-33.68,-37.55,-30.91,-35.71,-28.72,-33.62,-27.09,-31.25,-25.95,-28.61,-25.11,-25.74,-24.37,-22.7,-23.47,-19.56,-22.17,-16.38,-20.26,-13.16,-17.54,-9.92,-13.93,-6.58,-9.4,-3.07,-3.99,0.74,2.17,4.98,8.91,9.77,16.02,15.19,23.28,21.27,30.47,27.98,37.41,35.21,43.96,42.75,50.01,50.37,55.49,57.75</v>
+        <v>-7.45,2.61,-3.48,-0.75,1.08,-4.18,5.16,-6.66,7.8,-7.41,8.44,-6.14,7.01,-3.06,3.98,1.1,0.24,5.34,-3.16,8.61,-5.28,10.1,-5.53,9.47,-3.8,6.88,-0.56,3,3.35,-1.16,6.85,-4.57,9.01,-6.36,9.16,-6.13,7.2,-4.13,3.55,-0.87,-1.04,2.67,-5.34,5.22,-8.42,6.25,-9.77,5.41,-8.89,1.95,-6.49,-2.24,-3.14,-7.18,-0.19,-11.56,1.82,-14.33,0.65,-15.01,-1,-13.82,-5.62,-11.71,-9.71,-7.67,-15.83,-5.83,-20.3,-3.53,-21.03,-6.7,-21.7,-10.65,-21.77,-15.48,-21.29,-22.11,-13.33,-24.3,-11.78,-33.36,-13.71,-28.5,-19.54,-35.37,-21.3,-27.44,-22.87,-32.61,-37.23,-22.37,-30.16,-30.42,-44.52,-20.81,-39.28,-29.38,-40.72,-21.71,-27.89,-39.73,-18.82,-41.75,-21.13,-29.38,-19.38,-27.04,-22.03,-20.29,-0.26,-5.43,-5.06,-1.42,-0.22,5.1,11.22,7.18,15.67,28.76,24.6,40.07,37.75,33.77,33.34,39.67,75.53,57.45,78.73,74.55,93.49,64.69,97.6,97.11,123.82,112.69,139.12,117.52,114.05,149.28,147.72,167.51,166.8,171.08,161.16,178.12,198.58,224.55,214.9,224.08,217.8,208.09,255.06,225.67,256.61,228.57,272.44,231.79,284.03,265.68,274.91,271.48,308.41,275.76,263.44,269.21,302.93,309.59,287.47,341.89,321.32,282.79,336.8,300.28,326.25,355.65,359.79,334.45,368.93,328.34,350.52,356.21,339.03,319.94,297.04,341.47,340.96,359.26,318.14,294.66,327.1,296.11,296.53,321.22,328.43,324.57,313.95,312.32,325.88,297.68,256.6,267.59,298.32,264.84,250.68,256.94,262.94,257.64,224.34,249.68,225.67,232.31,218.91,221.55,197.69,228.29,177.72,199.4,184.33,180.28,178.29,158.22,162.71,142.75,150.1,146.16,134.24,130.57,131.44,109.06,125.63,116.23,126.03,96.76,108.28,113.06,90.2,93.76,75.05,94.64,62.51,84.84,69.56,70.59,67.97,55.5,62.16,52.45,57.31,43.78,52.42,35.69,44.86,26.51,45.9,27.41,34.7,31.08,29.23,27.9,24.24,27.45,17.7,30.8,10.22,25.87,11.35,20.96,12.31,16.31,13.32,9.18,14.67,4.16,17.55,0.73,16.13,0.32,15,0.12,10.29,4.65,6.67,6.48,1.17,8.07,-4.38,8.71,-5.04,8.62,-4.35,9.16,-2.69,4.31,-1.66,-3.7,-0.69,-5.06,5.07,-9.7,5.38,-10.77,0.38,-11.87,-1.43,-10.93,-3.16,-5.46,-11.36,-2.19,-13.63,-3.51,-18.59,-4.14,-18.14,-9.92,-19.54,-10.36,-13.23,-14.31,-12.85,-20.3,-9.19,-27.27,-10.36,-24.78,-14.18,-22.6,-20.39,-28.24,-23.07,-27.9,-20.3,-23.49,-24.01,-16.47,-32.51,-18.44,-35.52,-20.07,-31.76,-30.9,-26.39,-27.97,-20.54,-40.61,-21.77,-37.96,-21.15,-35.5,-22.36,-39.48,-32.47,-39.68,-21.48,-31.85,-28.25,-38.46,-30.67,-32.44,-36.68,-29.62,-39.72,-34.96,-34.19,-24.93,-31.69,-30.6,-28.44,-50.74,-40.14,-51.23,-33.87,-54.47,-32.9,-43.39,-46.14,-44.09,-25.73,-35.76,-42.98,-50.85,-60.42,-24.31,-50.35,-32.13,-51.59,-42.78,-60.53,-47.42,-63.76,-51.33,-56.5,-49.18,-54.31,-66.41,-48.98,-54.05,-29.78,-58.69,-36.19,-60.52,-43.37,-61.49,-55.58,-41.38,-72.95,-33.47,-68.55,-61.23,-58.51,-37.71,-46.96,-41.61,-60.55,-63.35,-69.32,-44.59,-55.18,-53.55,-49.67,-66.77,-46.77,-71.19,-50.12,-64.89,-57.41,-63.26,-57.96,-52.23,-46.85,-47.42,-49.51,-40.46,-46.86,-27.85,-59.89,-36.8,-52.16,-48.58,-46.17,-56.08,-43.81,-56.43,-44.16,-38.31,-42.99,-38.94,-37.57,-55,-30.86,-39.41,-44.38,-31.33,-42.35,-36.42,-46.14,-16.73,-35.44,-22.91,-30.09,-15.13,-31.92,-23.7,-30.71,-32,-19.82,-32.94,-17.73,-40.57,-11.36,-34.26,-20.44,-23.03,-10.61,-24.33,-22.8,-21.24,-20.66,-13.6,-25.8,-12.92,-30.1,-8.46,-21.77,-10.17,-29.37,-20.65,-24.25,-21.38,-14.5,-24.31,-13.62,-22.63,-8.09,-23.83,-4.46,-23.18,-10.38,-17.93</v>
       </c>
     </row>
     <row r="89">
@@ -1375,7 +1375,7 @@
         <v>[R_05_标记]</v>
       </c>
       <c r="C89" t="str">
-        <v>幅值: 60uv 相位: 33.5°</v>
+        <v>a: 21.6ms -44.8uv b: 49.3ms 309.9uv</v>
       </c>
     </row>
     <row r="90">
@@ -1386,7 +1386,7 @@
         <v>[L_05_名字]</v>
       </c>
       <c r="C90" t="str">
-        <v>FERG(5)_Flicker</v>
+        <v>FERG(5)_dRod</v>
       </c>
     </row>
     <row r="91">
@@ -1397,7 +1397,7 @@
         <v>[L_05_放大器]</v>
       </c>
       <c r="C91" t="str">
-        <v>1-300 Hz</v>
+        <v>1-75 Hz</v>
       </c>
     </row>
     <row r="92">
@@ -1408,7 +1408,7 @@
         <v>[L_05_闪光]</v>
       </c>
       <c r="C92" t="str">
-        <v>白色光: 3.00 cd·s/m²</v>
+        <v>b白色光:1.0cd.m-2,5ms</v>
       </c>
     </row>
     <row r="93">
@@ -1419,7 +1419,7 @@
         <v>[L_05_闪光背景]</v>
       </c>
       <c r="C93" t="str">
-        <v>白色背景光</v>
+        <v>b背景光_关:0.0cd.m-2</v>
       </c>
     </row>
     <row r="94">
@@ -1430,7 +1430,7 @@
         <v>[L_05_采样]</v>
       </c>
       <c r="C94" t="str">
-        <v>刺激间隔: 50.0S</v>
+        <v>刺激间隔:10.0S</v>
       </c>
     </row>
     <row r="95">
@@ -1441,7 +1441,7 @@
         <v>[L_05_分析时间]</v>
       </c>
       <c r="C95" t="str">
-        <v>500 ms</v>
+        <v>200ms</v>
       </c>
     </row>
     <row r="96">
@@ -1463,7 +1463,7 @@
         <v>[L_05_详细数据(uv)]</v>
       </c>
       <c r="C97" t="str">
-        <v>55.94,62.41,58.75,65.94,64.19,66.01,69.9,65.85,72.3,67.92,70.4,71.03,66.86,71.59,64.92,67.57,64.69,60.77,63.05,54.78,57.16,51.03,47.73,47.23,38.3,40.09,31.41,29.13,25.92,17.42,18.43,8.3,7.36,1.86,-5.11,-4.95,-15.25,-14.69,-21.74,-26.31,-26.97,-36.16,-34.13,-41.88,-43.49,-44.9,-51.91,-48.71,-56.28,-54.81,-56.91,-60.99,-57.14,-63.76,-59.56,-62.28,-63.15,-59.32,-64.43,-58.25,-61.5,-59.31,-56.24,-59.48,-52.33,-56,-51.27,-49.59,-50.82,-43.81,-47.67,-41.21,-41.31,-40.57,-34.71,-38.44,-31.12,-33.09,-30.52,-26.55,-29.7,-22.4,-25.94,-21.77,-20.06,-22.11,-15.53,-20.01,-14.52,-15.02,-15.45,-10.09,-14.65,-8.17,-10.48,-8.86,-5,-8.71,-1.63,-5.06,-1.21,1.08,-0.95,6.25,2.47,8.45,9.23,9.45,16.2,12.81,20.46,19.87,22.53,28.2,25.77,34.28,32.49,37.34,41.29,40.13,48.47,45.67,52.07,53.74,53.89,60.93,57.31,64.32,63.34,64.6,69.29,65.1,71.67,67.95,69.95,71.52,67.04,72.17,65.96,68.28,66.35,61.97,64.89,56.8,59.02,53.73,49.87,50.15,41.09,42.9,34.84,31.97,29.55,20.64,21.84,12.02,10.5,5.74,-1.91,-1.41,-11.74,-11.66,-18.13,-23.53,-23.74,-33.3,-31.6,-38.98,-41.48,-42.38,-50.03,-46.94,-54.39,-53.74,-55.31,-60.22,-56.25,-63,-59.44,-61.67,-63.44,-59.26,-64.72,-58.91,-61.76,-60.43,-56.81,-60.58,-53.49,-56.89,-52.88,-50.52,-52.41,-45.15,-48.92,-42.95,-42.36,-42.32,-35.95,-39.79,-32.71,-34.06,-32.18,-27.52,-31,-23.66,-26.75,-23.21,-20.72,-23.3,-16.44,-20.72,-15.73,-15.49,-16.59,-10.77,-15.42,-9.26,-10.96,-10.1,-5.64,-9.73,-2.76,-5.8,-2.69,0.26,-2.38,4.94,1.3,6.65,8.07,7.54,14.64,11.14,18.35,18.34,20.21,26.43,23.67,32.04,30.71,34.85,39.51,37.86,46.37,43.88,49.74,52.22,51.8,59.32,55.83,62.57,62.4,63.08,68.51,64.26,70.85,67.85,69.34,71.82,67.1,72.55,66.87,68.79,67.83,63.05,66.52,58.71,60.7,56.29,51.9,52.89,43.81,45.57,38.2,34.72,33.09,23.84,25.15,15.74,13.62,9.61,1.35,2.12,-8.14,-8.6,-14.45,-20.65,-20.47,-30.3,-28.99,-35.94,-39.33,-39.75,-47.96,-45.07,-52.32,-52.53,-53.58,-59.27,-55.25,-62.05,-59.21,-60.91,-63.56,-59.1,-64.83,-59.5,-61.88,-61.43,-57.31,-61.55,-54.63,-57.68,-54.44,-51.44,-53.92,-46.52,-50.11,-44.71,-43.41,-44.05,-37.24,-41.11,-34.36,-35.04,-33.86,-28.55,-32.28,-25.01,-27.57,-24.68,-21.44,-24.48,-17.43,-21.42,-16.98,-15.98,-17.72,-11.5,-16.14,-10.38,-11.42,-11.31,-6.3,-10.67,-3.9,-6.47,-4.13,-0.55,-3.71,3.63,0.22,4.88,6.96,5.72,13.08,9.56,16.27,16.87,17.96,24.66,21.66,29.77,28.97,32.36,37.69,35.62,44.2,42.09,47.36,50.63,49.67,57.58,54.3,60.69,61.34,61.46,67.56,63.33,69.85,67.62,68.58,71.93,67.04,72.7,67.64,69.13,69.13,63.99,67.94,60.5,62.19,58.7,53.82,55.47,46.46,48.08,41.47,37.39,36.52,27.03,28.37,19.46,16.7,13.45,4.65,5.62,-4.47,-5.52,-10.71,-17.67,-17.16,-27.15,-26.31,-32.77,-37.05,-37.02,-45.71,-43.1,-50.07,-51.18,-51.71,-58.12,-54.15,-60.9,-58.84,-60.01,-63.52,-58.85,-64.77,-59.99,-61.88,-62.32,-57.76,-62.37,-55.73,-58.38,-55.94,-52.32,-55.34,-47.89,-51.23,-46.48,-44.45,-45.74,-38.59,-42.4,-36.06,-36.03,-35.55,-29.65,-33.55,-26.43,-28.4,-26.19,-22.22,-25.64,-18.5,-22.11,-18.27,-16.5,-18.83,-12.29,-16.82,-11.52,-11.87,-12.49,-6.98,-11.53,-5.04,-7.08,-5.52,-1.33,-4.95,2.32,-0.77,3.16,5.9,4,11.53,8.08,14.21,15.46,15.77,22.89,19.73,27.5,27.27,29.9,35.85,33.43,41.97,40.3,44.93,48.97,47.53,55.73,52.74,58.69</v>
+        <v>18.16,8.78,22.18,6.62,25.78,5.03,28.78,4.15,31.02,4.08,32.4,4.85,32.86,6.46,32.42,8.83,31.14,11.86,29.12,15.37,26.53,19.17,23.53,23.05,20.35,26.78,17.19,30.13,14.26,32.91,11.75,34.93,9.81,36.06,8.55,36.23,8.04,35.4,8.3,33.62,9.28,30.96,10.89,27.54,13,23.58,15.43,19.26,18,14.79,20.56,10.46,22.8,6.44,24.57,3.05,25.79,0.3,26.27,-1.73,25.86,-2.62,24.42,-2.97,22.14,-2.39,19.8,-0.43,15.81,1.56,12.09,4.41,7.83,5.94,3.64,9.39,-0.07,10.88,-5.14,13,-8.33,13.11,-10.51,14.07,-13.81,13.46,-17,14.33,-15.83,11.9,-11.68,3.14,-18.36,0.65,-14.02,-6.05,-7.59,-9.45,-14.35,-12.45,-4.57,-9.78,-10.43,-20.02,-10.93,-23.61,-4.85,-30.4,-2.89,-20.01,-0.32,-24.37,3.22,-32.24,-0.69,-23.79,-8.58,-22.47,7.97,-1.44,12.85,-2.85,7.14,11.93,-6.52,4.42,1.82,39.35,2.37,22.53,20.99,35.67,32.07,41.19,28.37,66.36,54.43,77.57,55.38,84.15,77.74,94.39,67.51,99.89,104.17,114.57,107.9,142.19,124.79,145.44,169.13,165.63,146.66,175.49,170.49,149.77,179.72,165.16,229.26,177.37,241.93,189.77,255.9,241.35,240.78,239.82,240.45,263.28,299.16,245.59,297.18,311.85,304.06,283.6,324.61,324.95,332.55,331.86,327.95,358.7,329.78,303.98,290.19,371.67,356.13,341.33,293.6,352.07,310.62,374.02,321.96,346.84,372.38,379.86,324.13,369.9,333.08,367.51,308.86,331.83,357.62,348.09,335.61,310.87,350.64,315.32,316.96,299.09,303.29,325.7,298.17,317.84,323.48,275.29,326.89,279.18,258.01,275.97,254.88,275.82,248.11,269.69,220.04,251.38,245.78,231.92,219.82,219.36,197.16,202.77,178.18,182.63,153.35,195.84,162.66,172.39,155.86,169.84,139.76,164.79,124.95,127.42,106.28,122.78,116.23,104.42,90.21,107.57,90.81,81.7,84.07,83.24,79.61,72.34,79.91,60.59,83.66,54.57,77.32,46.94,66.73,44.76,62.81,34.57,58.18,36.79,55.42,30.72,51.36,34.46,44.29,34.12,36.46,32.05,30.43,36.08,26.77,35.7,21.13,38.63,17.63,39.54,16.15,41.09,12.02,39.1,11.37,38.72,11.75,36.24,9.83,32.45,12.63,29.63,14,24.06,14.56,21.86,19.56,15.75,20.22,10.01,24.03,7.23,24.3,2.3,23.79,1.79,24.8,-0.55,24.39,-3.3,24.35,-6.66,22.06,-6.46,17.73,-2.9,9.95,-5.66,8.85,-1.66,4.69,-2.12,-1.46,4.99,-9.83,2.6,-14.6,6.6,-18.33,4.66,-18.99,8.79,-25.64,0.76,-27.84,5.69,-21.53,0.63,-21.1,3.15,-18.18,-8.32,-24.38,-7.69,-22.11,-12.64,-15.38,-9.33,-16.77,-17.87,-7.27,-16.16,-11.96,-28.13,-1.69,-25.03,-9.54,-22.16,-6.97,-22,-11.42,-29.01,1.26,-23.31,-4.4,-34.41,-4,-19.6,-8.81,-30.73,-15.05,-11.46,-22.01,-8.82,-13.42,-15.84,-38.84,-8.94,-27.92,-12.42,-25.4,-0.67,-34.69,-11.51,-27.24,-6.32,-42.51,-6.18,-31.83,-20.74,-29.07,-23.14,-40.55,-16.53,-36.01,-23.82,-36.31,-26.42,-24.38,-43.82,-31.75,-30.01,-18,-53.32,-33.56,-44.48,-35.99,-44.42,-22.63,-61.82,-26.63,-52.8,-23.73,-62.19,-25.54,-54.14,-39.74,-37.07,-27.39,-60.44,-45.56,-38.38,-33.1,-36.99,-45.46,-37.01,-68.45,-46.17,-56.83,-23.27,-55,-27.6,-67.24,-26.36,-62.36,-18.58,-52.05,-25.25,-62.38,-41.91,-48.43,-18.16,-36.44,-32.32,-28.62,-36.59,-39.07,-31.36,-43.69,-39.42,-21.05,-28.69,-21.61,-34.83,-14.49,-38.75,-21.91,-33.79,-6.1,-41.99,-14.06,-37.72,-17.53,-24.52,-7.81,-30.21,-12.63,-32.38,-19.08,-10.78,-15.88,-19.17,-14.06,-3.91,-14.91,-3.55,-18.78,-3.97,-23.02,4.47,-22.12,-6.65,-24.11,7.57,-30.62,1.33,-30.35,8.84,-26.12,3.84,-14.12,-8.99,-16.18,-4.59,-16.57,-13.71,-6.61,-11.88</v>
       </c>
     </row>
     <row r="98">
@@ -1474,12 +1474,3774 @@
         <v>[L_05_标记]</v>
       </c>
       <c r="C98" t="str">
-        <v>幅值: 56.4uv 相位: 33.5°</v>
+        <v>a: 21.6ms -48.4uv b: 49.3ms 364.7uv</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B99" t="str">
+        <v>[R_06_名字]</v>
+      </c>
+      <c r="C99" t="str">
+        <v>FERG(6)_dRod</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B100" t="str">
+        <v>[R_06_放大器]</v>
+      </c>
+      <c r="C100" t="str">
+        <v>1-75 Hz</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B101" t="str">
+        <v>[R_06_闪光]</v>
+      </c>
+      <c r="C101" t="str">
+        <v>b白色光:3.0cd.m-2,4ms</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B102" t="str">
+        <v>[R_06_闪光背景]</v>
+      </c>
+      <c r="C102" t="str">
+        <v>b背景光_关:0.0cd.m-2</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B103" t="str">
+        <v>[R_06_采样]</v>
+      </c>
+      <c r="C103" t="str">
+        <v>刺激间隔:2.0S</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B104" t="str">
+        <v>[R_06_分析时间]</v>
+      </c>
+      <c r="C104" t="str">
+        <v>200ms</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B105" t="str">
+        <v>[R_06_数据长度]</v>
+      </c>
+      <c r="C105" t="str">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B106" t="str">
+        <v>[R_06_详细数据(uv)]</v>
+      </c>
+      <c r="C106" t="str">
+        <v>0.57,-2.51,6.83,-4.82,5.02,1.05,-2.12,7.18,-4.54,5.22,1.2,-2.06,7.18,-4.6,5.07,1.01,-2.34,6.84,-5.01,4.59,0.49,-2.93,6.21,-5.69,3.85,-0.28,-3.77,5.36,-6.58,2.92,-1.2,-4.74,4.39,-7.56,1.92,-2.18,-5.74,3.39,-8.54,0.94,-3.14,-6.68,2.5,-9.44,0.05,-4,-7.58,1.72,-10.23,-0.84,-4.84,-8.26,0.79,-11.33,-1.89,-5.81,-9.54,-0.15,-12.21,-2.79,-7.06,-11.08,-1.4,-14.1,-5.73,-10.28,-14.89,-5.3,-17.94,-9.29,-13.95,-18.67,-11.93,-22.91,-14.51,-23.29,-26.84,-19.1,-30.76,-21.85,-24.46,-38.12,-22.43,-43.53,-30.46,-39.22,-46.63,-42.89,-43.41,-45.56,-53.1,-57.46,-38.23,-60.33,-43.22,-44.61,-64.77,-42.8,-67.03,-39.63,-60.33,-66.55,-38.08,-46.97,-53.18,-57.89,-47.92,-36.36,-50.91,-38.44,-43.84,-27.66,-20,-25.62,-17.58,0.74,-7.05,5.5,3.9,14.14,18.57,29.37,36.31,39.19,62.55,47.85,60.7,82.6,73.59,77.29,87.86,98.36,111.65,100.61,133.11,121.65,150.42,135.08,161.86,161.2,192.59,181.73,188.75,207.06,220.45,219.95,193.62,217.55,219.66,226.41,243.48,275.26,283.42,250.71,253.54,318.49,305.38,323.63,279.64,339.31,335.07,326.12,337.18,287.44,330.01,370.3,340.94,329.23,331.08,343.81,368.13,343.74,318.55,332.48,368.18,364.42,364.24,362.12,358.95,385,334.06,333.75,349.43,351.07,321.68,337.82,307.91,281.93,267.37,278.82,298,254.16,294.04,249.57,271.56,281.05,238.45,258.63,259.23,209.12,206.4,220.6,225,203.23,201.12,171.07,156.97,163.43,177.28,144.12,157.07,151.59,157.52,121.5,138.53,127.3,107.01,104.05,82.73,95.17,81.77,87.54,76.71,68.72,75.76,63.64,53.77,61.7,39.62,55.55,42.52,39.47,45.82,31.34,36.73,29.27,20.13,28.46,19.49,25.99,16.56,15.18,20.08,8.38,14.53,11.42,4.9,15.6,2.25,10.44,7.87,1.82,10.82,-1.95,8.54,3.54,-0.33,9.14,-3.85,5.13,1.45,-2.02,7.31,-3.97,3.86,0.25,-3.24,6.7,-6.09,3.42,-1.19,-5.62,3.9,-8.13,2.04,-1.82,-6.38,3.47,-8.59,1.37,-2.01,-6.75,0.5,-9.51,-0.38,-5.38,-8.41,2.05,-14.22,-2.88,-4.71,-13.17,-1.96,-16.24,-5.09,-9.81,-14.45,-7.34,-18.25,-11.22,-9.33,-18.75,-9.39,-22.28,-14.5,-13.53,-21.82,-12.09,-26.52,-15.64,-15.23,-21.85,-9.32,-29.53,-21.51,-22.55,-23.3,-15.28,-23.89,-24.37,-19.76,-31.73,-21.58,-32.84,-26.44,-23.02,-30.47,-14.62,-33.56,-17.78,-32.68,-29.14,-18.36,-37.2,-28.57,-28.98,-26.46,-18.14,-43.1,-27.63,-24.64,-41.95,-32.53,-39.87,-35.56,-23.59,-42.68,-33.62,-50.38,-31.4,-25.84,-45.62,-23.7,-32.52,-44.85,-37.47,-45.41,-23.29,-36.22,-48.24,-41.69,-44.22,-23.81,-54.74,-29.61,-38.23,-50.12,-31.12,-38.67,-41.08,-35.43,-37.78,-53.44,-51.68,-48.99,-60.19,-57.98,-35.26,-71.21,-46.95,-41.52,-52.1,-52.12,-72.82,-45.89,-51.15,-68.09,-34.16,-76.76,-49.74,-70.51,-69.84,-48.45,-68.93,-64.55,-66.38,-67.35,-38.45,-57.57,-49.56,-63.17,-63.85,-62.2,-78.54,-67.74,-52.64,-57.56,-53.22,-49.97,-40.59,-52.14,-66.35,-55.96,-56.43,-48.53,-61.88,-56.38,-50.26,-69.13,-60.2,-64.15,-63.99,-46.45,-74.94,-66.41,-58.82,-68.54,-59.33,-69.29,-35.94,-61.96,-63.09,-44.39,-65.58,-39.57,-43.84,-47.64,-50.76,-47.49,-36.43,-34,-42.65,-40.51,-43.7,-36.4,-30.08,-41.23,-38.24,-48.73,-27.26,-31.39,-48.76,-19.13,-51.8,-27.26,-28.15,-46.79,-23.24,-41.77,-23.44,-30.9,-32.65,-29.88,-30.7,-22,-36.62,-38.46,-28.54,-39.5,-26.13,-27.7,-32.57,-16.78,-38.33,-20.87,-22.62,-26.92,-14.65,-27.85,-19.54,-17.92,-24.42,-19.48,-27.49,-21.6,-23.25,-23.33,-18.95,-27.14,-17.52,-17.59,-26.02,-8.86,-20.3,-12.32,-14.51,-24.88,-12.63,-20.31,-18.04</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B107" t="str">
+        <v>[R_06_标记]</v>
+      </c>
+      <c r="C107" t="str">
+        <v>a: 24.7ms -64.8uv b: 51.6ms 344.1uv</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B108" t="str">
+        <v>[L_06_名字]</v>
+      </c>
+      <c r="C108" t="str">
+        <v>FERG(6)_dRod</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B109" t="str">
+        <v>[L_06_放大器]</v>
+      </c>
+      <c r="C109" t="str">
+        <v>1-75 Hz</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B110" t="str">
+        <v>[L_06_闪光]</v>
+      </c>
+      <c r="C110" t="str">
+        <v>b白色光:3.0cd.m-2,4ms</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B111" t="str">
+        <v>[L_06_闪光背景]</v>
+      </c>
+      <c r="C111" t="str">
+        <v>b背景光_关:0.0cd.m-2</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B112" t="str">
+        <v>[L_06_采样]</v>
+      </c>
+      <c r="C112" t="str">
+        <v>刺激间隔:2.0S</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B113" t="str">
+        <v>[L_06_分析时间]</v>
+      </c>
+      <c r="C113" t="str">
+        <v>200ms</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B114" t="str">
+        <v>[L_06_数据长度]</v>
+      </c>
+      <c r="C114" t="str">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B115" t="str">
+        <v>[L_06_详细数据(uv)]</v>
+      </c>
+      <c r="C115" t="str">
+        <v>-2.85,-8.52,4.78,-12.21,5.07,-7.71,-1.93,1.19,-9.63,6.68,-10.87,3.94,-4.4,-4.44,3.99,-10.86,6.7,-9.56,1.2,-1.84,-7.69,5.13,-12.17,4.79,-8.47,-2.89,-0.3,-11.34,4.54,-13.37,1.2,-7.63,-7.8,0.16,-14.88,2.4,-14.19,-3.53,-6.96,-12.85,-0.34,-17.75,-0.89,-14.37,-8.74,-6.39,-17.34,-1.59,-19.64,-4.85,-13.9,-13.91,-6.17,-21.02,-3.55,-20.26,-9.51,-12.89,-18.64,-6.69,-24.15,-7.57,-21.37,-15.4,-13.27,-23.73,-8.81,-27.28,-12.22,-23.12,-21.16,-14.2,-31.84,-11.99,-32.66,-21.36,-28.67,-31.06,-20.43,-37.36,-24.35,-41.47,-30.76,-36.27,-43.59,-33.29,-43.82,-30.13,-41.74,-44.82,-36.85,-51.68,-45.14,-50.32,-45.39,-58.57,-53.41,-47.25,-71.64,-52.09,-57.45,-47.95,-49.83,-65.16,-43.69,-49.7,-30.83,-42.88,-40.39,-44.88,-49.98,-25.19,-43.26,-31.77,-18.37,-19.95,-15.63,-9.26,-8.27,-8.47,-2.37,15.83,12.09,37.36,22.38,46.94,47.27,37.96,61.51,37.56,72.54,69.34,90.03,99.86,78.37,106.27,112.03,111.85,120.2,120.75,141.95,133.86,164.08,175.47,166.53,167.83,199.51,210.95,175.4,225.32,209.62,198.66,252.54,240.41,252.72,217.45,236.01,227.15,243.25,265.34,279,300.65,276.21,314.53,330.42,323.69,336.12,276.34,344.35,286.59,330.65,316.04,290.81,372.4,304.43,368.98,300.74,317.05,351.65,358.8,376.47,330.66,314.3,299.06,316.14,351.54,299.37,333.92,328.48,317.43,320.83,302.11,307.47,257.74,276.33,279.29,295.19,235.26,221.6,260.92,248.54,222.11,226.55,210.77,238.6,212.75,203.38,171,174.06,193.57,164.22,191.05,134.34,150.51,139.74,127.63,132.42,113.08,139.69,94.23,105.92,107.27,102.1,84.25,66.79,82.53,70.19,75.34,60.85,48.07,53.11,34.65,50.59,40.27,39.97,41.57,25.67,38.56,16.43,26.24,14.78,18.23,22.38,5.82,19.45,1.68,8.54,4.46,-1.02,8.56,-11.13,7.19,-7.83,-0.3,-1.03,-10.86,1.3,-15.41,-1,-11.74,-9.23,-2.93,-17.64,-0.31,-17.42,-6.03,-11.24,-14.71,-4.46,-20.91,-4.49,-18.94,-11.45,-10.14,-19.22,-4.72,-23.25,-7.91,-17.42,-14.74,-9.38,-23.28,-5.86,-24.5,-12.11,-18.1,-20.99,-10.55,-27.12,-8.79,-24.75,-17.49,-16.47,-28.19,-11.97,-29.65,-16.24,-25.13,-25.89,-17.42,-33.74,-15,-33.98,-20.77,-25.93,-32.73,-24.15,-37.06,-22,-40.54,-29.79,-30.59,-42.72,-28.07,-43.31,-26.31,-43.09,-39.87,-27.78,-44.08,-25.6,-50.03,-30.8,-42.45,-38.91,-36.66,-46.14,-36.04,-47.5,-37.21,-41.79,-55.31,-33.98,-49.69,-36.4,-52.3,-48.29,-46.87,-54.4,-42.96,-48.48,-48.91,-45.36,-44.8,-43.66,-59.18,-32.49,-59.32,-49.42,-47.97,-49.82,-51.86,-68.79,-53.01,-47,-43.17,-37.73,-58.75,-39.06,-61.84,-45.09,-54.31,-62.79,-60.57,-61.18,-47.14,-59.51,-59.31,-59.27,-65.46,-51.21,-60.61,-60.98,-53.44,-73.45,-45.23,-71.76,-41.59,-77.54,-73.65,-80.15,-64.78,-66.51,-74.89,-73.14,-84.77,-57.89,-58.44,-77.11,-56.89,-71.09,-63.82,-71.11,-78.33,-83.16,-74.67,-52.4,-72.37,-63.93,-64.07,-82.41,-72.09,-84.22,-68.28,-86.4,-75.58,-65.72,-85.48,-79.31,-92.98,-76.43,-97.69,-91.61,-61.39,-102.5,-55.29,-90.71,-85.45,-78.6,-77.92,-65.34,-81.3,-76.25,-93.46,-60.05,-61.96,-77.81,-80.55,-97.28,-73.26,-90.62,-60.38,-79.18,-87.2,-72.23,-91.49,-57.77,-76.11,-59.92,-50.07,-70.91,-52.04,-73.46,-67.85,-72.49,-55.78,-42.07,-63.31,-42.99,-55.06,-56.18,-63.45,-60.96,-49.78,-75.05,-53.48,-60.34,-50.21,-49.08,-61.87,-45.61,-65.37,-42.97,-40.65,-65.57,-45.08,-60.58,-41.11,-46.82,-56.08,-36.41,-58.37,-45.76,-56.69,-40.49,-41.1,-43.73,-37.64,-59.56,-40.57,-48.37,-46.53,-40.28,-45.21,-38.61,-49.55,-38.27,-44.27,-40.59,-36.05,-51.36,-33.87,-53.33,-33.27,-47.44,-44.1,-31.49,-53.02,-31.8,-46.32</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B116" t="str">
+        <v>[L_06_标记]</v>
+      </c>
+      <c r="C116" t="str">
+        <v>a: 24.8ms -62.5uv b: 51.5ms 311.2uv</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B117" t="str">
+        <v>[R_07_名字]</v>
+      </c>
+      <c r="C117" t="str">
+        <v>FERG(7)_dMax</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B118" t="str">
+        <v>[R_07_放大器]</v>
+      </c>
+      <c r="C118" t="str">
+        <v>1-75 Hz</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B119" t="str">
+        <v>[R_07_闪光]</v>
+      </c>
+      <c r="C119" t="str">
+        <v>b白色光:3.0cd.m-2,5ms</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B120" t="str">
+        <v>[R_07_闪光背景]</v>
+      </c>
+      <c r="C120" t="str">
+        <v>b背景光_关:0.0cd.m-2</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B121" t="str">
+        <v>[R_07_采样]</v>
+      </c>
+      <c r="C121" t="str">
+        <v>刺激间隔:15.0S</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B122" t="str">
+        <v>[R_07_分析时间]</v>
+      </c>
+      <c r="C122" t="str">
+        <v>200ms</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B123" t="str">
+        <v>[R_07_数据长度]</v>
+      </c>
+      <c r="C123" t="str">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B124" t="str">
+        <v>[R_07_详细数据(uv)]</v>
+      </c>
+      <c r="C124" t="str">
+        <v>7.5,-6.42,2.36,6.5,-7.08,3.12,5.24,-7.71,3.7,3.77,-8.29,4.1,2.11,-8.77,4.33,0.34,-9.14,4.4,-1.49,-9.37,4.34,-3.34,-9.44,4.16,-5.13,-9.32,3.88,-6.83,-9,3.52,-8.36,-8.49,3.09,-9.71,-7.78,2.61,-10.84,-6.92,2.09,-11.74,-5.94,1.45,-12.44,-4.94,0.83,-13.2,-3.91,-0.09,-13.53,-3.24,-1.18,-14.42,-2.78,-3.32,-15.02,-2.74,-6.17,-17.14,-2.75,-9.12,-18.95,-4.37,-14.18,-22.76,-11.32,-17.71,-23.99,-15.31,-27.74,-31.16,-27.73,-32.76,-44.18,-28.55,-40.28,-42.46,-44.32,-56.82,-57.84,-65.12,-78.65,-66.44,-77.1,-75.33,-77.26,-72.6,-80.67,-95.29,-87.6,-87.92,-103.62,-82.06,-96.85,-81.71,-84.7,-111.08,-103.7,-88.07,-110.01,-73.02,-80.7,-75.83,-35.72,-33.37,-61.72,-19.66,-27.41,-35.59,-0.14,13.15,25.94,45.01,59.51,37.03,89.1,101.34,135.08,160.92,138.66,153.3,194.28,173.92,201.41,225.62,271.2,273.84,308.82,321.83,362.4,311.28,343.62,336.06,447.72,422.19,435.4,431.67,487.44,516.88,545.14,498.23,567.6,561.52,600.66,535.26,545.01,513.62,596.42,610.5,597.95,631.59,665.86,578.21,685.75,710.52,722.63,619.29,659.78,687.17,697.01,720.92,733.4,618.96,653.66,655.36,613.73,614.46,617.94,590.87,670.14,646.19,652.79,603.11,549.1,656.57,592.33,528.27,599.3,588.33,533.02,487.26,494.26,542.76,534.93,454.23,460.54,474.23,416.6,462.18,418.53,416.49,384.55,397.37,420.14,421,380.41,338.01,367.71,285.11,326.39,324.51,312.55,284.99,312.34,259.81,261.6,247.53,261.38,231.45,265.27,231.71,209.57,206.51,223.17,191.27,185.54,150.88,191.74,163.05,163.35,194.31,160.27,178.81,183.95,133.18,151.34,149.94,157.73,153.37,167.57,156.98,125.01,106.76,116.61,101.53,141.48,114.9,80.04,96.42,85.47,102.81,89.22,92.12,87.45,77.13,98.37,68.9,72.04,65.78,81.05,86,51.36,57.21,54.14,59.09,47.56,49.66,36.34,54.08,49.5,29.64,46.52,47.13,20.07,29.23,42.56,23.81,32.61,29.65,9.19,29.93,20.56,7.66,23.99,8.67,3.26,13.98,4.1,-1.64,9.73,3.7,-8.21,5.64,-0.63,-9.94,0.94,-3.02,-8.01,-0.37,-12.25,-13.01,-7.69,-12.25,-19.89,-5.58,-24.62,-23.3,-9.07,-28.18,-22.78,-16.26,-30,-22.57,-13.19,-30.43,-18.08,-23.48,-26.5,-25.69,-18.6,-29.71,-19.72,-23.44,-38.41,-27.76,-27.42,-32.73,-28.85,-37.14,-44.63,-31.08,-28.89,-44.08,-33.14,-39.12,-37.4,-33.26,-39.27,-51.65,-29.38,-31.44,-52.31,-40.94,-48.82,-41.54,-39.65,-38.73,-34.66,-41.51,-48.33,-44.61,-24.54,-50.46,-32.44,-33.36,-50.69,-41.26,-50.54,-60.16,-53.63,-33.43,-58.06,-39.37,-33.64,-72.1,-58.9,-58.73,-56.44,-55.19,-57.15,-52.22,-46.56,-56.82,-65.94,-39.03,-45.44,-60.66,-64.4,-45.5,-64.66,-52.94,-61.43,-68.49,-46.44,-68.23,-71.57,-66.01,-54.34,-72.09,-77.34,-69.19,-67.3,-68.67,-86.78,-57.53,-79.52,-63.15,-71.64,-67.98,-82.43,-83.61,-58.54,-76.24,-88.8,-83.95,-75.18,-54.72,-68.1,-95.75,-81.29,-55.86,-91.3,-50.51,-74.85,-91.14,-58.6,-55.49,-84.69,-70.26,-54.76,-94.78,-70.01,-76.75,-72.12,-72.78,-62.84,-86.03,-74.97,-71.89,-64.91,-60.63,-63.46,-73.55,-66.59,-80.93,-62.28,-42.11,-64.55,-43.14,-58.79,-53.22,-61.31,-55.42,-65.56,-65.58,-55.83,-70.45,-49.75,-36,-44.51,-38.55,-45.3,-52.46,-50.83,-32.86,-62.11,-42.3,-46.05,-49.37,-37.67,-43.67,-55.63,-28.56,-52.41,-40.73,-31.79,-44.2,-44.71,-30.67,-32.23,-35.04,-31.94,-41.99,-32.91,-23.36,-47.5,-33.43,-26.17,-38.25,-47.55,-30.26,-48.33,-30.18,-30.35,-45.11,-33.42,-18.02,-30,-25.72,-17.33,-36.18,-18.4,-22.58,-30.01,-25.89,-20.17,-33.94,-17.32,-16.55,-29.08,-11.25,-22.54,-30.68,-16.47,-15.29,-26.61,-15.57,-16.82,-20.52,-10.22,-19.62</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B125" t="str">
+        <v>[R_07_标记]</v>
+      </c>
+      <c r="C125" t="str">
+        <v>a: 25.9ms -122.8uv b: 55.3ms 458.6uv</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B126" t="str">
+        <v>[L_07_名字]</v>
+      </c>
+      <c r="C126" t="str">
+        <v>FERG(7)_dMax</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B127" t="str">
+        <v>[L_07_放大器]</v>
+      </c>
+      <c r="C127" t="str">
+        <v>1-75 Hz</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B128" t="str">
+        <v>[L_07_闪光]</v>
+      </c>
+      <c r="C128" t="str">
+        <v>b白色光:3.0cd.m-2,5ms</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B129" t="str">
+        <v>[L_07_闪光背景]</v>
+      </c>
+      <c r="C129" t="str">
+        <v>b背景光_关:0.0cd.m-2</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B130" t="str">
+        <v>[L_07_采样]</v>
+      </c>
+      <c r="C130" t="str">
+        <v>刺激间隔:15.0S</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B131" t="str">
+        <v>[L_07_分析时间]</v>
+      </c>
+      <c r="C131" t="str">
+        <v>200ms</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B132" t="str">
+        <v>[L_07_数据长度]</v>
+      </c>
+      <c r="C132" t="str">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B133" t="str">
+        <v>[L_07_详细数据(uv)]</v>
+      </c>
+      <c r="C133" t="str">
+        <v>-7.84,-0.81,-13.28,-4.14,-3.57,-13.55,-1.33,-7.39,-11.99,-0.25,-11.21,-9.12,-1.29,-13.99,-5.85,-4.22,-15.02,-3.23,-8.32,-14.14,-2.15,-12.55,-11.73,-3.08,-15.81,-8.65,-5.91,-17.31,-5.96,-9.97,-16.83,-4.65,-14.35,-14.68,-5.21,-17.86,-11.68,-7.74,-19.65,-8.8,-12.22,-20.08,-7.33,-16.96,-18.23,-8.63,-20.63,-15.86,-10.96,-23.07,-15.33,-17.1,-27.35,-13.7,-21.99,-26.79,-14.39,-31.37,-29.05,-24.92,-35.44,-28.5,-33.05,-45.26,-32.97,-44.67,-41.32,-34.44,-48.73,-53.72,-51.22,-67.8,-53.4,-58.61,-72.31,-50.63,-67.92,-86.86,-70.77,-67.86,-85.09,-74.07,-72.63,-70.85,-74.37,-79.57,-67.92,-78.14,-98.83,-63.6,-81.75,-79.33,-66.61,-80.67,-35.35,-37.01,-68.22,-45.97,-21.1,-42.48,23.71,-27.61,-10.58,17.35,17.5,53.59,50.12,26.11,92.07,93.43,118.74,93.74,123.46,151.02,152.56,160.94,213.45,209.85,184.47,223.81,237.42,295.57,319.24,283.88,282.55,347.1,351.56,394.14,346.89,354.71,407.15,493.25,425.62,453.83,490.06,515.25,483.44,474.3,567.54,503.22,566.56,497.45,567.68,516.21,628.19,624.92,615.31,617.28,554.26,637.77,688.76,649.18,587.6,609.13,683.22,609.61,693.42,704.01,649.44,627.8,719.23,623.72,610.28,692.69,572.45,667.52,655.76,641.56,577.16,684.04,627.23,630.97,549.97,586.61,636.39,593.09,528.15,555.68,583.48,504.79,578.89,450.4,512.59,474.01,501.32,460.07,487,486.77,380.94,475.57,435.38,384.62,392.95,337.77,386.65,342.43,319.84,339.57,332.4,312.37,281.66,309.97,324.44,302.53,263.48,306.69,245.62,283.81,242.99,236.45,255.33,273.54,219.59,246.89,180.08,235.27,187.11,216.06,188.34,183.32,162.37,181.67,187.93,155.68,180.66,142.41,118.19,170.03,139.23,123.94,152.92,118.33,99.44,127.74,119.72,98.2,112.9,108.22,96.45,67.71,66.64,106.16,80.42,59.86,85.02,64.27,67.12,75.84,65.22,61.16,42.99,42.11,50.74,28.3,30.72,40.58,34.39,28.69,38.03,20.31,33,16.27,20.25,24.75,9.33,19.82,17.32,1.15,11.35,9.57,1.75,16.4,-0.74,-2.84,2.89,-7.92,-0.59,3.79,-8.98,-7.42,-2.27,-17.81,-4.69,-11.55,-20.61,-7.3,-21.62,-18.44,-8.96,-24.05,-15.08,-12.09,-30.91,-20.46,-19.41,-36.1,-17.46,-29.91,-36.36,-24.81,-37.39,-29.47,-26.71,-36.24,-31.19,-28.68,-43.95,-27.76,-30.81,-37.79,-26.57,-43.29,-39.95,-39.64,-52.86,-42.98,-41.33,-55.97,-30.9,-37.71,-46.07,-34.35,-54.97,-49.3,-29.48,-56.77,-33.1,-36.02,-52.01,-31.31,-54.79,-51.18,-37.61,-48.08,-50.02,-32.48,-64.08,-49.11,-36.3,-63.85,-50.43,-60.4,-62.55,-50.2,-55.13,-50.26,-40.9,-63.69,-49.95,-59.74,-55.37,-40.41,-66.73,-68.19,-52.31,-59.15,-73.35,-45.84,-58.69,-74.76,-44.77,-81.38,-71.14,-65.72,-76.87,-73.24,-86.34,-80.74,-76.89,-91.22,-82.4,-67.4,-66.04,-57.56,-53.75,-73.37,-75.9,-69.62,-93.47,-71.28,-66.89,-86.95,-60.67,-71.92,-68.82,-64.23,-78.9,-75.5,-70.96,-84.49,-66.87,-89.84,-65.76,-73.84,-87.12,-87.39,-67.11,-79.59,-70.04,-91.89,-77.92,-65.78,-97.78,-71.56,-57.14,-74.36,-85.09,-89.69,-83.23,-56.32,-81.4,-68.31,-72.52,-72.99,-60.24,-81.94,-83.39,-75.91,-57.55,-86.47,-54.67,-83.79,-75.18,-48.12,-72.27,-75.28,-50.99,-85.31,-51.35,-54.65,-83.6,-60.52,-64.48,-69.99,-64.03,-58.24,-68.99,-43.93,-48.68,-67.52,-57,-55.54,-41.59,-43.81,-54.8,-43.12,-43.52,-56.95,-34.58,-54.29,-42.27,-35.08,-63.28,-42.82,-54.45,-51.62,-33.88,-42.65,-53.78,-43.09,-42.65,-46.04,-37.27,-39.27,-37.18,-29.57,-55.29,-40.38,-45.84,-47.03,-32.03,-45.78,-44.5,-26.11,-49.79,-40.88,-25.19,-44.3,-35.52,-26.24,-32.93,-33.03,-33.06,-40.16,-20.32,-36.18,-27.31,-20.7,-30.04,-22.62,-29.07,-30.91,-17.87,-33.62,-30.86,-17.6,-29.58,-26.58,-17.32,-32.56</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B134" t="str">
+        <v>[L_07_标记]</v>
+      </c>
+      <c r="C134" t="str">
+        <v>a: 26.0ms -126.1uv b: 55.2ms 470.3uv</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B135" t="str">
+        <v>[R_08_名字]</v>
+      </c>
+      <c r="C135" t="str">
+        <v>FERG(8)_dOps</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B136" t="str">
+        <v>[R_08_放大器]</v>
+      </c>
+      <c r="C136" t="str">
+        <v>1-75 Hz</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B137" t="str">
+        <v>[R_08_闪光]</v>
+      </c>
+      <c r="C137" t="str">
+        <v>b白色光:3.0cd.m-2,5ms</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B138" t="str">
+        <v>[R_08_闪光背景]</v>
+      </c>
+      <c r="C138" t="str">
+        <v>b背景光_关:0.0cd.m-2</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B139" t="str">
+        <v>[R_08_采样]</v>
+      </c>
+      <c r="C139" t="str">
+        <v>刺激间隔:15.0S</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B140" t="str">
+        <v>[R_08_分析时间]</v>
+      </c>
+      <c r="C140" t="str">
+        <v>200ms</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B141" t="str">
+        <v>[R_08_数据长度]</v>
+      </c>
+      <c r="C141" t="str">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B142" t="str">
+        <v>[R_08_详细数据(uv)]</v>
+      </c>
+      <c r="C142" t="str">
+        <v>-13.93,-11.05,-0.96,-8.63,-16.42,-6.41,-3.46,-15.36,-14.38,-3.49,-9.7,-18.64,-9.35,-4.39,-15.86,-16.31,-4.68,-8.79,-18.47,-10.1,-3.35,-14.4,-16.5,-4.44,-7.26,-17.91,-11.76,-3.95,-14.43,-18.99,-7.98,-9.15,-21.15,-16.81,-6.97,-16.89,-21.9,-11.16,-8.83,-19.69,-15.39,-3.62,-9.8,-14.84,-3.57,1.83,-8.77,-5.82,6,2.09,-8.66,0.22,4.32,-8.45,-10.61,-1.62,-9.39,-20.91,-16.61,-11.32,-23.82,-28.31,-14.6,-19.91,-29.54,-17.45,-6.24,-12.07,-10.92,5.07,9.12,2.52,14.18,26.61,19.84,14.27,25.4,19.86,3.32,6.88,8.39,-7.85,-22.16,-22.86,-22.62,-41.56,-52.26,-33.3,-47.85,-61.29,-38.47,-31.84,-38.56,-26.72,-3.48,0.84,3.79,27.15,29.29,29.15,30.17,51.91,32.77,24.87,31.09,23.48,-1.97,-16.19,-19.57,-28.86,-61.47,-63.54,-49.94,-75.77,-73.84,-61.72,-55.04,-63.47,-41.2,-24.11,-17.7,-9.56,17.9,30.1,32,39.64,49.99,52.3,32.94,38.56,33.87,9.7,2.17,2.64,-16.46,-37.91,-38.13,-37.6,-51.02,-67.51,-53.8,-47.15,-66.04,-44.49,-24.16,-29.22,-19.21,2.62,13.27,7.03,19.23,29.78,33.48,29.47,37.02,32.24,15.16,12.33,16.6,-2.16,-15.43,-12.63,-14.14,-34.23,-32.21,-27.56,-27.56,-41.85,-22.83,-18.33,-27.91,-22.15,-5.52,-5.72,-11.4,2.16,10.37,2.01,-1.99,14.31,8.87,-5.79,-1,5.49,-8.27,-14.5,-5.49,-10.4,-22.9,-18.12,-12.62,-22.71,-25.86,-13.89,-13.66,-24.9,-19.71,-8.67,-15.35,-20.35,-8.13,-5.34,-16.31,-13.62,-2.66,-9.85,-16.93,-7.05,-4.31,-16.6,-15.58,-5.02,-11.05,-20.33,-11.26,-6.09,-17.52,-18.09,-6.25,-9.95,-19.68,-11.28,-4.09,-14.23,-16.21,-4.12,-5.94,-16.38,-9.51,-1.03,-10.58,-14.6,-2.86,-3.11,-14.39,-9.3,0.15,-8.5,-14.28,-3.12,-1.65,-13.24,-9.89,0.5,-6.88,-14.2,-3.8,-0.6,-12.24,-10.78,0.26,-5.72,-14.48,-5.16,-0.36,-11.87,-12.36,-0.99,-5.45,-15.44,-7.42,-1.13,-12.18,-14.57,-3.11,-5.89,-16.81,-10.23,-2.54,-12.8,-16.97,-5.62,-6.6,-18.13,-13.09,-4.14,-13.31,-19.11,-8.11,-7.21,-19.02,-15.62,-5.58,-13.39,-20.63,-10.22,-7.42,-19.19,-17.45,-6.53,-12.77,-21.25,-11.65,-7.01,-18.42,-18.39,-6.85,-11.35,-20.87,-12.31,-5.94,-16.74,-18.42,-6.56,-9.23,-19.59,-12.3,-4.39,-14.35,-17.74,-5.89,-6.71,-17.68,-11.89,-2.68,-11.6,-16.67,-5.16,-4.16,-15.54,-11.45,-1.21,-8.93,-15.6,-4.77,-2.03,-13.58,-11.33,-0.36,-6.73,-14.89,-5.03,-0.66,-12.13,-11.81,-0.41,-5.29,-14.76,-6.14,-0.24,-11.38,-13,-1.44,-4.73,-15.27,-8.08,-0.8,-11.31,-14.81,-3.35,-4.93,-16.26,-10.65,-2.12,-11.71,-16.96,-5.85,-5.64,-17.43,-13.5,-3.88,-12.26,-19.09,-8.53,-6.49,-18.41,-16.18,-5.66,-12.58,-20.77,-10.98,-7.1,-18.81,-18.3,-7.09,-12.34,-21.66,-12.84,-7.19,-18.38,-19.58,-7.93,-11.37,-21.57,-13.92,-6.64,-17.02,-19.91,-8.1,-9.65,-20.5,-14.23,-5.5,-14.86,-19.38,-7.74,-7.39,-18.66,-13.95,-4.04,-12.17,-18.27,-7.12,-4.94,-16.4,-13.42,-2.61,-9.38,-16.95,-6.62,-2.71,-14.13,-13.01,-1.61,-6.91,-15.81,-6.6,-1.09,-12.25,-13.05,-1.38,-5.11,-15.17,-7.33,-0.38,-11.02,-13.74,-2.1,-4.18,-15.15,-8.88,-0.67,-10.52,-15.1,-3.76,-4.12,-15.73,-11.15,-1.85,-10.66,-16.94,-6.15,-4.75,-16.67,-13.85,-3.65,-11.15,-18.94,-8.9,-5.73,-17.62,-16.59,-5.68,-11.63,-20.68,-11.6,-6.68,-18.2,-18.92,-7.52,-11.74,-21.79,-13.84,-7.25,-18.08,-20.51,-8.86,-11.21,-21.99,-15.34,-7.22,-17.08,-21.15,-9.53,-9.95,-21.2,-16.01,-6.56,-15.22,-20.84,-9.55,-8.05,-19.51,-15.94,-5.43,-12.72,-19.78,-9.13,-5.79,-17.23,-15.42,-4.14,-9.92,-18.31,-8.61,-3.57,-14.76,-14.79,-3.08,-7.27</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B143" t="str">
+        <v>[R_08_标记]</v>
+      </c>
+      <c r="C143" t="str">
+        <v>84uv</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B144" t="str">
+        <v>[L_08_名字]</v>
+      </c>
+      <c r="C144" t="str">
+        <v>FERG(8)_dOps</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B145" t="str">
+        <v>[L_08_放大器]</v>
+      </c>
+      <c r="C145" t="str">
+        <v>1-75 Hz</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B146" t="str">
+        <v>[L_08_闪光]</v>
+      </c>
+      <c r="C146" t="str">
+        <v>b白色光:3.0cd.m-2,5ms</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B147" t="str">
+        <v>[L_08_闪光背景]</v>
+      </c>
+      <c r="C147" t="str">
+        <v>b背景光_关:0.0cd.m-2</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B148" t="str">
+        <v>[L_08_采样]</v>
+      </c>
+      <c r="C148" t="str">
+        <v>刺激间隔:15.0S</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B149" t="str">
+        <v>[L_08_分析时间]</v>
+      </c>
+      <c r="C149" t="str">
+        <v>200ms</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B150" t="str">
+        <v>[L_08_数据长度]</v>
+      </c>
+      <c r="C150" t="str">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B151" t="str">
+        <v>[L_08_详细数据(uv)]</v>
+      </c>
+      <c r="C151" t="str">
+        <v>-17.57,-28.24,-18.06,-14.54,-27.51,-23,-13.59,-24.97,-27.55,-15.21,-21.46,-30.51,-19.12,-18.42,-31.11,-24.31,-16.97,-29.35,-29.24,-17.55,-25.84,-32.51,-19.98,-21.56,-32.87,-23.5,-17.8,-30.51,-26.97,-16.17,-25.84,-29.88,-17.32,-21.76,-31.61,-21.2,-18.61,-31.83,-26.85,-18.13,-30.28,-32.16,-20.95,-27.11,-36.19,-23.36,-23.01,-34.5,-24.85,-16.62,-27.67,-24.5,-11.43,-18.07,-22.18,-8.14,-10.35,-20.79,-9.61,-5.83,-19.53,-15.8,-7.36,-21.13,-26.97,-16.56,-25.56,-38.37,-30.84,-28.07,-43.32,-33.54,-25.42,-35.02,-32.01,-17.13,-19.52,-22.2,-3.76,1.84,-3.79,4.89,12.05,1.47,5.54,13.65,2.98,-6.82,0.39,-12.27,-31.37,-29.4,-30.55,-53.01,-60.13,-50.55,-62.04,-65.08,-50.32,-48.74,-56.24,-32.22,-23.81,-26.08,-7.65,9.57,8.39,15.74,38.96,22.52,16.26,36.41,18.25,2.72,1.22,-8.44,-32.91,-44.59,-43.13,-73.3,-85.39,-63.15,-81.61,-91.26,-74.41,-71.58,-69.55,-49.46,-29.95,-25.99,-14.69,8.87,16.77,16.9,31.45,50.86,37.19,40.34,27.97,8.78,0.85,-0.61,-20.48,-38.33,-38.33,-53.75,-65.33,-61.36,-57.4,-84.12,-68.24,-49.32,-56.08,-48.73,-22.37,-17.63,-17.31,2.02,11.23,10.67,15.91,36.42,13.26,17.64,27.67,12.09,-3.23,-0.74,-9.47,-29.09,-30.13,-31.43,-44.78,-45.12,-34.6,-46.64,-45.89,-33.27,-34.96,-38.86,-23.7,-15.46,-23.18,-14.55,-1.07,-10.47,-10.92,4.23,0.11,-14.87,-1.42,-3.77,-19.23,-17.61,-12.33,-27.7,-30.52,-21.25,-30.09,-40.24,-26.95,-28.77,-37.82,-28.56,-22.55,-33.73,-29.04,-16.55,-24.87,-28,-13.36,-16.84,-26.4,-16.09,-12.59,-25.25,-20.35,-11.89,-23.59,-25.56,-13.72,-20.97,-29.41,-17.58,-17.7,-29.52,-21.92,-14.4,-26.44,-24.83,-12.58,-20.95,-26.25,-13,-14.91,-25.45,-15.39,-10.37,-22.8,-18.81,-8.32,-18.68,-21.92,-9.09,-14.14,-23.49,-12.27,-10.2,-22.81,-16.57,-8.06,-19.89,-20.59,-8.28,-15.71,-23.12,-10.85,-11.55,-23.45,-15.07,-8.85,-21.55,-19.7,-8.56,-18.13,-23.4,-10.85,-14.34,-25.16,-15.13,-11.52,-24.56,-20.22,-10.69,-21.95,-24.72,-12.28,-18.34,-27.42,-16,-15.03,-27.66,-20.87,-13.23,-25.55,-25.55,-13.68,-21.9,-28.74,-16.35,-17.97,-29.55,-20.53,-15.06,-27.81,-24.98,-14.12,-24.09,-28.33,-15.47,-19.54,-29.52,-18.64,-15.53,-28.13,-22.57,-13.22,-24.48,-25.94,-13.2,-19.57,-27.54,-15.32,-14.77,-26.7,-18.73,-11.36,-23.49,-22.18,-10.22,-18.7,-24.39,-11.47,-13.6,-24.45,-14.53,-9.58,-22.15,-18.24,-7.68,-18.01,-21.27,-8.34,-13.17,-22.54,-11.21,-8.99,-21.53,-15.28,-6.69,-18.48,-19.24,-6.93,-14.29,-21.83,-9.63,-10.29,-22.27,-13.98,-7.75,-20.47,-18.7,-7.55,-17.1,-22.44,-9.88,-13.33,-24.17,-14.16,-10.5,-23.53,-19.23,-9.66,-20.88,-23.7,-11.25,-17.25,-26.37,-14.97,-13.94,-26.58,-19.84,-12.16,-24.45,-24.51,-12.61,-20.78,-27.67,-15.28,-16.83,-28.43,-19.45,-13.91,-26.65,-23.86,-12.97,-22.89,-27.17,-14.3,-18.31,-28.32,-17.46,-14.29,-26.88,-21.37,-11.97,-23.2,-24.71,-11.95,-18.27,-26.27,-14.07,-13.46,-25.41,-17.48,-10.07,-22.18,-20.93,-8.94,-17.38,-23.12,-10.22,-12.3,-23.17,-13.29,-8.3,-20.87,-17.02,-6.44,-16.74,-20.06,-7.13,-11.92,-21.34,-10.04,-7.78,-20.33,-14.14,-5.52,-17.29,-18.12,-5.81,-13.13,-20.72,-8.54,-9.15,-21.16,-12.92,-6.65,-19.37,-17.66,-6.49,-16.01,-21.41,-8.85,-12.26,-23.13,-13.16,-9.45,-22.48,-18.23,-8.62,-19.82,-22.69,-10.23,-16.18,-25.34,-13.96,-12.87,-25.52,-18.82,-11.08,-23.36,-23.46,-11.54,-19.66,-26.58,-14.21,-15.69,-27.31,-18.35,-12.76,-25.48,-22.74,-11.81,-21.68,-26.01,-13.13,-17.08,-27.11,-16.27,-13.04,-25.63,-20.17,-10.72,-21.92,-23.47,-10.7,-16.97,-25.01,-12.82,-12.16,-24.12,-16.24,-8.77,-20.87,-19.67,-7.66,-16.07,-21.86</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B152" t="str">
+        <v>[L_08_标记]</v>
+      </c>
+      <c r="C152" t="str">
+        <v>84.4uv</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B153" t="str">
+        <v>[R_09_名字]</v>
+      </c>
+      <c r="C153" t="str">
+        <v>FERG(9)_dMax</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B154" t="str">
+        <v>[R_09_放大器]</v>
+      </c>
+      <c r="C154" t="str">
+        <v>1-75 Hz</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B155" t="str">
+        <v>[R_09_闪光]</v>
+      </c>
+      <c r="C155" t="str">
+        <v>b白色光:20.0cd.m-2,5ms</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B156" t="str">
+        <v>[R_09_闪光背景]</v>
+      </c>
+      <c r="C156" t="str">
+        <v>b背景光_关:0.0cd.m-2</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B157" t="str">
+        <v>[R_09_采样]</v>
+      </c>
+      <c r="C157" t="str">
+        <v>刺激间隔:15.0S</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B158" t="str">
+        <v>[R_09_分析时间]</v>
+      </c>
+      <c r="C158" t="str">
+        <v>200ms</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B159" t="str">
+        <v>[R_09_数据长度]</v>
+      </c>
+      <c r="C159" t="str">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B160" t="str">
+        <v>[R_09_详细数据(uv)]</v>
+      </c>
+      <c r="C160" t="str">
+        <v>-19.81,-29.9,-29.21,-19.1,-16.61,-26.05,-31.84,-24.45,-16.29,-21,-30.78,-29.34,-19.06,-17.01,-26.54,-31.65,-23.7,-15.76,-20.88,-30.31,-28.17,-17.78,-16.19,-25.86,-30.32,-22.02,-14.34,-19.88,-29.12,-26.22,-16.22,-15.01,-25.25,-29.63,-20.37,-14.01,-20.33,-29.24,-25.8,-16.14,-16.74,-27.81,-31.31,-23.15,-18.23,-24.53,-37.03,-33.14,-21.51,-23.92,-37.61,-43.29,-37.05,-33.79,-37.62,-54.19,-52.47,-45.74,-42.48,-60.82,-61.69,-61.31,-53.12,-71.03,-85.01,-84.65,-80.05,-68.77,-94.4,-82.15,-89.52,-87.48,-90.04,-110.89,-84.61,-83.99,-102.58,-95.78,-80.57,-107.49,-79.4,-84.6,-87.82,-90.89,-97.67,-82.06,-82.65,-69.19,-67.37,-46.51,-57.11,-38.24,-24.66,-29.81,-30.17,-5.05,16.03,40.13,59.63,74.2,72.63,74.62,95.37,131.77,134.06,128.64,129.8,181.19,196.16,210.14,259.04,218.28,278.24,314.19,316.83,283.53,318.42,401.67,409.66,352.32,410.13,407.01,477.45,400.07,510.47,516.56,496.74,486.92,538.42,528.31,538.13,575.21,564.47,640.65,550.22,668.96,673.16,564.32,688.99,672.79,629,729.45,597.65,636.73,599.83,700.32,759.98,697.06,757.52,605.15,623.63,713.12,748.31,697.78,594.62,680.49,661.83,621.17,701.62,621.18,594.2,592.09,600.47,640.73,571.31,622.11,644.9,602.43,604.04,566.86,517.35,534.38,558.05,504.61,471.29,477.32,479.29,481.1,511.3,432.51,425.03,422.25,425.08,400.48,354.91,395.36,365.99,380.09,325.53,388.92,317.58,321.37,345.7,285.89,306.39,305.22,269.91,296.41,258.5,253.75,259.72,268.19,226.08,220.27,239.27,192.08,241.81,193.11,205.16,214.16,213.24,202.06,145.71,188.05,177.38,175.18,160.38,143.75,170.23,152.02,129.24,138.82,137.56,116.56,99.68,97.12,97.07,132.57,103.91,111.93,93.4,79.2,80.53,78.48,72.26,64.89,68.36,86.28,74.62,43.39,62.28,61.5,53.94,49.51,45.17,41.12,45.11,37.18,23.59,19.6,32.5,28.44,2.61,10.59,16.1,11.42,10.3,-1.5,3.63,8.56,3.78,-8.5,-14.91,1.62,-7.83,-18.37,-19.38,-11.49,-8.39,-18.66,-25.47,-20.36,-16.77,-22.2,-31.67,-27.07,-23.6,-23.44,-29.57,-40.05,-33.23,-21.35,-25.69,-34.86,-36.24,-26.55,-32.18,-30.09,-40.58,-32.27,-33.37,-32.64,-49.02,-47.52,-40.96,-27.55,-45.73,-43.72,-36.81,-30.09,-36.46,-39.97,-46.67,-42.79,-32.17,-44.84,-45.68,-38.83,-30.55,-34.11,-53.74,-43.86,-41.43,-31.4,-50.79,-56.29,-47.01,-33.27,-52.34,-59.44,-66.55,-53.42,-41.1,-59.87,-66.58,-64.68,-38.72,-42.78,-68.75,-66.05,-64.65,-43.75,-70.86,-79.32,-67.63,-57.36,-59.19,-67.74,-73.65,-55.25,-47.25,-70.78,-75.79,-79.12,-78.05,-78.79,-97.2,-86.29,-55.88,-63.75,-95.55,-76.79,-61.73,-58.75,-72.31,-91.26,-100.98,-75.79,-84.59,-100.62,-95.06,-97.14,-95.17,-81.62,-96.17,-80.99,-88.29,-79,-73.97,-93.87,-96.4,-77.37,-84.54,-113.41,-81.78,-101.18,-92.77,-100.73,-89.89,-89.67,-85.17,-77.28,-102.37,-107.43,-90.38,-96.96,-91.2,-75.61,-93.51,-92.19,-95.32,-109.48,-88.14,-67.62,-97.93,-94.02,-79.97,-85.5,-79.9,-95.19,-96.24,-80.54,-77.99,-81.85,-89.82,-93.16,-75.94,-63.74,-71.02,-72.06,-92.23,-70.82,-63.12,-99.08,-63.47,-74.83,-83.83,-88.26,-88.98,-82.43,-60.8,-61.54,-87.84,-79.7,-72.24,-60.52,-73.5,-75.93,-62.41,-46,-60.11,-60.17,-83.45,-69.71,-51.01,-78.31,-80.19,-68.14,-67.55,-48.54,-60.31,-67.78,-54.97,-46.67,-72.32,-78.28,-57.62,-51.19,-56.26,-59.73,-58.34,-49.87,-59.57,-61.83,-56.89,-60.95,-41.38,-50.73,-49.94,-53.23,-35.85,-40.85,-50.77,-45.22,-50.83,-43.64,-49.73,-55.15,-37.46,-28.74,-27.95,-39.41,-37.32,-39.45,-32.07,-27.62,-44.18,-37.9,-21.4,-31.98,-39.09,-41.57,-31.93,-14.5,-32.32,-32.05,-30.47,-14.77,-20.95,-33.04,-25.47,-21.56,-14.64,-24.73,-27.72,-18.39,-15.19,-10.42,-27.9,-21.95</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B161" t="str">
+        <v>[R_09_标记]</v>
+      </c>
+      <c r="C161" t="str">
+        <v>a: 28.7ms -144.9uv b: 62.3ms 668.0uv</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B162" t="str">
+        <v>[L_09_名字]</v>
+      </c>
+      <c r="C162" t="str">
+        <v>FERG(9)_dMax</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B163" t="str">
+        <v>[L_09_放大器]</v>
+      </c>
+      <c r="C163" t="str">
+        <v>1-75 Hz</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B164" t="str">
+        <v>[L_09_闪光]</v>
+      </c>
+      <c r="C164" t="str">
+        <v>b白色光:20.0cd.m-2,5ms</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B165" t="str">
+        <v>[L_09_闪光背景]</v>
+      </c>
+      <c r="C165" t="str">
+        <v>b背景光_关:0.0cd.m-2</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B166" t="str">
+        <v>[L_09_采样]</v>
+      </c>
+      <c r="C166" t="str">
+        <v>刺激间隔:15.0S</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B167" t="str">
+        <v>[L_09_分析时间]</v>
+      </c>
+      <c r="C167" t="str">
+        <v>200ms</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B168" t="str">
+        <v>[L_09_数据长度]</v>
+      </c>
+      <c r="C168" t="str">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B169" t="str">
+        <v>[L_09_详细数据(uv)]</v>
+      </c>
+      <c r="C169" t="str">
+        <v>9.18,-3.35,3.86,16.31,9.41,-4.04,1.42,14.79,9.83,-4.28,-0.65,13.39,10.46,-4.02,-2.28,12.17,11.34,-3.23,-3.42,11.17,12.45,-1.93,-4.04,10.4,13.76,-0.17,-4.17,9.83,15.17,1.97,-3.87,9.39,16.61,4.33,-3.22,9,17.95,6.86,-2.43,8.41,18.82,9.12,-1.59,7.52,19.27,10.39,-1.39,5.6,18.97,11.66,-1.34,2.84,16.07,10.36,-3.61,-0.2,13.29,9.81,-5.3,-6,3.48,3.14,-13.5,-15.47,-1.09,-6.57,-25.11,-27.63,-14.25,-7.71,-29.06,-32.21,-34.27,-27.98,-39.05,-46.7,-53.69,-35.88,-43.49,-67.03,-57.57,-41.29,-63.25,-67.74,-56.53,-64.84,-89.73,-76.45,-83.18,-86.56,-88.89,-91.81,-81.71,-58.09,-88.08,-96.94,-83.87,-57.7,-64.26,-47.89,-28.5,-4.65,-31.65,-48.44,-20.77,14.21,42.75,24.11,50.96,94.4,62.2,110.64,123.88,107.6,128.61,154.81,144.85,201.87,206.07,244.34,229.15,302.42,296.34,323.24,325.93,327.75,337.64,372.36,380.27,428.77,404.98,481.2,481.25,446.3,465.66,527.56,458.35,546.19,611.38,570.48,567.21,610.5,692.91,660.43,613.5,686.66,687.33,627.46,722.46,707.16,620.3,649.59,759.31,769.04,690,673.1,738.45,705.97,670.55,716.12,658.8,656.36,712.72,673.65,783.77,671.28,748.48,775.96,666,730.48,652.92,630.68,665.46,576.68,683.01,583.54,639.31,644.65,561.51,555.94,564.72,527.43,504.36,606.44,572.01,543.09,519.98,535.45,475.86,461.67,456.07,466.53,469.45,425.66,381.22,432.55,442.94,388.9,393.54,367.14,401.59,321.51,326.15,350.89,339.4,298.25,292.19,271.75,292.51,264.56,270.75,286.64,285.91,247.38,222.07,247.59,243.17,208.55,183.14,216.67,221.06,221.49,197.13,203.74,203.73,164.43,141.74,196.63,181.3,165.26,139.53,164.61,171.24,129.8,117.99,130.27,157.36,117.06,120.58,129.22,119.23,120.99,86.48,94.68,110.19,112.06,89.53,78.37,85.26,84.02,72.1,54.53,63.05,86.06,52.97,62.6,66.89,54.46,47.97,42.46,41.4,48.84,28.85,32.49,26.44,37.12,28.62,14.16,23.43,28.99,14.89,2.51,11.2,18.76,12.47,-4.03,1.77,11.05,5.24,-8.74,-3.58,5.58,6.76,-8.86,-13.55,3.04,-1.56,-20.83,-19.34,-1.04,-0.22,-18.74,-19.23,-7.37,-10.02,-18.46,-21.47,-7.74,-4.4,-15.79,-29.35,-14.74,-12.22,-25.4,-33.87,-21.45,-14.36,-21.28,-33.95,-14.08,-14.06,-23.09,-25.54,-31.57,-13.86,-25.83,-35.12,-30.72,-23.78,-22.59,-31.29,-27.46,-16.32,-15.49,-29.59,-36.42,-32.45,-28.78,-31.18,-42.81,-36.71,-40.31,-43.64,-32.69,-18.75,-29.12,-39.29,-55.71,-26.79,-37.23,-37.54,-50.66,-45.44,-46.99,-67.19,-46.03,-53.53,-47,-52.6,-68.65,-38.01,-35.65,-44.83,-58.26,-43.74,-34.76,-47.19,-87.43,-77.09,-49.12,-61.84,-61.75,-82.18,-43.57,-72.91,-63.51,-65.08,-51.53,-79.63,-68.58,-61.97,-59.27,-58.75,-89.16,-96.01,-53.49,-80.73,-82.34,-100.04,-65.35,-79.46,-70.41,-96.7,-80.54,-56.58,-88.15,-94.66,-72.63,-64.1,-67.28,-72.77,-68.46,-77.63,-90.53,-76.74,-79.86,-51.35,-86.82,-83.52,-57.98,-65.45,-90.62,-81.51,-63.85,-72.21,-57.44,-79.55,-85.68,-57.28,-65.93,-66.31,-78.32,-59.4,-67.26,-84.58,-67.27,-52.95,-58.4,-66.02,-55.89,-58.71,-49.22,-68.03,-53.84,-44.29,-59.54,-67.01,-68.7,-47.74,-37.68,-79.83,-75.26,-57.83,-54.57,-78,-81.74,-48.38,-52.13,-50.2,-54.69,-51.66,-40.9,-62.72,-68.43,-42.39,-44.68,-44.07,-61.95,-66.54,-34.77,-62.59,-65.16,-42.67,-35.68,-49.5,-58.64,-65.38,-38.54,-42.44,-60.39,-47.55,-46.85,-31.75,-47.23,-43.32,-34.22,-26.8,-53.06,-40.43,-39.53,-37.92,-38.02,-44.51,-31.7,-25.73,-31.63,-41.62,-23.45,-29.61,-39.2,-31.25,-27.62,-16.28,-21.65,-30.51,-19.51,-8.13,-23.39,-31.57,-17.59,-6.4,-17.12,-25.55,-20.97,-5.91,-17.26,-27.16,-20.38,0.63,-6.62</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B170" t="str">
+        <v>[L_09_标记]</v>
+      </c>
+      <c r="C170" t="str">
+        <v>a: 28.9ms -141.6uv b: 62.2ms 679.6uv</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B171" t="str">
+        <v>[R_10_名字]</v>
+      </c>
+      <c r="C171" t="str">
+        <v>FERG(10)_dOps</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B172" t="str">
+        <v>[R_10_放大器]</v>
+      </c>
+      <c r="C172" t="str">
+        <v>1-75 Hz</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B173" t="str">
+        <v>[R_10_闪光]</v>
+      </c>
+      <c r="C173" t="str">
+        <v>b白色光:20.0cd.m-2,5ms</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B174" t="str">
+        <v>[R_10_闪光背景]</v>
+      </c>
+      <c r="C174" t="str">
+        <v>b背景光_关:0.0cd.m-2</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B175" t="str">
+        <v>[R_10_采样]</v>
+      </c>
+      <c r="C175" t="str">
+        <v>刺激间隔:15.0S</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B176" t="str">
+        <v>[R_10_分析时间]</v>
+      </c>
+      <c r="C176" t="str">
+        <v>200ms</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B177" t="str">
+        <v>[R_10_数据长度]</v>
+      </c>
+      <c r="C177" t="str">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B178" t="str">
+        <v>[R_10_详细数据(uv)]</v>
+      </c>
+      <c r="C178" t="str">
+        <v>-22,-32.16,-30.6,-18.73,-7.97,-8.65,-19.88,-30.46,-29.77,-18.16,-6.66,-6.06,-16.54,-27.59,-27.97,-17.12,-5.11,-3.47,-13.51,-25.18,-26.84,-16.6,-4.42,-1.74,-11.05,-23.15,-25.67,-15.83,-3.07,1.13,-7.12,-19.06,-22.33,-13.32,0.32,5.56,-2.4,-14.08,-19.55,-10.93,1.38,6.52,-1.12,-14.62,-21.53,-15.93,-4.3,1.18,-6.72,-19.72,-28.66,-22.5,-9.64,-2.41,-7.51,-19.97,-26.55,-20.93,-6.47,3.46,0.16,-8.88,-16.27,-11.64,0.08,8.45,5.59,-9.71,-22.05,-21.5,-12.73,-6.7,-12.79,-27.93,-42.56,-42.67,-36.08,-26.07,-31.74,-38.49,-50.03,-45.8,-28.58,-12.41,-7.14,-12.31,-16.19,-14.1,0.13,23.02,22.33,13.12,2.39,-6.36,0.19,4.69,-0.87,-17.49,-38.49,-52.03,-46.9,-35.63,-41.71,-58.37,-66.86,-61.27,-58.65,-32.82,-22.4,-18.81,-20.91,-13.22,1.12,29.56,46.93,44.17,26.55,24.55,28.2,38.8,43.58,26.1,-1.86,-21.47,-29.62,-26.87,-28.03,-51.77,-67.33,-83.76,-67.41,-58.86,-39.44,-39.35,-43.01,-38.59,-21.16,4.7,26.23,30.96,32.26,37.98,32.29,43.02,54.1,49.06,29.16,10.41,-7.46,-7.59,-9.34,-22.68,-46.53,-64.16,-77.73,-64.33,-50,-54,-54.07,-58.21,-52.14,-35.03,-12.69,-1.54,-0.66,-8.84,-1.2,19.19,31.9,32.57,16.01,7.19,0.94,-0.95,2.53,-2.2,-19.85,-38.73,-53.22,-50.42,-33.74,-32.03,-44,-54.64,-53.73,-42.84,-24.02,-15.37,-15.47,-22.93,-22.84,-12.02,6.55,12.27,11.6,-0.87,-12.89,-4.44,3.27,8.37,1.06,-14.52,-25.55,-23.49,-14.12,-7.77,-11.82,-25.51,-35.41,-28.79,-15,-4.88,-5.28,-16.14,-23.36,-18.63,-4.51,6.47,6.04,-6.3,-14.99,-12.96,-2.26,7.5,6.07,-7.36,-18.74,-19.94,-9.68,0.48,-0.43,-12.38,-24.81,-26.08,-15.09,-4.19,-3.23,-13.12,-25.18,-27.05,-16.91,-4.78,-2.47,-12.29,-24.64,-27.76,-18.7,-6.93,-3.81,-13.23,-26.12,-30.72,-22.68,-10.38,-6.35,-14.83,-27.9,-33.08,-25.67,-13.03,-7.64,-14.96,-27.75,-33.7,-26.86,-13.87,-7.27,-13.36,-26.04,-32.76,-26.78,-13.67,-6.07,-11.04,-23.57,-31.1,-26.04,-13,-4.38,-8.28,-20.52,-28.82,-24.71,-11.82,-2.32,-5.1,-17.03,-26.07,-23.01,-10.43,-0.2,-1.92,-13.52,-23.34,-21.44,-9.34,1.48,0.75,-10.52,-21.1,-20.44,-8.97,2.29,2.52,-8.39,-19.69,-20.3,-9.57,2.03,3.19,-7.27,-19.23,-21.11,-11.21,0.66,2.75,-7.19,-19.69,-22.81,-13.78,-1.71,1.33,-7.97,-20.88,-25.17,-17.03,-4.78,-0.76,-9.29,-22.44,-27.8,-20.54,-8.14,-3.1,-10.72,-23.96,-30.28,-23.88,-11.35,-5.24,-11.84,-25,-32.16,-26.61,-13.98,-6.81,-12.28,-25.2,-33.12,-28.41,-15.75,-7.53,-11.79,-24.37,-32.97,-29.12,-16.5,-7.29,-10.33,-22.47,-31.69,-28.76,-16.29,-6.18,-8,-19.66,-29.46,-27.51,-15.34,-4.46,-5.1,-16.24,-26.63,-25.73,-14.01,-2.51,-2.03,-12.64,-23.61,-23.84,-12.73,-0.76,0.76,-9.31,-20.84,-22.27,-11.92,0.37,2.86,-6.66,-18.72,-21.38,-11.91,0.57,3.97,-4.96,-17.49,-21.4,-12.9,-0.34,3.94,-4.34,-17.25,-22.37,-14.89,-2.33,2.82,-4.72,-17.89,-24.14,-17.7,-5.19,0.83,-5.87,-19.14,-26.42,-21.01,-8.58,-1.66,-7.4,-20.6,-28.8,-24.38,-12.05,-4.21,-8.88,-21.86,-30.83,-27.37,-15.16,-6.4,-9.9,-22.49,-32.12,-29.59,-17.55,-7.88,-10.14,-22.21,-32.39,-30.78,-18.96,-8.43,-9.42,-20.88,-31.52,-30.84,-19.33,-8.04,-7.76,-18.53,-29.59,-29.87,-18.8,-6.86,-5.36,-15.41,-26.85,-28.14,-17.64,-5.2,-2.55,-11.87,-23.68,-26.04,-16.26,-3.47,0.24,-8.37,-20.52,-24.01,-15.08,-2.12,2.55,-5.33,-17.8,-22.45,-14.51,-1.52,4.03,-3.12,-15.87,-21.68,-14.82,-1.94,4.42,-1.96,-14.91,-21.86,-16.14,-3.45,3.68,-1.89,-14.92,-22.94,-18.38,-5.96,1.91,-2.76,-15.75</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B179" t="str">
+        <v>[R_10_标记]</v>
+      </c>
+      <c r="C179" t="str">
+        <v>90uv</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B180" t="str">
+        <v>[L_10_名字]</v>
+      </c>
+      <c r="C180" t="str">
+        <v>FERG(10)_dOps</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B181" t="str">
+        <v>[L_10_放大器]</v>
+      </c>
+      <c r="C181" t="str">
+        <v>1-75 Hz</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B182" t="str">
+        <v>[L_10_闪光]</v>
+      </c>
+      <c r="C182" t="str">
+        <v>b白色光:20.0cd.m-2,5ms</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B183" t="str">
+        <v>[L_10_闪光背景]</v>
+      </c>
+      <c r="C183" t="str">
+        <v>b背景光_关:0.0cd.m-2</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B184" t="str">
+        <v>[L_10_采样]</v>
+      </c>
+      <c r="C184" t="str">
+        <v>刺激间隔:15.0S</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B185" t="str">
+        <v>[L_10_分析时间]</v>
+      </c>
+      <c r="C185" t="str">
+        <v>200ms</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B186" t="str">
+        <v>[L_10_数据长度]</v>
+      </c>
+      <c r="C186" t="str">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B187" t="str">
+        <v>[L_10_详细数据(uv)]</v>
+      </c>
+      <c r="C187" t="str">
+        <v>2.86,-7.64,-14.66,-9.82,1.21,5.07,-2.73,-12.38,-12.05,-2.18,5.84,1.64,-9.22,-14.01,-7.07,3.04,3.58,-6.16,-14.61,-11.61,-1.51,4.44,-1.6,-11.81,-12.79,-2.91,7.01,6.28,-3.17,-8.22,-2.04,10.45,13.48,6.95,-3.57,-2.05,7.91,15.17,8.73,-3.02,-8.27,-2.12,6.63,5.44,-6.16,-14.44,-13.97,-3.06,3.75,-3.76,-13.89,-12.68,-0.97,10.11,10.32,2.93,-0.11,8.64,18.38,22.91,12.76,2.75,7.21,14.36,17.88,6.52,-7.96,-16.47,-12.68,-9.02,-13.09,-24.51,-38.22,-30.98,-20.41,-20.11,-24.71,-26.04,-23.68,-8.17,7.15,8.58,9.25,8.2,19.21,30.35,36.66,25.94,14.24,6.97,16.16,12.81,-1.29,-21.86,-33.67,-36.93,-33.88,-36.41,-55.44,-55.63,-60.33,-38.06,-36.8,-37.32,-32.95,-22.76,-0.98,21.68,29.82,19.07,23.63,41.46,54.53,45.68,41.86,20.2,26.72,22.26,15.09,-3.99,-25.64,-46.86,-45.17,-41.65,-45.6,-55.58,-68.08,-52.19,-34.82,-23.5,-24.16,-24.21,-7.4,19.02,38.29,44.65,48.53,39.06,43.05,60.17,62.07,44.31,19.63,21.21,13.95,5.86,-16.06,-34.34,-51.82,-52.82,-52.01,-43.6,-62.18,-64.95,-53.6,-29.72,-23.78,-18.8,-17.61,-6.03,16.66,35.44,34.08,29.43,19.27,24.76,36.81,38.62,18.34,3.48,-4.03,-4.08,-10.17,-25.39,-45.94,-45.74,-47.78,-42.87,-37.84,-47.01,-53.26,-37.65,-20.37,-12.84,-16.03,-17.71,-8.87,6.28,16,12.92,6.26,4.58,12.85,17.7,9.65,-0.96,-14.48,-12.82,-6.79,-6.29,-16.74,-32.16,-33.73,-20.17,-16.96,-19.11,-27.34,-29.85,-17.6,-3.96,-0.31,-7.05,-12.6,-6.61,6.26,13.32,6.3,-5.53,-5.76,2.74,10.04,6.29,-6.23,-14.28,-10.28,-1,0.02,-9.5,-19.72,-18.86,-9.44,-2.43,-6.75,-16.57,-19.99,-11.24,-0.48,0.08,-9.38,-17.06,-13,-2.11,2.76,-4.87,-15.5,-17.82,-8.67,-1.13,-4.62,-16.05,-22.47,-16.84,-6.91,-5.37,-14.84,-24.37,-22.78,-12.69,-6.1,-11.62,-22.5,-25.44,-17.1,-7.48,-8.24,-18.48,-25.66,-21.2,-10.38,-6.44,-14.05,-24.2,-24.5,-14.64,-6.62,-10.17,-20.92,-25.8,-18.79,-8.26,-6.86,-16.03,-24.48,-21.69,-10.74,-4.61,-10.39,-20.75,-22.75,-13.63,-4.08,-5.33,-15.49,-21.93,-16.48,-5.45,-1.88,-9.82,-19.35,-18.66,-8.32,-0.65,-4.74,-15.42,-19.58,-12.01,-1.75,-1.14,-10.81,-18.98,-15.69,-4.91,0.28,-6.44,-16.98,-18.65,-9.54,-0.83,-3.25,-14.06,-20.37,-14.77,-4.31,-1.97,-10.88,-20.58,-19.64,-9.57,-2.96,-8.2,-19.35,-23.3,-15.67,-6.15,-6.7,-17.09,-25.15,-21.53,-11.05,-6.84,-14.41,-24.99,-26.15,-16.86,-8.75,-12,-23.01,-28.74,-22.53,-12.2,-10.51,-19.75,-28.91,-27.07,-16.61,-10.34,-15.96,-26.74,-29.64,-21.17,-11.6,-12.48,-22.7,-29.78,-25.02,-14.06,-10.04,-17.64,-27.46,-27.36,-17.24,-9.1,-12.55,-23.12,-27.7,-20.43,-9.81,-8.4,-17.58,-25.9,-22.93,-11.96,-5.96,-11.89,-22.24,-24.17,-15.03,-5.63,-7.1,-17.4,-23.81,-18.34,-7.43,-4.12,-12.28,-21.88,-21.17,-10.94,-3.52,-7.89,-18.74,-22.94,-15.45,-5.42,-5.13,-15.05,-23.31,-20.08,-9.48,-4.59,-11.6,-22.28,-23.98,-14.96,-6.48,-9.19,-20.16,-26.48,-20.88,-10.55,-8.44,-17.52,-27.21,-26.19,-16.13,-9.65,-15.04,-26.19,-29.99,-22.25,-12.75,-13.4,-23.78,-31.67,-27.84,-17.26,-13.06,-20.62,-31.03,-31.91,-22.41,-14.24,-17.47,-28.33,-33.76,-27.27,-16.78,-15.05,-24.18,-33.08,-30.91,-20.23,-13.89,-19.45,-30.03,-32.62,-23.9,-14.23,-15.1,-25.22,-32.05,-27.04,-15.97,-11.97,-19.57,-29.25,-28.94,-18.69,-10.61,-14.16,-24.71,-29.15,-21.78,-11.22,-9.98,-19.28,-27.56,-24.53,-13.62,-7.83,-13.97,-24.42,-26.33,-17.25,-8.07,-9.82,-20.31,-26.78,-21.36,-10.64,-7.65,-16.08,-25.8,-25.14,-15.04,-7.92,-12.6,-23.63,-27.88,-20.46</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B188" t="str">
+        <v>[L_10_标记]</v>
+      </c>
+      <c r="C188" t="str">
+        <v>89.2uv</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B189" t="str">
+        <v>[R_11_名字]</v>
+      </c>
+      <c r="C189" t="str">
+        <v>FERG(11)_dMax</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B190" t="str">
+        <v>[R_11_放大器]</v>
+      </c>
+      <c r="C190" t="str">
+        <v>1-75 Hz</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B191" t="str">
+        <v>[R_11_闪光]</v>
+      </c>
+      <c r="C191" t="str">
+        <v>b白色光:200.0cd.m-2,5ms</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B192" t="str">
+        <v>[R_11_闪光背景]</v>
+      </c>
+      <c r="C192" t="str">
+        <v>b背景光_关:0.0cd.m-2</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B193" t="str">
+        <v>[R_11_采样]</v>
+      </c>
+      <c r="C193" t="str">
+        <v>刺激间隔:15.0S</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B194" t="str">
+        <v>[R_11_分析时间]</v>
+      </c>
+      <c r="C194" t="str">
+        <v>200ms</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B195" t="str">
+        <v>[R_11_数据长度]</v>
+      </c>
+      <c r="C195" t="str">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B196" t="str">
+        <v>[R_11_详细数据(uv)]</v>
+      </c>
+      <c r="C196" t="str">
+        <v>-13.74,-13.51,-10.76,-6.57,-2.61,-0.46,-0.93,-3.74,-7.58,-10.73,-11.78,-10.16,-6.49,-2.21,0.93,1.71,-0.14,-3.75,-7.52,-9.79,-9.51,-6.79,-2.7,1.1,2.98,2.21,-0.84,-4.93,-8.25,-9.34,-7.93,-4.46,-0.6,2.27,2.51,0.4,-3.79,-7.98,-10.15,-10.61,-8.2,-4.27,-1.28,-0.08,-0.73,-4.44,-9.69,-13.55,-15.02,-13.65,-11.7,-7.42,-5.81,-6.34,-8.35,-14.62,-22.61,-24.88,-23.29,-26.05,-18.72,-17.96,-18.95,-24.1,-29.47,-29.93,-39.8,-44.65,-46.7,-36.86,-42.69,-40.21,-46.42,-48.17,-53.27,-63.04,-68.66,-74.97,-58.98,-52.64,-55.92,-61.01,-54.31,-63.48,-67.95,-76.17,-77.81,-78.64,-69.69,-63.99,-39.08,-59.36,-52.41,-66.07,-51.62,-40.91,-60.68,-18.83,-15.35,2.26,1,24.82,5.26,35.43,11.75,12.87,72.48,40.91,53.43,91.02,127.56,102.51,159.11,116.15,126.63,139.34,174.77,171.44,264.09,280.83,234.69,290.4,281.33,280.29,344.96,305.67,336.55,348.05,412.59,364.92,390.71,438.9,485.97,444.6,482.61,470.01,509.82,486.37,535.16,489.41,568.99,489.94,570.85,616.4,535.25,588.25,591.45,555.58,609.69,588.33,634.36,609.74,627.82,604.79,670.62,605.2,650.49,753.42,699.18,722.28,698.64,727.98,627.57,647.63,617.09,729.94,702.78,685.5,604.97,712.65,630.41,576.58,587.51,610.69,655.66,594.8,598.37,656.43,605.44,630.99,609.63,537.73,623.77,516.39,577.86,545.23,567.95,530.25,553.63,450.65,498.23,480.37,520.92,487.69,437.93,465.8,405.59,390.8,432.23,425.15,424.55,393.18,395.99,431.82,410.47,396.46,335.85,319.84,290.87,322.34,349.92,315.71,306.39,319.86,327.33,242.33,285.01,286.96,260.46,218.69,239.39,226.83,229.25,219.71,218.85,210.32,191.5,182.36,202.02,193.4,158.93,171.1,163.82,144.57,177.84,148.56,147.42,136.43,128.29,122.49,98.83,139.26,114.79,131.04,98.83,73.44,68.57,90.14,60.27,93.25,75.24,79.86,80.98,62.03,62.62,66.32,39.65,45.89,40.02,44.66,43.49,38.72,37.7,36.69,32.79,25.17,15.74,14.42,16.1,21.76,21.36,24.93,22.46,7.17,4.3,1.7,4.71,9.56,6.32,6.46,5.33,6.4,3.22,-3.8,-4.96,-3.63,-6.8,-8.27,-5.1,0.27,-2.16,-7.5,-6.39,-10.13,-20.39,-11.83,-15.77,-14.42,-12.34,-8.43,-5.55,-8.55,-18.2,-24.53,-25.1,-20.09,-25.67,-16.67,-23.45,-10.47,-14.75,-32.63,-30.79,-30.5,-32.39,-30.33,-32.45,-27.17,-18.39,-26.44,-23.14,-44.3,-36.55,-40.07,-33.76,-35.92,-29.81,-29.96,-30.62,-39.08,-51.45,-41.5,-41.01,-60.12,-53.68,-40.81,-44.97,-34.46,-49.51,-43.4,-60.48,-49.62,-67.87,-65.69,-51.08,-48.98,-38.11,-51.71,-52.26,-48.36,-57.76,-68.27,-62.78,-58.9,-44.54,-53.5,-41.6,-54.57,-55.51,-60.41,-69.26,-64.78,-69.52,-44.49,-47.61,-67.16,-42.33,-61.23,-58.89,-68.05,-78.47,-74.86,-69.15,-52.34,-65.5,-73.36,-70.52,-65.16,-79.62,-85.93,-85.04,-63.85,-79.69,-71.08,-60.53,-51.44,-63.2,-75.76,-63.15,-68.64,-65.7,-88.16,-82.27,-74.55,-61.61,-51.72,-80.92,-86.89,-73.97,-91.26,-74.81,-72.54,-50.24,-45.07,-54.04,-80.2,-66.64,-81.12,-62.41,-63.29,-75.29,-55.79,-52.21,-67.06,-61.81,-57.99,-75.43,-58.01,-63,-54.1,-65.3,-52.91,-44.5,-64.94,-51.26,-62.99,-60.76,-79.91,-63.34,-61.71,-74.79,-59.26,-66.75,-72.89,-63.8,-66.15,-51.65,-67.62,-67.91,-50.57,-64.54,-37.18,-41.03,-63.3,-54.35,-58.42,-55.25,-42.86,-55.98,-35.25,-33.47,-36.11,-34.91,-30.05,-45.06,-39.06,-47.62,-32.89,-32.11,-29.63,-26.87,-20.21,-28.43,-34.79,-32.54,-42.96,-44.92,-28.83,-22.1,-27.43,-20.24,-20.79,-20.91,-33.83,-27.09,-24.02,-21.08,-14.81,-14.72,-17.7,-20.65,-20.31,-29.83,-20.32,-31.42,-18.53,-16.99,-17.24,-7.07,-9.16,-15.43,-12.27,-15.66,-27.1,-26.39,-19.69,-7.4,-4.72,-4.95,-8.87</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B197" t="str">
+        <v>[R_11_标记]</v>
+      </c>
+      <c r="C197" t="str">
+        <v>a: 32.5ms -169.3uv b: 69.5ms 794.3uv</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B198" t="str">
+        <v>[L_11_名字]</v>
+      </c>
+      <c r="C198" t="str">
+        <v>FERG(11)_dMax</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B199" t="str">
+        <v>[L_11_放大器]</v>
+      </c>
+      <c r="C199" t="str">
+        <v>1-75 Hz</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B200" t="str">
+        <v>[L_11_闪光]</v>
+      </c>
+      <c r="C200" t="str">
+        <v>b白色光:200.0cd.m-2,5ms</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B201" t="str">
+        <v>[L_11_闪光背景]</v>
+      </c>
+      <c r="C201" t="str">
+        <v>b背景光_关:0.0cd.m-2</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B202" t="str">
+        <v>[L_11_采样]</v>
+      </c>
+      <c r="C202" t="str">
+        <v>刺激间隔:15.0S</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B203" t="str">
+        <v>[L_11_分析时间]</v>
+      </c>
+      <c r="C203" t="str">
+        <v>200ms</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B204" t="str">
+        <v>[L_11_数据长度]</v>
+      </c>
+      <c r="C204" t="str">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B205" t="str">
+        <v>[L_11_详细数据(uv)]</v>
+      </c>
+      <c r="C205" t="str">
+        <v>11.86,15.29,12.86,6.17,-0.63,-3.28,-0.05,7.26,14.45,17.31,14.36,7.46,0.95,-1.21,2.62,10.16,16.93,19.11,15.25,8.3,1.87,0.28,4.03,11.84,17.57,19.2,14.83,6.61,0.22,-1.7,3.57,9.9,16.08,15.35,8.19,1.74,-4.91,-8.69,-1.69,2.12,8.34,3.12,-5.02,-15.16,-19.46,-17.41,-14.98,-12.36,-7.88,-15.34,-16.32,-30.9,-43.09,-42.49,-42.11,-41.73,-29.79,-32.55,-58.79,-53.2,-62.11,-55.19,-67.96,-69.52,-46.18,-50.91,-72.45,-77.87,-77.39,-60.24,-79.73,-46.13,-31.41,-64.77,-46.17,-46.43,-74.18,-57.11,-41.14,-22.04,2.16,5.74,-22.18,1.99,7.61,7.46,27.4,53.62,61.38,55.04,72.76,91.51,105.56,87.08,146.53,144.65,175.1,204.66,214.09,166.61,200.06,237.82,236.92,295.99,343.48,324.01,338.61,347.18,324.6,332.6,357.99,433.2,458.17,460.02,470.54,513.65,468.69,490.37,483.21,501.08,554.63,528.98,515,618.17,575.12,560.68,568.01,675.61,570.51,635.68,615.67,626.22,619.02,667.16,639.68,602.01,692.43,723.12,689.12,690.17,630.36,629.29,737.43,685.4,693.42,589.67,693.79,704.82,589.56,671.43,670.98,614.4,678.48,592.27,619.17,631.46,627.25,534.27,583.43,619.61,597.12,523.78,520.33,540.01,501.01,569.68,488.36,542.25,480.81,447.44,462.31,417.56,479.11,438.43,426.37,452.18,413.24,396.72,419.16,327.16,348.82,353.62,365.45,325.57,313.2,283.64,266.2,275.27,322.81,262.24,281.27,289.57,271.19,249.55,274.86,273.62,264.1,211.4,253.93,234.07,215.75,202.23,179.78,162.79,185.02,174.76,187.3,174.07,190.94,152.34,154.09,159.24,150.18,141.38,172.82,145.57,133.31,117.24,94.24,119.53,122.96,110.11,107.78,129.03,85.48,90.89,72.91,95.31,85.53,92.06,96.23,79.17,72,67.74,41.73,44.58,40.44,58.74,45.35,52.74,45.06,31.86,19.46,31.69,28.77,38.49,39.31,27.45,11.91,6.92,4.09,6.18,10.08,16.85,15.09,6.57,2.49,-3.42,-14.88,-7.83,-1.26,5.29,6.39,-3.8,-12.82,-20.85,-18.6,-13.56,-5.77,-0.53,-4.46,-6.82,-15.45,-25.78,-24.95,-17.88,-8.96,-1.23,-4.37,-18.7,-26.76,-25.2,-24.17,-20.6,-18.12,-14.06,-10.97,-18.14,-21.4,-36.51,-26.7,-16.28,-9.56,-15.04,-11.98,-31.51,-37.72,-38.41,-37.52,-28.9,-21.73,-12.91,-26.19,-39.58,-34.04,-49.05,-45.06,-40.11,-26.59,-36.01,-21.19,-41.98,-57.39,-53.41,-46.94,-36.46,-31.09,-45.98,-41.47,-39.77,-61.25,-47.79,-54.4,-40,-47.42,-38.83,-57.42,-62.96,-75.87,-64.34,-67.92,-67.52,-58.17,-40.43,-62.6,-76.43,-60.48,-60.43,-73.85,-57.65,-41.39,-73.1,-76.31,-82.09,-92.16,-75.33,-82.95,-61.18,-73.44,-77.91,-82.47,-82.24,-93.09,-80.69,-67.11,-54.6,-64.05,-78.71,-82.57,-92.84,-79.68,-85.06,-65.85,-84.26,-60.75,-51.99,-56.98,-88.45,-66.83,-81.98,-76.13,-71.62,-45.45,-60.33,-82.72,-69.56,-97.72,-66.72,-63.78,-52.85,-66.51,-49.39,-54.24,-73.06,-88.51,-91.99,-73.08,-67.07,-50.13,-47.96,-75.95,-75.26,-81.95,-56.05,-60.48,-66.17,-61.47,-67.9,-65.86,-73.91,-82.26,-57.48,-69.54,-50.77,-54.92,-62.34,-74.01,-64.69,-73.93,-55.93,-70.67,-40.95,-68.55,-46.69,-70.82,-63.31,-59.4,-64.96,-63.16,-43.54,-41.67,-54.34,-56.31,-64.38,-80.31,-67.52,-54.58,-53.95,-59.93,-51.55,-70.69,-78.98,-78.03,-57.25,-54.6,-55.26,-43.95,-63.07,-58.63,-50.96,-63.14,-56.82,-32.58,-43.57,-43.19,-39.85,-43.5,-52.27,-56.34,-39.69,-40.88,-32.88,-36.02,-44.55,-37.89,-37.23,-43.05,-33.95,-22.37,-29.13,-29.26,-36.95,-40.74,-45.71,-31.44,-27.65,-11.95,-20.77,-22.61,-25.84,-28.68,-33.36,-26.3,-12.42,-10.34,-8.28,-14.16,-24.78,-25.53,-31.45,-22.06,-17.6,-5.56,-11.88,-8.24,-23.79,-22.75,-25.85,-17.92,-7.4,-8.14,-4.95,-15.21,-23,-25.45,-29.5,-21.66,-16.03,-10.27,-10.81</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B206" t="str">
+        <v>[L_11_标记]</v>
+      </c>
+      <c r="C206" t="str">
+        <v>a: 32.4ms -173.9uv b: 69.5ms 789.1uv</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B207" t="str">
+        <v>[R_12_名字]</v>
+      </c>
+      <c r="C207" t="str">
+        <v>FERG(12)_dOps</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B208" t="str">
+        <v>[R_12_放大器]</v>
+      </c>
+      <c r="C208" t="str">
+        <v>1-75 Hz</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B209" t="str">
+        <v>[R_12_闪光]</v>
+      </c>
+      <c r="C209" t="str">
+        <v>b白色光:200.0cd.m-2,5ms</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B210" t="str">
+        <v>[R_12_闪光背景]</v>
+      </c>
+      <c r="C210" t="str">
+        <v>b背景光_关:0.0cd.m-2</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B211" t="str">
+        <v>[R_12_采样]</v>
+      </c>
+      <c r="C211" t="str">
+        <v>刺激间隔:15.0S</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B212" t="str">
+        <v>[R_12_分析时间]</v>
+      </c>
+      <c r="C212" t="str">
+        <v>200ms</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B213" t="str">
+        <v>[R_12_数据长度]</v>
+      </c>
+      <c r="C213" t="str">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B214" t="str">
+        <v>[R_12_详细数据(uv)]</v>
+      </c>
+      <c r="C214" t="str">
+        <v>-16.63,-14.97,-13.38,-11.69,-10.31,-9.24,-8.67,-8.72,-9.05,-10.09,-11.16,-12.28,-13.68,-14.91,-16.1,-16.91,-17.2,-17.63,-16.91,-16.42,-14.87,-13.94,-12.13,-10.49,-9.71,-9.35,-9.12,-9.5,-10.73,-12.1,-15.1,-17.35,-19.95,-22.26,-23.17,-24.77,-26.45,-25.93,-25.41,-24.29,-21.7,-19.01,-14.99,-12.7,-8.2,-7.34,-3.64,-2.07,-0.09,-0.01,-3.88,-7.03,-11.58,-16.97,-23.31,-29.06,-36.89,-39.08,-42.18,-43.56,-44.97,-45.6,-44.55,-36.59,-30.48,-25.02,-16.88,-9.16,-2.52,4.63,10.24,19.77,18.51,13.61,16.06,11.68,2.84,-0.88,-11.8,-22.53,-30.6,-38.93,-49.05,-51.73,-56.73,-57.03,-54.92,-60.46,-53.14,-44.02,-32.25,-19.03,-8.49,3.73,14.39,29.59,34.63,30.33,32.16,28.2,36.18,27.53,16.37,8.39,-7.43,-18.14,-30.1,-38.63,-57.85,-65.87,-64.16,-63.76,-66.54,-56.37,-63.95,-46.25,-39.52,-28.94,-17.15,-6.33,9.03,23.01,25.83,30.1,25.69,45.27,40.78,29.04,16.96,6.08,2.42,-11.8,-23.25,-32.86,-46.84,-56.32,-68.82,-65.52,-71.93,-60.37,-63.71,-56.2,-56.62,-39.9,-31.14,-20.91,-7.95,-3.5,4.62,20.11,24.18,26.18,24.77,20.74,15.82,11.68,0.17,-7.8,-17.35,-26.21,-35.6,-40.08,-45.33,-49.02,-51.41,-54.54,-57.39,-45.94,-42.49,-37.17,-28.42,-18.97,-12.2,-0.85,5.07,7.94,7.48,16.31,14.74,7.62,6.64,0.46,-4.53,-10.73,-16.33,-21.5,-26.22,-30.79,-36.43,-36.85,-37.15,-32.69,-31.15,-27.65,-23.4,-20.78,-15.97,-11.43,-7.73,-4.83,-2.72,-2.76,-3.21,-4.23,-6.47,-9.97,-11.77,-16.06,-18.42,-21.36,-23.53,-25.07,-25.45,-25.65,-25.57,-24.08,-22.29,-20.94,-19.04,-17.33,-16.56,-15.55,-15.04,-14.95,-15.58,-16.5,-18.24,-19.5,-21.18,-22.81,-24.25,-25.04,-25.88,-26.02,-25.5,-24.68,-23.43,-21.95,-20.31,-18.87,-17.37,-16.23,-15.6,-15.29,-15.68,-16.33,-17.42,-18.69,-20.21,-21.7,-23.08,-24.17,-24.86,-25.18,-24.91,-24.22,-22.99,-21.46,-19.6,-17.69,-15.78,-14.09,-12.7,-11.73,-11.25,-11.29,-11.85,-12.85,-14.19,-15.78,-17.47,-19.08,-20.47,-21.55,-22.19,-22.33,-21.97,-21.12,-19.87,-18.3,-16.57,-14.81,-13.18,-11.82,-10.86,-10.37,-10.41,-10.99,-12.05,-13.53,-15.31,-17.25,-19.19,-20.98,-22.5,-23.61,-24.24,-24.36,-23.96,-23.11,-21.88,-20.4,-18.82,-17.28,-15.92,-14.9,-14.29,-14.18,-14.59,-15.5,-16.85,-18.52,-20.41,-22.35,-24.19,-25.79,-27.03,-27.79,-28.04,-27.75,-26.95,-25.72,-24.17,-22.42,-20.64,-18.97,-17.56,-16.52,-15.94,-15.86,-16.29,-17.18,-18.45,-19.99,-21.65,-23.29,-24.75,-25.89,-26.62,-26.85,-26.55,-25.73,-24.46,-22.81,-20.93,-18.95,-17.03,-15.31,-13.94,-13,-12.57,-12.67,-13.28,-14.33,-15.72,-17.31,-18.97,-20.54,-21.87,-22.85,-23.38,-23.41,-22.93,-21.97,-20.62,-18.98,-17.2,-15.41,-13.79,-12.45,-11.53,-11.1,-11.21,-11.84,-12.96,-14.47,-16.25,-18.17,-20.07,-21.8,-23.22,-24.23,-24.75,-24.75,-24.26,-23.32,-22.03,-20.51,-18.92,-17.41,-16.11,-15.16,-14.66,-14.66,-15.18,-16.19,-17.63,-19.38,-21.31,-23.26,-25.1,-26.67,-27.85,-28.55,-28.73,-28.37,-27.52,-26.26,-24.7,-22.97,-21.24,-19.64,-18.33,-17.41,-16.95,-17.01,-17.56,-18.57,-19.94,-21.54,-23.24,-24.88,-26.31,-27.41,-28.07,-28.22,-27.84,-26.95,-25.61,-23.92,-22.01,-20.03,-18.14,-16.48,-15.18,-14.33,-13.99,-14.18,-14.87,-15.97,-17.39,-18.99,-20.62,-22.13,-23.38,-24.25,-24.65,-24.55,-23.95,-22.87,-21.42,-19.71,-17.88,-16.08,-14.46,-13.16,-12.29,-11.92,-12.09,-12.78,-13.95,-15.48,-17.27,-19.17,-21.02,-22.67,-23.99,-24.89,-25.29,-25.18,-24.57,-23.54,-22.19,-20.64,-19.04,-17.55,-16.31,-15.44,-15.03,-15.13,-15.76,-16.87,-18.38,-20.19,-22.15,-24.12,-25.94,-27.47,-28.59,-29.23,-29.33,-28.91,-28,-26.71,-25.14,-23.43,-21.75,-20.24,-19.03,-18.22</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B215" t="str">
+        <v>[R_12_标记]</v>
+      </c>
+      <c r="C215" t="str">
+        <v>85.5uv</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B216" t="str">
+        <v>[L_12_名字]</v>
+      </c>
+      <c r="C216" t="str">
+        <v>FERG(12)_dOps</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B217" t="str">
+        <v>[L_12_放大器]</v>
+      </c>
+      <c r="C217" t="str">
+        <v>1-75 Hz</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B218" t="str">
+        <v>[L_12_闪光]</v>
+      </c>
+      <c r="C218" t="str">
+        <v>b白色光:200.0cd.m-2,5ms</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B219" t="str">
+        <v>[L_12_闪光背景]</v>
+      </c>
+      <c r="C219" t="str">
+        <v>b背景光_关:0.0cd.m-2</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B220" t="str">
+        <v>[L_12_采样]</v>
+      </c>
+      <c r="C220" t="str">
+        <v>刺激间隔:15.0S</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B221" t="str">
+        <v>[L_12_分析时间]</v>
+      </c>
+      <c r="C221" t="str">
+        <v>200ms</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B222" t="str">
+        <v>[L_12_数据长度]</v>
+      </c>
+      <c r="C222" t="str">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B223" t="str">
+        <v>[L_12_详细数据(uv)]</v>
+      </c>
+      <c r="C223" t="str">
+        <v>-6.32,-2.35,2.09,6.51,9.92,11.83,12.1,10.52,7.38,3.44,-0.41,-3.83,-5.97,-6.46,-5.37,-2.58,1.24,5.36,9.02,11.57,12.56,11.77,9.04,5.35,0.87,-3.57,-7.18,-9.16,-9.38,-7.71,-4.66,-0.37,4.23,8.3,10.77,12.07,11.55,8.93,4.92,-0.17,-4.29,-7.5,-10.74,-11.41,-10.7,-8.71,-5.91,-4.13,-2.15,-1.59,-2.55,-3.59,-7.96,-10.84,-14.48,-17.46,-18.25,-17.97,-15.2,-11.14,-3.63,0.41,8.27,11.07,12.91,16.4,11.32,9.98,2.55,-4.07,-11.72,-18.04,-22.12,-26.3,-24.88,-24.23,-19.83,-22.77,-16.33,-15.12,-11.03,-14.36,-11.67,-8.46,-7.1,-2.96,2.08,6.83,10.64,16.26,32.22,33.22,40.91,33.36,29.64,24.43,14.62,1.28,-11.7,-22.37,-31.44,-48.41,-49.94,-51.04,-49.36,-42.96,-34.47,-18.75,-12.61,-0.35,8.43,15.61,25.25,27.59,27.62,31.7,40.55,42.53,49.63,44.61,30.81,28.27,20.41,8.71,-5.24,-24.7,-35.78,-55.43,-54.88,-61.76,-83.55,-83.34,-65.35,-48.03,-43.9,-23.01,-5.24,9.98,26.14,37.27,45.76,44.28,49.19,44.31,45.36,30.99,19.18,14,4.92,-6.41,-14.85,-24.79,-37.43,-37.61,-55.5,-55.79,-65.56,-71.63,-58.96,-64.46,-50.84,-36.95,-23.88,-8.05,9.3,22.51,40.04,41.62,47.75,41.39,48.04,37.94,23.76,8.95,2.99,-10.19,-18.56,-24.52,-27.79,-29.71,-35.68,-24.52,-34.81,-33.38,-28.33,-22.27,-22.99,-17.76,-16.96,-11.26,-4.64,3.94,13.07,20.99,21.95,31.38,27.11,29.81,24.6,20.22,11.22,1.38,-8.37,-15.72,-22.25,-23.27,-27.33,-23.93,-19.55,-18.6,-11.46,-6.39,-3.62,-2.66,-2.91,-4.61,-6.83,-8.72,-10.23,-12.14,-8.87,-6.82,-5.49,-3.05,0.76,1.87,2.54,1.08,-2.51,-7.12,-12.94,-18.36,-22.79,-26.56,-26.29,-25.67,-23.87,-19.44,-14.56,-9.63,-6.01,-3.51,-3,-4.08,-7.12,-10.93,-14.38,-18.12,-20.15,-20.85,-19.64,-16.87,-13.15,-8.95,-5.22,-2.49,-1.34,-1.83,-4.07,-7.55,-11.48,-15.23,-18.12,-19.44,-19.17,-16.97,-13.38,-8.9,-4.27,-0.26,2.51,3.52,2.64,0.24,-3.4,-7.56,-11.43,-14.26,-15.61,-15.17,-13.03,-9.58,-5.41,-1.28,2.06,4.02,4.25,2.63,-0.47,-4.59,-9,-12.93,-15.68,-16.84,-16.2,-13.94,-10.49,-6.52,-2.77,0.01,1.28,0.77,-1.5,-5.18,-9.67,-14.23,-18.11,-20.68,-21.53,-20.59,-18.07,-14.49,-10.55,-7.02,-4.57,-3.71,-4.63,-7.22,-11.07,-15.53,-19.85,-23.28,-25.26,-25.45,-23.86,-20.79,-16.8,-12.64,-9.05,-6.68,-5.97,-7.04,-9.7,-13.46,-17.64,-21.47,-24.27,-25.49,-24.9,-22.57,-18.9,-14.49,-10.11,-6.49,-4.24,-3.72,-4.98,-7.74,-11.47,-15.44,-18.89,-21.17,-21.81,-20.64,-17.83,-13.83,-9.31,-5.03,-1.71,0.1,0.12,-1.62,-4.77,-8.74,-12.78,-16.15,-18.21,-18.58,-17.18,-14.24,-10.28,-6,-2.17,0.53,1.61,0.87,-1.59,-5.32,-9.7,-13.96,-17.37,-19.35,-19.59,-18.07,-15.13,-11.32,-7.38,-4.06,-2.01,-1.65,-3.1,-6.16,-10.35,-14.97,-19.26,-22.51,-24.21,-24.11,-22.29,-19.14,-15.28,-11.46,-8.42,-6.75,-6.82,-8.65,-11.97,-16.23,-20.71,-24.66,-27.39,-28.46,-27.7,-25.28,-21.64,-17.47,-13.51,-10.49,-8.96,-9.18,-11.12,-14.43,-18.5,-22.6,-25.97,-27.99,-28.28,-26.75,-23.66,-19.51,-15.02,-10.95,-7.99,-6.62,-7.04,-9.14,-12.48,-16.43,-20.22,-23.14,-24.6,-24.29,-22.23,-18.73,-14.36,-9.87,-6,-3.42,-2.53,-3.45,-5.99,-9.66,-13.76,-17.54,-20.29,-21.5,-20.93,-18.68,-15.13,-10.9,-6.76,-3.44,-1.55,-1.41,-3.09,-6.28,-10.44,-14.85,-18.75,-21.47,-22.56,-21.86,-19.55,-16.07,-12.09,-8.39,-5.66,-4.46,-5.05,-7.38,-11.11,-15.61,-20.15,-23.98,-26.47,-27.24,-26.22,-23.64,-20.03,-16.09,-12.59,-10.21,-9.42,-10.43,-13.09,-16.98,-21.46,-25.75,-29.13,-31.04</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B224" t="str">
+        <v>[L_12_标记]</v>
+      </c>
+      <c r="C224" t="str">
+        <v>87.4uv</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B225" t="str">
+        <v>[R_13_名字]</v>
+      </c>
+      <c r="C225" t="str">
+        <v>FERG(13)_dMax</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B226" t="str">
+        <v>[R_13_放大器]</v>
+      </c>
+      <c r="C226" t="str">
+        <v>1-75 Hz</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B227" t="str">
+        <v>[R_13_闪光]</v>
+      </c>
+      <c r="C227" t="str">
+        <v>b白色光:600.0cd.m-2,5ms</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B228" t="str">
+        <v>[R_13_闪光背景]</v>
+      </c>
+      <c r="C228" t="str">
+        <v>b背景光_关:0.0cd.m-2</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B229" t="str">
+        <v>[R_13_采样]</v>
+      </c>
+      <c r="C229" t="str">
+        <v>刺激间隔:15.0S</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B230" t="str">
+        <v>[R_13_分析时间]</v>
+      </c>
+      <c r="C230" t="str">
+        <v>200ms</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B231" t="str">
+        <v>[R_13_数据长度]</v>
+      </c>
+      <c r="C231" t="str">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B232" t="str">
+        <v>[R_13_详细数据(uv)]</v>
+      </c>
+      <c r="C232" t="str">
+        <v>-17.65,-17.35,-17.04,-16.72,-16.37,-16.01,-15.65,-15.27,-14.88,-14.49,-14.1,-13.7,-13.31,-12.92,-12.54,-12.17,-11.81,-11.46,-11.13,-10.81,-10.52,-10.24,-9.99,-9.77,-9.56,-9.4,-9.25,-9.15,-9.06,-9.01,-9.01,-9.04,-9.08,-9.19,-9.36,-9.5,-9.76,-10.04,-10.35,-10.78,-11,-11.57,-12.25,-12.59,-13.59,-14,-14.64,-15.41,-17.39,-17.38,-18.54,-20.92,-22.3,-23.28,-23.92,-27.75,-28.4,-32,-33.81,-37.5,-42.56,-43.24,-45.57,-51.8,-49.77,-51,-66.49,-69.18,-70.73,-73.26,-71.01,-76.3,-91.02,-88.09,-84.2,-87.79,-101.82,-121.17,-109.23,-129.37,-116.95,-112.26,-134.19,-131.43,-117.28,-126.43,-122.72,-124.21,-98.56,-121.51,-115.09,-122.59,-97.37,-93.55,-82.04,-94.48,-86.57,-84.5,-39.99,-64.06,-29.21,-20.24,-0.5,-9.3,41.21,14.14,49.65,57.93,94.86,93.19,121.24,150.67,142.02,178.98,230.61,231.23,213.55,235.11,269.52,277.98,275.94,351.35,306.19,377.47,337.47,415.74,449.65,447.7,478.61,438.32,507.69,474.31,530.55,491.91,515.69,563.32,609.97,600.77,599.29,614.94,695.89,581,646.9,649.85,662.66,638.14,647.37,634.42,608.78,674.95,642.86,632.1,681.15,733.91,713.91,709.05,677.14,703.55,608.28,724.14,668.11,618.85,645.72,660.4,659.54,613.63,589.7,528.85,610.29,520.74,515.96,508.34,567.39,500.57,501.28,538.18,449.94,446.53,419.02,395.7,401.96,399.25,421.5,402.81,359.36,348.86,358.07,378.44,319.05,302.58,333.09,293.5,302.44,273.34,299.13,290.03,258.58,285.33,225.7,251.89,213.71,204.79,218.53,169.97,178.03,190.71,203.79,207,164.38,187.7,153.58,180.15,151.85,130.65,140.55,122.08,125.81,113.67,148.79,145.71,110.55,107.61,115.34,85.95,135.77,79.08,117.9,97.62,80.47,93,75.5,89.98,73.29,92.93,95.06,83.1,62.97,74.54,76.18,59.96,61.69,54.21,39.74,37.22,57.15,55.05,47.43,30.97,31.46,22.22,41.15,18.23,32.11,20.13,27.64,18.21,14.05,21.65,14.71,23.62,18.45,10.44,18.6,8.41,7.72,10.89,8.14,3.43,0.8,0.77,-2.37,-4.76,1.92,-1.03,-4.92,-2.27,-5.92,-7.18,-10.32,-10.19,-6.52,-13.16,-14.39,-8.89,-20.18,-18.61,-12.55,-23.75,-22.38,-20.78,-20.45,-27.37,-28.21,-26.46,-34.24,-29.01,-33.21,-33.78,-35.47,-39.6,-38.22,-37.5,-37.48,-36.05,-42.04,-48.75,-40.27,-46.64,-44.25,-48.36,-55.86,-43.41,-53.49,-55.79,-59.45,-61.96,-49.13,-57.96,-49.41,-63.88,-65.53,-57.26,-68.66,-52.53,-62.76,-61.27,-57.6,-64.2,-49.55,-63.74,-63.83,-59.81,-52.47,-70.85,-65.73,-54.39,-51.11,-70.62,-70.48,-69.35,-57.87,-69.09,-56.59,-55.75,-50.59,-61.73,-47.51,-61.56,-66.72,-75.49,-73.92,-46.64,-54.63,-63.93,-76.97,-61.77,-61.88,-59.17,-61.67,-67.67,-63.1,-72.98,-74.84,-78.59,-75.15,-72.97,-61.18,-75.62,-82.46,-83.47,-65.31,-67.63,-85.82,-61.54,-94.21,-93.72,-74.58,-99.41,-63.7,-82.13,-76.21,-97.07,-103.33,-86.52,-68.68,-81.98,-104.62,-108.08,-107.42,-96.11,-98.71,-104.2,-108.94,-101.02,-85.74,-84.28,-96.47,-91.12,-106.9,-101.69,-108.48,-94.75,-72.91,-101.49,-104.07,-90.93,-99.57,-79.21,-99.19,-98.22,-81.39,-99.13,-102.2,-87.69,-71.65,-66.4,-65.61,-88.61,-59.65,-86.11,-67.4,-83.88,-71.34,-57.33,-61.05,-72.51,-81.7,-68.44,-54.83,-66.69,-48.11,-51,-49.94,-45.82,-51.03,-50.18,-56.22,-57.55,-53.83,-41.32,-61.81,-55.75,-63.42,-37.49,-51.57,-39.38,-42.19,-48.07,-33.81,-35.79,-37.81,-45.54,-48.51,-43.88,-51.98,-41.03,-47.72,-33.42,-37.4,-35.72,-47.09,-50.37,-53.14,-33.61,-43.77,-35.71,-34.62,-33.84,-50.03,-50.71,-37.7,-39.05,-50.78,-39.31,-35.57,-45.55,-46.71,-43.08,-36.83,-40.75,-46.26,-45.14,-46.15,-40.98,-39.03,-40.66,-33.94,-38.04,-34.66,-38.02,-31.01,-26.97,-30.3,-32.71,-32.42,-24.55,-24.94,-29.99,-25.49,-25.32</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B233" t="str">
+        <v>[R_13_标记]</v>
+      </c>
+      <c r="C233" t="str">
+        <v>a: 36.6ms -183.1uv b: 77.4ms 839.5uv</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B234" t="str">
+        <v>[L_13_名字]</v>
+      </c>
+      <c r="C234" t="str">
+        <v>FERG(13)_dMax</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B235" t="str">
+        <v>[L_13_放大器]</v>
+      </c>
+      <c r="C235" t="str">
+        <v>1-75 Hz</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B236" t="str">
+        <v>[L_13_闪光]</v>
+      </c>
+      <c r="C236" t="str">
+        <v>b白色光:600.0cd.m-2,5ms</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B237" t="str">
+        <v>[L_13_闪光背景]</v>
+      </c>
+      <c r="C237" t="str">
+        <v>b背景光_关:0.0cd.m-2</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B238" t="str">
+        <v>[L_13_采样]</v>
+      </c>
+      <c r="C238" t="str">
+        <v>刺激间隔:15.0S</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B239" t="str">
+        <v>[L_13_分析时间]</v>
+      </c>
+      <c r="C239" t="str">
+        <v>200ms</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B240" t="str">
+        <v>[L_13_数据长度]</v>
+      </c>
+      <c r="C240" t="str">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B241" t="str">
+        <v>[L_13_详细数据(uv)]</v>
+      </c>
+      <c r="C241" t="str">
+        <v>6.71,7.66,8.57,9.43,10.24,10.99,11.69,12.33,12.91,13.44,13.89,14.29,14.62,14.89,15.09,15.23,15.3,15.31,15.25,15.13,14.96,14.72,14.42,14.07,13.66,13.2,12.69,12.13,11.53,10.89,10.21,9.49,8.74,7.95,7.14,6.31,5.45,4.58,3.7,2.79,1.89,0.97,0.08,-0.88,-1.86,-2.74,-3.68,-4.61,-5.55,-6.4,-7.54,-8.44,-9.26,-10.22,-11.31,-11.85,-12.86,-13.93,-15.35,-16.54,-17.69,-18.06,-20.52,-20.87,-23.42,-23.99,-28.67,-30.21,-30.56,-34.2,-33.31,-35.57,-42.43,-44.67,-47.55,-51.04,-45.28,-53.75,-59.02,-54.83,-66.64,-60.76,-76.95,-67.39,-74.38,-71.44,-78.22,-95.03,-89.18,-104.42,-84.85,-102.32,-97.14,-110.86,-88.58,-110.65,-103.32,-114.91,-113.94,-94.3,-102.54,-73.46,-88,-84.65,-56.91,-62.98,-42.44,-55.8,-36.32,-29.5,-23.23,6.47,-1.39,1.27,33.16,59.8,50.62,81.56,96.54,99.55,130.75,152.78,164.41,209.28,213.8,237.67,228.57,283.74,236.77,265.85,292.12,306.6,314.09,390.59,428.52,445.54,472.11,443.81,469.32,435.74,512.49,492.28,541.81,484.17,599.97,555.53,607.13,583.56,589.33,576.48,658.73,705.74,646.57,679.58,735.52,633.06,725.61,628.67,623.67,694.61,638.46,728.34,705.07,652.48,627.06,765.81,752.97,700.79,649.22,621.71,615.02,731.7,668.87,733.26,642.85,709.89,603.91,557.45,576.29,560.12,639.61,548.92,501.33,504.75,611.54,575.23,526.35,511.11,498.8,467.92,460.2,412.52,425.17,396.6,438.28,412.05,341.96,390.5,373.71,338.18,359.35,363.85,326.25,288.17,297.02,270.53,242.93,273.88,260.87,270.81,243.93,270.99,275.94,220.82,255.91,226.05,219.07,234.88,224.69,202.96,196.18,163.8,202.7,189.15,154.39,144.89,193.56,143.44,173.01,153.7,137.69,137.12,134.52,164.58,127.3,154.07,157.03,152.3,149.75,103.39,152.09,123.8,106.04,115.46,95.95,128.58,92.08,116.45,94.78,89.37,101.84,80.7,88.67,73.37,77.94,97.77,91.08,72.16,74.74,66.46,62.97,66.35,53.1,64.34,62.07,62.93,41.97,41.31,43.05,42.96,41.37,27.47,31.01,29.64,31.98,21.27,16.62,18.85,14.37,15.81,11,11.4,7.46,7.41,2.99,0.88,-11.21,-8.63,-10.6,-11.63,-12.92,-17.04,-16.15,-21.54,-23.67,-22.1,-23.93,-27.61,-31.32,-32.9,-25.93,-29.37,-33.64,-33.98,-38.92,-43.32,-32.47,-42.83,-42.47,-45.29,-42.52,-36.2,-35.88,-37.48,-45.76,-44.88,-45.2,-49.38,-41.86,-36.47,-44.52,-36.42,-37.75,-39.04,-48.18,-48.09,-37.04,-47.22,-43.5,-48.85,-40.2,-38.41,-39.46,-36.18,-37.53,-37.99,-47.86,-44.06,-29.4,-41.1,-38.52,-46.12,-34.69,-32.26,-39.75,-42.55,-32.75,-26.75,-45.47,-34.49,-26.14,-24.44,-24.51,-42.1,-26.36,-40.49,-43.07,-32.32,-43.75,-44.9,-50.76,-44.5,-37.15,-35.18,-27.49,-42.66,-32.08,-46.91,-33.19,-35.23,-60.5,-55.68,-53.13,-41.29,-55.53,-64.21,-46.57,-55.75,-46.93,-65.85,-69.46,-53.57,-55.79,-78.17,-80.67,-73.58,-62.67,-71.71,-71.69,-72.71,-87.31,-77.54,-69.73,-90.94,-62.54,-93.06,-90.14,-88.42,-85.22,-87.53,-76.51,-72.6,-93.7,-91.54,-94.15,-72.44,-81.13,-106.23,-108.4,-77.08,-89.85,-99.91,-79.62,-103.22,-86.93,-88.47,-99.65,-80.96,-103.48,-76.87,-103.15,-93.35,-89.53,-96.03,-62.19,-91.98,-95.95,-75.29,-65.12,-72.35,-83.14,-75.02,-68.66,-55.27,-80,-51.09,-48.35,-69.94,-48.93,-61.13,-47.84,-51.39,-48.74,-52.91,-57.17,-47.07,-41.44,-38.56,-50.56,-35.37,-30.06,-38.47,-47.82,-34.65,-36.97,-19.41,-27.84,-19.55,-41.69,-26.62,-37.98,-24.94,-33.96,-32.87,-25.32,-14.78,-28.93,-16.88,-29.32,-32.43,-11.56,-14.37,-22.9,-22.87,-28.46,-26.86,-14.93,-22.46,-20.41,-12.05,-11.73,-13.31,-19.03,-18.21,-22.13,-25.18,-20.36,-23.83,-13.96,-24.64,-16.72,-19.61,-18.46,-16.02,-22.48,-23,-13.96,-24.08,-23,-12.7</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B242" t="str">
+        <v>[L_13_标记]</v>
+      </c>
+      <c r="C242" t="str">
+        <v>a: 36.6ms -189.1uv b: 77.5ms 877.8uv</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B243" t="str">
+        <v>[R_14_名字]</v>
+      </c>
+      <c r="C243" t="str">
+        <v>FERG(14)_dOps</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B244" t="str">
+        <v>[R_14_放大器]</v>
+      </c>
+      <c r="C244" t="str">
+        <v>1-75 Hz</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B245" t="str">
+        <v>[R_14_闪光]</v>
+      </c>
+      <c r="C245" t="str">
+        <v>b白色光:600.0cd.m-2,5ms</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B246" t="str">
+        <v>[R_14_闪光背景]</v>
+      </c>
+      <c r="C246" t="str">
+        <v>b背景光_关:0.0cd.m-2</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B247" t="str">
+        <v>[R_14_采样]</v>
+      </c>
+      <c r="C247" t="str">
+        <v>刺激间隔:15.0S</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B248" t="str">
+        <v>[R_14_分析时间]</v>
+      </c>
+      <c r="C248" t="str">
+        <v>200ms</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B249" t="str">
+        <v>[R_14_数据长度]</v>
+      </c>
+      <c r="C249" t="str">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B250" t="str">
+        <v>[R_14_详细数据(uv)]</v>
+      </c>
+      <c r="C250" t="str">
+        <v>4.71,6.4,6.03,3.47,-0.66,-5.72,-10.98,-15.59,-18.6,-19.36,-18.03,-14.18,-10.12,-5.23,-1.08,1.63,2.24,0.82,-2.31,-6.13,-10.19,-14.99,-17.09,-17.44,-17.03,-13.84,-10.86,-7.22,-4.68,-3.84,-4.4,-8.23,-12.66,-17.16,-23.58,-27.58,-29.2,-28.35,-26.15,-20.76,-13.96,-6.5,-0.1,4.88,10.52,9.71,9.59,7.78,3.3,-2.96,-5.63,-8.73,-10.4,-9.57,-9.22,-8.61,-9.88,-8.73,-11.23,-14.8,-25.03,-28.72,-27.73,-31.09,-32.98,-24.77,-19.02,-9.93,-0.12,12.38,25.68,35.05,31.76,40.63,35.03,33.96,20.71,8.78,5.65,-6.73,-13.03,-20.34,-25.29,-31.61,-34.49,-31.72,-29.99,-44.5,-40.25,-45.15,-38.18,-33.91,-29.74,-21.29,-9.34,8.04,20.91,34.4,48.69,45.05,42.86,43.48,37.03,30.35,12.75,-1.38,-17.43,-32.61,-40.69,-48.24,-65.14,-53.15,-61.5,-55.64,-61.12,-52.37,-47.05,-41.78,-35.94,-29.29,-18.66,-8.74,12.87,25.05,36.21,39.53,49.21,58.07,50.8,33.25,24.53,8.11,-8.11,-24.21,-40.92,-51.44,-53.21,-66.33,-59.44,-51.8,-45.83,-53.46,-43.37,-27.25,-19.48,-14.43,-7.79,-1.67,6.79,6.06,12.27,29.32,25.71,38.63,36.01,32.58,28.33,16.23,8.31,-4.67,-16.56,-27.09,-36.69,-47.11,-41.44,-43.53,-37.32,-37.7,-21.33,-18.46,-9.84,-5.22,-1.11,-0.06,1.34,1.74,0.26,1.16,-0.38,2.48,2.26,6.26,7.18,6.53,2.27,-2.03,-8.23,-16.4,-24.02,-31.83,-33.7,-36.96,-35.79,-36.64,-29.68,-24.32,-17.02,-11.06,-7.21,-5.77,-6.41,-7.92,-12.47,-14.95,-19.88,-21.44,-22.78,-21.51,-17.69,-14.19,-11.39,-9.01,-8.07,-9.07,-12.25,-16.13,-20.72,-25.8,-29.43,-29.87,-30,-26.41,-22.13,-16.44,-11,-6.51,-3.8,-3.38,-4.93,-7.8,-12.16,-16.77,-20.18,-22.01,-21.68,-19.87,-16.07,-11.6,-7.01,-3.35,-1.26,-1.1,-2.94,-6.59,-11.03,-15.43,-18.96,-20.93,-20.79,-18.76,-15.03,-10.41,-5.79,-2.04,0.05,0.06,-1.96,-5.68,-10.51,-15.29,-19.4,-21.88,-22.39,-20.85,-17.65,-13.47,-9.2,-5.75,-3.87,-3.99,-6.15,-10.01,-14.88,-19.87,-24.09,-26.74,-27.39,-25.99,-22.87,-18.71,-14.41,-10.86,-8.82,-8.76,-10.75,-14.44,-19.17,-24.04,-28.16,-30.74,-31.32,-29.81,-26.54,-22.18,-17.59,-13.7,-11.28,-10.82,-12.39,-15.69,-20.06,-24.62,-28.47,-30.82,-31.18,-29.46,-25.95,-21.31,-16.42,-12.18,-9.39,-8.55,-9.77,-12.75,-16.87,-21.25,-24.97,-27.25,-27.58,-25.84,-22.31,-17.63,-12.66,-8.34,-5.44,-4.5,-5.65,-8.61,-12.76,-17.25,-21.15,-23.66,-24.27,-22.81,-19.56,-15.14,-10.41,-6.27,-3.55,-2.78,-4.1,-7.28,-11.7,-16.51,-20.78,-23.7,-24.73,-23.71,-20.86,-16.81,-12.38,-8.5,-5.99,-5.39,-6.89,-10.26,-14.88,-19.93,-24.48,-27.7,-29.03,-28.28,-25.67,-21.78,-17.46,-13.62,-11.08,-10.42,-11.83,-15.1,-19.65,-24.65,-29.17,-32.38,-33.71,-32.93,-30.25,-26.23,-21.71,-17.6,-14.75,-13.74,-14.78,-17.69,-21.91,-26.61,-30.88,-33.86,-34.98,-33.99,-31.07,-26.78,-21.94,-17.47,-14.22,-12.79,-13.42,-15.95,-19.84,-24.27,-28.32,-31.15,-32.14,-31.05,-28.03,-23.62,-18.63,-13.98,-10.53,-8.91,-9.36,-11.75,-15.56,-19.98,-24.1,-27.05,-28.22,-27.33,-24.51,-20.29,-15.46,-10.95,-7.61,-6.08,-6.66,-9.2,-13.21,-17.89,-22.33,-25.66,-27.23,-26.75,-24.34,-20.5,-16,-11.77,-8.68,-7.37,-8.15,-10.91,-15.16,-20.13,-24.89,-28.57,-30.5,-30.39,-28.3,-24.73,-20.45,-16.36,-13.35,-12.07,-12.86,-15.62,-19.89,-24.89,-29.71,-33.48,-35.5,-35.45,-33.4,-29.81,-25.43,-21.19,-17.95,-16.4,-16.89,-19.35,-23.33,-28.08,-32.68,-36.25,-38.1,-37.88,-35.62,-31.79,-27.11,-22.52,-18.89,-16.92,-16.97,-19.01,-22.62,-27.03,-31.36,-34.7,-36.37,-35.97,-33.55,-29.53,-24.65,-19.8,-15.9,-13.64,-13.42,-15.22,-18.63,-22.93,-27.2,-30.56</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B251" t="str">
+        <v>[R_14_标记]</v>
+      </c>
+      <c r="C251" t="str">
+        <v>83.3uv</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B252" t="str">
+        <v>[L_14_名字]</v>
+      </c>
+      <c r="C252" t="str">
+        <v>FERG(14)_dOps</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B253" t="str">
+        <v>[L_14_放大器]</v>
+      </c>
+      <c r="C253" t="str">
+        <v>1-75 Hz</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B254" t="str">
+        <v>[L_14_闪光]</v>
+      </c>
+      <c r="C254" t="str">
+        <v>b白色光:600.0cd.m-2,5ms</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B255" t="str">
+        <v>[L_14_闪光背景]</v>
+      </c>
+      <c r="C255" t="str">
+        <v>b背景光_关:0.0cd.m-2</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B256" t="str">
+        <v>[L_14_采样]</v>
+      </c>
+      <c r="C256" t="str">
+        <v>刺激间隔:15.0S</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B257" t="str">
+        <v>[L_14_分析时间]</v>
+      </c>
+      <c r="C257" t="str">
+        <v>200ms</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B258" t="str">
+        <v>[L_14_数据长度]</v>
+      </c>
+      <c r="C258" t="str">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B259" t="str">
+        <v>[L_14_详细数据(uv)]</v>
+      </c>
+      <c r="C259" t="str">
+        <v>-0.24,3.88,6.94,8.81,9.73,8.55,5.84,1.68,-2.54,-8.2,-13.59,-18.77,-23.14,-26.19,-27.98,-28.43,-28,-25.26,-21.97,-18.59,-13.17,-9.5,-5.35,-2.94,-1.29,-1.13,-1.85,-4.4,-6.5,-9.69,-13.7,-19.09,-20.67,-25.69,-27.01,-27,-26.87,-26.26,-24.63,-22.94,-20.74,-17.18,-17.04,-17.48,-14.66,-14.9,-17,-16.14,-17.63,-19.28,-19.3,-18.98,-18.62,-17.27,-13.46,-10.96,-5.53,1.36,2.22,5.06,7.34,10.02,8.34,5.65,0.34,-5.35,-12.06,-21.74,-26.28,-37.7,-38.56,-37.97,-40.57,-38.61,-37.76,-28.69,-20.78,-8.6,0.73,17.44,25.68,35.24,47.15,42.58,45.85,39.94,34.03,24.06,10.49,-3.67,-17.17,-30.22,-44.42,-58.74,-69.07,-64.33,-64.28,-68.39,-51.72,-46.48,-34.89,-24.29,-9.46,3.59,14.85,24.45,29.28,39.8,46.77,45.84,29.16,20.08,18.1,-0.44,-13.09,-23.64,-33.83,-42.72,-53.41,-58.34,-70.4,-69.49,-75.77,-63.2,-50.95,-50.58,-42.68,-32.69,-26.48,-17.35,-5.2,3.41,13.3,23.46,12.17,15.24,19.3,35.82,32.4,23.38,17.91,6.3,-3.92,-16.26,-29.65,-38.03,-49.23,-60.15,-58.21,-59.57,-62.58,-60.51,-57.7,-52.31,-36.32,-25.17,-12.63,2.69,19.66,29.28,33.37,44.33,55.31,40.2,46.06,33.88,22.39,13.8,-0.86,-14.24,-28.83,-35.94,-47.61,-56.71,-56.33,-52.49,-52.23,-49.27,-42.47,-30.8,-15.99,-6.29,3.73,10.55,18.91,24.62,23.65,24.13,19.01,8.16,2.32,-7.03,-14.6,-23.54,-29.17,-33.52,-36,-38.7,-35.73,-34.36,-34.24,-26.76,-24.51,-20.49,-17.38,-15.17,-15.42,-14.78,-15.54,-17.31,-19.14,-19.38,-20.98,-22.43,-23.78,-25.46,-25.97,-21.68,-19.94,-18.1,-15.53,-13.38,-12,-11.48,-10.17,-12.45,-14.31,-16.78,-19.2,-23.71,-25.4,-28.45,-30.41,-30.88,-30.2,-28.34,-24.64,-21.19,-15.84,-11.12,-6.23,-2.1,1.03,3.57,4.13,3.22,1.23,-2.2,-6.43,-11.16,-15.49,-20.01,-23.01,-25.66,-26.35,-25.54,-23.84,-20.41,-16.18,-11.63,-7.09,-2.88,0.5,2.63,3.37,2.93,0.82,-2.66,-6.91,-11.8,-16.78,-21.47,-25.38,-28.21,-29.76,-29.87,-28.63,-26.22,-22.95,-19.08,-15.02,-11.4,-8.45,-6.57,-5.98,-6.76,-8.9,-12.2,-16.38,-21.05,-25.8,-30.19,-33.87,-36.4,-37.61,-37.45,-35.84,-33.08,-29.36,-25.1,-20.72,-16.63,-13.25,-10.92,-9.83,-10.12,-11.71,-14.46,-18.08,-22.19,-26.37,-30.19,-33.25,-35.21,-35.86,-35.1,-32.98,-29.65,-25.41,-20.64,-15.77,-11.22,-7.41,-4.67,-3.23,-3.18,-4.5,-7.01,-10.43,-14.4,-18.48,-22.25,-25.3,-27.31,-28.05,-27.41,-25.45,-22.32,-18.32,-13.82,-9.23,-5.01,-1.56,0.81,1.84,1.46,-0.32,-3.32,-7.26,-11.77,-16.42,-20.77,-24.42,-27.04,-28.39,-28.38,-27.03,-24.5,-21.09,-17.16,-13.13,-9.44,-6.49,-4.6,-4.01,-4.82,-7,-10.36,-14.64,-19.46,-24.38,-28.98,-32.85,-35.65,-37.14,-37.22,-35.93,-33.42,-29.97,-25.96,-21.79,-17.92,-14.74,-12.58,-11.68,-12.15,-13.94,-16.9,-20.74,-25.1,-29.55,-33.65,-37.01,-39.28,-40.24,-39.77,-37.92,-34.83,-30.8,-26.2,-21.44,-16.97,-13.19,-10.45,-8.97,-8.87,-10.12,-12.56,-15.91,-19.81,-23.84,-27.56,-30.58,-32.54,-33.23,-32.54,-30.49,-27.26,-23.11,-18.42,-13.61,-9.13,-5.38,-2.7,-1.32,-1.36,-2.79,-5.46,-9.08,-13.29,-17.67,-21.79,-25.23,-27.66,-28.85,-28.67,-27.17,-24.48,-20.9,-16.79,-12.56,-8.66,-5.48,-3.38,-2.57,-3.18,-5.18,-8.4,-12.57,-17.33,-22.24,-26.87,-30.81,-33.71,-35.35,-35.59,-34.47,-32.14,-28.87,-25.02,-21.01,-17.28,-14.23,-12.21,-11.44,-12.04,-13.99,-17.12,-21.17,-25.77,-30.48,-34.89,-38.57,-41.19,-42.5,-42.39,-40.88,-38.13,-34.4,-30.07,-25.55,-21.27,-17.66,-15.05,-13.69,-13.68,-15.01,-17.54,-20.98,-24.98,-29.11,-32.95,-36.08,-38.16,-38.96,-38.36,-36.39,-33.19,-29.03,-24.3</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B260" t="str">
+        <v>[L_14_标记]</v>
+      </c>
+      <c r="C260" t="str">
+        <v>89uv</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B261" t="str">
+        <v>[R_15_名字]</v>
+      </c>
+      <c r="C261" t="str">
+        <v>FERG(15)_dMax</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B262" t="str">
+        <v>[R_15_放大器]</v>
+      </c>
+      <c r="C262" t="str">
+        <v>1-75 Hz</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B263" t="str">
+        <v>[R_15_闪光]</v>
+      </c>
+      <c r="C263" t="str">
+        <v>f白色光:1000.0cd.m-2,5ms</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B264" t="str">
+        <v>[R_15_闪光背景]</v>
+      </c>
+      <c r="C264" t="str">
+        <v>b背景光_关:0.0cd.m-2</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B265" t="str">
+        <v>[R_15_采样]</v>
+      </c>
+      <c r="C265" t="str">
+        <v>刺激间隔:15.0S</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B266" t="str">
+        <v>[R_15_分析时间]</v>
+      </c>
+      <c r="C266" t="str">
+        <v>200ms</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B267" t="str">
+        <v>[R_15_数据长度]</v>
+      </c>
+      <c r="C267" t="str">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B268" t="str">
+        <v>[R_15_详细数据(uv)]</v>
+      </c>
+      <c r="C268" t="str">
+        <v>-4.59,0.82,0.63,-5.22,-13.18,-18.39,-17.69,-11.65,-4.2,-0.16,-2.16,-9.03,-16.5,-19.9,-17.14,-9.98,-2.96,-0.52,-4.17,-11.6,-18.06,-19.44,-14.78,-6.96,-0.82,-0.13,-5.22,-12.74,-17.82,-17.1,-10.89,-2.94,1.89,0.72,-5.53,-12.74,-16.16,-13.47,-6.17,1.31,4.39,1.35,-5.74,-12.27,-14.01,-9.59,-1.78,4.48,5.51,0.64,-7.08,-12.58,-13.05,-7.45,0.34,4.36,3.34,-4.41,-12.26,-16.35,-15.13,-9.61,-5.56,-1.13,-8.12,-16.8,-25.08,-30.04,-32.21,-27.18,-18.56,-22.94,-31.13,-41.28,-49.64,-61.75,-53.28,-47.87,-56.61,-54.04,-76.43,-77.73,-81.44,-95.4,-89.13,-78.12,-83.11,-112.9,-96.82,-117.66,-142.17,-109.43,-132.43,-110.61,-115.7,-107.29,-139.04,-129.35,-108.61,-103.11,-85.21,-112.74,-107.24,-75.27,-67.32,-87.47,-74.4,-60.52,-31.36,-14.12,-11.91,17.46,-3.99,-4.78,41.14,65.2,106.12,116,101.58,143.5,125.6,187.03,174.66,233.47,214.77,230.71,284.15,258.4,282.25,356.94,379.04,326.68,432.82,387.54,413.66,462.31,502.33,472.79,469.01,503.55,581.66,548.89,569.13,537.56,605.12,615.02,612.32,643.39,702.56,738.38,638.02,604.68,756.63,728.2,713.33,754.26,668.8,664.1,645.75,664.23,751.77,665.54,652.47,768.6,672.15,635.67,618.74,672.48,670.22,703.11,711.68,605.83,674.36,604.43,637.28,651.79,620.61,537.16,594.46,519.16,563.3,523.46,511.18,527.39,525.18,493.98,446.83,472.92,393.14,394.65,391.05,383.05,346.39,337.56,351.04,343.55,314.04,313.47,324.46,269.3,286.6,302,250.68,278.51,242.7,209.23,234.17,213.47,231.97,248.61,206.09,204,174.38,167.69,186.94,192.1,191.13,189.36,168.47,171.45,166.81,165.98,147.54,187.42,135.63,183.7,136.17,135.06,154.63,144.82,145.4,161.2,140.07,149.3,120.12,135.32,95.37,116.91,83,124.24,112.47,108.33,88.82,79.07,58.44,55.58,88.93,76.52,98.29,72.98,67.01,40.54,55.91,46.79,55.22,69.31,56.46,39.48,43.28,26.95,30.34,19.63,32.72,37.75,26.79,11.83,3.08,4.09,5.69,8.48,12.89,6.97,2.7,-8.15,-15.88,-14.75,-8.96,-5.57,0.36,-4.34,-15,-16.83,-21.46,-27.62,-17.09,-7.73,-12.51,-14.33,-28.17,-34.32,-32.93,-26.33,-23.05,-19.83,-23.67,-20.01,-28.58,-40.79,-40.25,-33.7,-30.17,-16.71,-17.49,-26.52,-40.73,-40.35,-47.18,-29.03,-26.17,-23.34,-33.12,-41.62,-48.04,-49.08,-37.71,-45.73,-39.32,-33.9,-30.54,-37.56,-52.96,-53.52,-51.62,-46.14,-41.18,-39.45,-36.38,-58.88,-57.02,-66.23,-54.3,-34.96,-34.06,-48.66,-61.29,-60.37,-66.17,-56.67,-59.71,-45.71,-62.1,-66.95,-75.74,-76.61,-67.05,-82.3,-75.85,-48.64,-47.77,-77.2,-79.77,-82.55,-87.81,-78.25,-63.15,-78.27,-57.65,-69.81,-93.61,-81.66,-85.1,-89.89,-84.2,-89.5,-86.31,-80.53,-104.8,-77.63,-83.97,-77.27,-93.94,-89.38,-87.05,-87.84,-86.98,-105.69,-75.04,-82.39,-89.45,-78.57,-68.87,-114.96,-117.13,-103.53,-87.51,-66.08,-88.21,-98.13,-94.93,-113.86,-98.13,-99.54,-82.99,-65.9,-88.18,-66.38,-83.24,-107.76,-102.33,-105.87,-73.93,-63.59,-63.17,-98.91,-91.03,-75.96,-97.86,-106.13,-96.89,-58.2,-64.52,-82.86,-81.79,-80.07,-96.58,-65.53,-72.54,-88.93,-80.95,-90.03,-107.59,-91.61,-69.94,-77.43,-57.03,-89.35,-81.28,-79.05,-73.79,-72.66,-93.97,-88.7,-74.08,-62.71,-93.04,-88.31,-101.49,-98.48,-80.02,-69.44,-71.53,-76.83,-82.53,-70.23,-68.28,-81.74,-56.03,-57.15,-52.95,-55.05,-72.3,-73.46,-66.19,-75.1,-70.31,-59.41,-69.94,-60.59,-65.35,-65.32,-67.29,-56.72,-43.77,-55.94,-56,-53.64,-64.08,-63.59,-65.1,-43.67,-51.98,-53.82,-50.81,-58.1,-66.12,-60.77,-59.96,-50.05,-44.13,-28.42,-40.65,-44.6,-48.83,-53.31,-33.55,-39.59,-28.3,-31.69,-40.61,-42.39,-46.62,-34.2,-33.87,-21.48,-15.92,-30.43,-37.59,-32.81,-39.45,-30.55</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B269" t="str">
+        <v>[R_15_标记]</v>
+      </c>
+      <c r="C269" t="str">
+        <v>a: 40.3ms -191.6uv b: 84.5ms 932.2uv</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B270" t="str">
+        <v>[L_15_名字]</v>
+      </c>
+      <c r="C270" t="str">
+        <v>FERG(15)_dMax</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B271" t="str">
+        <v>[L_15_放大器]</v>
+      </c>
+      <c r="C271" t="str">
+        <v>1-75 Hz</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B272" t="str">
+        <v>[L_15_闪光]</v>
+      </c>
+      <c r="C272" t="str">
+        <v>f白色光:1000.0cd.m-2,5ms</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B273" t="str">
+        <v>[L_15_闪光背景]</v>
+      </c>
+      <c r="C273" t="str">
+        <v>b背景光_关:0.0cd.m-2</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B274" t="str">
+        <v>[L_15_采样]</v>
+      </c>
+      <c r="C274" t="str">
+        <v>刺激间隔:15.0S</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B275" t="str">
+        <v>[L_15_分析时间]</v>
+      </c>
+      <c r="C275" t="str">
+        <v>200ms</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B276" t="str">
+        <v>[L_15_数据长度]</v>
+      </c>
+      <c r="C276" t="str">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B277" t="str">
+        <v>[L_15_详细数据(uv)]</v>
+      </c>
+      <c r="C277" t="str">
+        <v>-35.24,-32.97,-27.18,-20.61,-16.33,-16.39,-20.88,-27.89,-34.37,-37.51,-35.98,-30.57,-23.77,-18.73,-17.76,-21.36,-27.95,-34.59,-38.33,-37.49,-32.46,-25.48,-19.69,-17.65,-20.24,-26.25,-32.92,-37.17,-37.02,-32.44,-25.4,-18.96,-15.9,-17.48,-22.86,-29.49,-34.26,-34.85,-30.88,-23.98,-17.12,-13.17,-13.84,-18.63,-25.31,-30.57,-32.09,-29,-22.63,-15.57,-11.24,-11.2,-15.58,-22.56,-28.39,-31.67,-29.16,-24.08,-17.34,-13.58,-12.83,-18.64,-25.97,-31.87,-37.47,-39.99,-35.53,-31.69,-27.12,-27.94,-34.78,-44.81,-54.84,-59.32,-65.55,-66.79,-54.98,-63.03,-51.51,-71.9,-76.23,-98.03,-88.17,-105.8,-104.22,-100.46,-107.24,-112.47,-115.99,-132.38,-127.89,-139.77,-126.44,-132.3,-142.47,-133.83,-137.16,-113.5,-152.03,-120.4,-129.72,-121.26,-130.6,-126.81,-94.78,-108.11,-75.42,-90.25,-68.66,-77.25,-59.02,-41.21,-39.67,0.22,22.87,3.71,55.91,73,64.35,107.76,81.42,140.67,152.15,163.36,213,186.21,201.24,200.9,280.69,258.43,328.12,311.35,363.02,349.04,428.61,431.13,455.17,414.73,484.85,429.05,520.65,471.19,581.25,522,562.87,522.71,528.34,582.73,637.4,626.5,692.61,616.38,707.08,752.83,596.59,649.25,693.16,742.41,721.54,745.24,634.59,679.99,637.34,717.07,708.01,678.85,701.49,747.84,708.26,732.55,752.15,743.89,694.79,612.57,693.62,570.05,565.95,553.93,545.05,575.75,538.84,534.44,526.1,505.79,469.94,446.86,444.8,449.48,507.07,420.77,378.93,428.57,395.13,383.54,341.03,358.74,366.62,341.59,347.11,335.77,270.13,243.27,249.12,257.02,265.08,254.97,282.6,258.47,203.51,226.42,216.07,188.22,167.34,202.34,177.19,191.44,203.46,181.11,180.82,138.32,145.16,167.5,132.64,152.78,142.24,127.35,158.81,129.98,115.35,142.91,133.23,125,148.11,119.12,112.97,133.89,110.73,106.99,117.21,77.36,95.04,79.26,104.99,76.06,78.62,96.99,67.54,47.11,52.29,75.81,49.08,47.69,76.6,71.24,68.63,53.05,49.4,28.58,36.75,28.12,43.44,34.1,39.43,35.29,24.87,11.68,2.08,-3.77,-5.13,12.11,7.65,9.1,8.7,0.22,-12.36,-22.33,-17.21,-22.37,-7.97,-7.07,-3.92,-9.01,-18.59,-28.19,-31.81,-36.1,-35.83,-25.65,-20.01,-18.8,-18.54,-28.61,-31.25,-44.24,-39.82,-40.67,-34.88,-26.75,-28.73,-20.83,-30.39,-38.13,-46.2,-42.47,-49.66,-47.16,-33.16,-33.21,-25.34,-31.61,-45.12,-45.63,-56.43,-48.96,-54.33,-47.27,-35.01,-34.4,-31.21,-34.69,-57.65,-63.49,-64.19,-48.21,-38.81,-43.65,-29.85,-43.47,-57.48,-60.09,-65.86,-69.76,-62.05,-48.96,-41.77,-43.58,-48.87,-48.62,-69.13,-73.74,-58.76,-69.14,-54.01,-46.29,-40.63,-47.63,-72.79,-73.78,-71.81,-75.3,-69.36,-82.06,-73.05,-74.41,-57.48,-82.39,-68.57,-68.43,-102.46,-86.77,-68.48,-68.71,-73.01,-79.75,-85.13,-73.08,-83.08,-104.06,-98.92,-92.9,-80.4,-97.77,-69.56,-69.9,-68.64,-102.83,-116.08,-109.03,-89.92,-78.95,-102.69,-75.32,-101.77,-93.77,-103.01,-102.98,-119.79,-82.51,-108.3,-78.01,-96.93,-90.61,-95.94,-109.73,-115.06,-83.06,-79.57,-104.6,-66.58,-86.96,-95.2,-88.88,-101.01,-80.36,-80.35,-99.35,-81.26,-76.99,-72.47,-59.78,-82.14,-97.26,-85.94,-84.26,-78.61,-86.72,-98.45,-57.92,-55.67,-92.46,-62.18,-84.53,-109.11,-102.14,-96.98,-82.34,-89.83,-81.25,-80.91,-78.31,-94.92,-93.89,-85.7,-96.54,-87.89,-70.76,-53.42,-60.31,-58.71,-89.1,-74.41,-75.27,-70.57,-59.46,-78.79,-71.47,-57.64,-68.79,-58.77,-85.92,-80.89,-88.72,-70.06,-68.6,-46.35,-54.23,-50.67,-56.45,-71.43,-80.18,-74.43,-74.24,-47.76,-42.53,-37.42,-60.41,-64.62,-63.45,-67.75,-57.1,-56.72,-58.87,-55.53,-32.24,-47.96,-41.88,-52.71,-64.2,-60.38,-46.98,-53.03,-35.21,-24.83,-29.96,-29.96,-48.25,-50.29,-48.57,-39.77,-36.88,-23.94,-24.81,-16.91,-30.96,-37.19,-31.45,-37.6,-30.98,-24.77,-17.72</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B278" t="str">
+        <v>[L_15_标记]</v>
+      </c>
+      <c r="C278" t="str">
+        <v>a: 40.2ms -196.1uv b: 84.8ms 965.1uv</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B279" t="str">
+        <v>[R_16_名字]</v>
+      </c>
+      <c r="C279" t="str">
+        <v>FERG(16)_dOps</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B280" t="str">
+        <v>[R_16_放大器]</v>
+      </c>
+      <c r="C280" t="str">
+        <v>1-75 Hz</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B281" t="str">
+        <v>[R_16_闪光]</v>
+      </c>
+      <c r="C281" t="str">
+        <v>f白色光:1000.0cd.m-2,5ms</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B282" t="str">
+        <v>[R_16_闪光背景]</v>
+      </c>
+      <c r="C282" t="str">
+        <v>b背景光_关:0.0cd.m-2</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B283" t="str">
+        <v>[R_16_采样]</v>
+      </c>
+      <c r="C283" t="str">
+        <v>刺激间隔:15.0S</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B284" t="str">
+        <v>[R_16_分析时间]</v>
+      </c>
+      <c r="C284" t="str">
+        <v>200ms</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B285" t="str">
+        <v>[R_16_数据长度]</v>
+      </c>
+      <c r="C285" t="str">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B286" t="str">
+        <v>[R_16_详细数据(uv)]</v>
+      </c>
+      <c r="C286" t="str">
+        <v>-10.01,-2.72,5.91,5.61,-3.43,-9.71,-5.48,3.93,6.64,-1.07,-9.63,-8.67,0.03,5.39,0.48,-9.54,-11.66,-3.5,5.18,3.19,-5.12,-9.52,-2.91,7.39,9.72,2.93,-3.66,-0.2,11.4,15.54,9.49,0.84,-0.42,8.87,14.76,10.3,-0.75,-5.82,-1.41,6.13,3.59,-5.95,-11.38,-9.17,-1.08,4.14,-2.6,-7.92,-5.27,6.51,15.87,13.92,5.58,5.41,14.48,24.5,23.39,13.71,8.92,13.06,17.41,15.43,2.88,-9.84,-13.7,-9.43,-8.79,-14.68,-26.31,-32.96,-21.14,-10.11,-15.37,-19.87,-17.27,-6.43,9.1,17.49,16.49,9.72,21.77,35.21,38.43,25.7,23.03,14.84,18.53,15.48,4.3,-14.09,-27.23,-24.34,-26.71,-37.38,-44.52,-56.59,-48,-32.2,-27.26,-24.44,-24.54,-14.42,4.41,23.94,25.49,24.14,25.97,43.35,56.6,61.28,37.53,30.49,24.82,27.7,17.33,-3.97,-24.32,-35.6,-36.85,-36.68,-42.69,-55.45,-62.52,-55.29,-38.63,-24.72,-28.29,-15.41,3.61,22.74,38.99,40.81,37.99,56.09,58.15,72.72,59.31,36.56,33.36,29.14,23.15,6.65,-16.84,-25.5,-35.23,-30.85,-47.43,-53.88,-63.13,-53.31,-37.85,-25.95,-24.05,-19.02,-7.52,13.99,27.74,27.13,30.88,36.63,48.64,50.27,39.3,27.02,14.98,19.58,13.77,6.08,-12.39,-28.3,-29.76,-24.24,-28.31,-33.54,-50.85,-47.1,-30.61,-23.56,-19.02,-18.67,-15.84,-0.96,12.91,15.58,13.71,9.77,18.72,23.55,30.2,18.57,2.75,3.81,8.23,8.45,-2.36,-15.63,-19.97,-14.42,-10.49,-11.83,-19.72,-23.09,-18.81,-4.03,-1.19,-7.12,-10.31,-3.59,8.8,16.5,10.46,4.18,5.7,13.06,20.72,14.21,4.74,0.01,4.75,11.28,8.59,-2.09,-9.17,-7.33,1.75,4.2,-2.14,-11.12,-9.13,1.15,6.64,2.73,-5.35,-6.7,2,10.59,9.22,-0.2,-5.7,0.12,8.37,9.77,0.57,-7.68,-5.99,2.52,6.25,-0.62,-10.43,-11.72,-3.44,3.17,-0.36,-10.04,-13.87,-7.3,1.37,1.64,-7.15,-13.66,-9.79,-0.17,3.12,-3.85,-12.49,-12,-2.85,3.08,-1.44,-11.03,-13.65,-6.29,1.92,0.61,-8.56,-14.08,-8.99,0.55,2.68,-4.96,-12.67,-10.41,-0.78,4.49,-0.81,-9.73,-10.72,-2.21,5.53,3.15,-6.03,-10.19,-3.8,5.47,6.29,-2.04,-8.85,-5.33,4.35,8.33,1.86,-6.76,-6.52,2.45,9.09,5.26,-4.12,-7.2,-0.03,8.5,7.76,-1.3,-7.34,-2.82,6.55,8.98,1.33,-6.95,-5.64,3.45,8.76,3.43,-6.09,-8.15,-0.42,7.13,4.77,-4.86,-10.03,-4.59,4.3,5.19,-3.39,-11.06,-8.56,0.61,4.64,-1.87,-11.12,-11.86,-3.51,3.17,-0.49,-10.21,-14.1,-7.57,0.97,0.6,-8.43,-15.01,-11.08,-1.71,1.25,-6.01,-14.49,-13.63,-4.54,1.39,-3.24,-12.6,-14.92,-7.21,0.99,-0.45,-9.58,-14.8,-9.39,0.09,2,-5.8,-13.31,-10.84,-1.22,3.82,-1.73,-10.62,-11.4,-2.79,4.77,2.14,-7.08,-11.02,-4.44,4.73,5.32,-3.12,-9.75,-6.01,3.68,7.42,0.76,-7.76,-7.3,1.73,8.18,4.1,-5.31,-8.19,-0.89,7.5,6.47,-2.69,-8.57,-3.87,5.44,7.6,-0.23,-8.4,-6.87,2.24,7.33,1.77,-7.72,-9.54,-1.7,5.69,3.08,-6.6,-11.56,-5.94,2.89,3.52,-5.18,-12.69,-9.95,-0.76,3.05,-3.64,-12.79,-13.27,-4.8,1.72,-2.15,-11.85,-15.5,-8.77,-0.3,-0.9,-9.99,-16.36,-12.18,-2.79,-0.04,-7.44,-15.77,-14.64,-5.45,0.32,-4.5,-13.8,-15.85,-7.97,0.13,-1.54,-10.7,-15.69,-10.05,-0.6,1.08,-6.84,-14.18,-11.46,-1.79,3.04,-2.7,-11.52,-12.05,-3.32,4.08,1.2,-8.03,-11.76,-5.01,4.06,4.39,-4.16,-10.64,-6.68,2.98,6.47,-0.38,-8.83,-8.15,0.95,7.18,2.85,-6.57,-9.24,-1.8,6.43,5.13,-4.13,-9.84,-4.95,4.29,6.18,-1.81,-9.88,-8.13,1.02</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B287" t="str">
+        <v>[R_16_标记]</v>
+      </c>
+      <c r="C287" t="str">
+        <v>77.3uv</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B288" t="str">
+        <v>[L_16_名字]</v>
+      </c>
+      <c r="C288" t="str">
+        <v>FERG(16)_dOps</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B289" t="str">
+        <v>[L_16_放大器]</v>
+      </c>
+      <c r="C289" t="str">
+        <v>1-75 Hz</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B290" t="str">
+        <v>[L_16_闪光]</v>
+      </c>
+      <c r="C290" t="str">
+        <v>f白色光:1000.0cd.m-2,5ms</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B291" t="str">
+        <v>[L_16_闪光背景]</v>
+      </c>
+      <c r="C291" t="str">
+        <v>b背景光_关:0.0cd.m-2</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B292" t="str">
+        <v>[L_16_采样]</v>
+      </c>
+      <c r="C292" t="str">
+        <v>刺激间隔:15.0S</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B293" t="str">
+        <v>[L_16_分析时间]</v>
+      </c>
+      <c r="C293" t="str">
+        <v>200ms</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B294" t="str">
+        <v>[L_16_数据长度]</v>
+      </c>
+      <c r="C294" t="str">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B295" t="str">
+        <v>[L_16_详细数据(uv)]</v>
+      </c>
+      <c r="C295" t="str">
+        <v>6.02,2.82,5,10.02,12.58,9.62,4.25,1.11,4.07,9.15,11.95,9.25,4.43,2.34,5.7,11.55,14.8,12.27,7.59,5.86,9.31,14.32,17.41,13.51,8.49,5.6,7.93,12.41,13.54,9.45,2.38,0.69,2.61,6.82,9.47,5.38,2.5,1.51,5.75,12.93,16.29,14.52,11.55,11.53,17.08,26.28,26.12,23.94,18.02,15.53,19.98,21.04,19.55,12.71,4.36,-1.73,-2.46,1.92,2.02,-5.13,-10.03,-15.96,-9.24,0.57,5.53,2.99,4.17,8.37,18,28.89,36.57,38.36,33.3,36.78,32.3,39.13,37.81,25.76,14.97,4.99,0.77,-3.73,-8.37,-22.58,-38.44,-39.03,-37.99,-31.19,-31.02,-27.55,-21.01,-13.02,1.12,16.37,26.62,30.66,30.25,35.8,56.46,50.77,49.6,54.87,35.8,33.18,26.53,17.26,4.66,-12,-27.62,-32.43,-38.56,-41.62,-38.87,-41.01,-43.65,-43.59,-24.67,-10.78,2.6,9.27,16.9,30.39,53.47,56.07,64.12,59.96,61.42,45.91,60.88,50.17,34.66,18.87,1.52,-7.22,-19.41,-24,-33.95,-42.69,-48.55,-37.3,-40.38,-19.4,-17.3,-14.27,-6.83,5.26,21.95,33.83,36.79,40.36,35.73,43.32,46.3,51.31,45.75,32.34,20.95,13.43,9.85,4.28,-8.1,-16.06,-27.74,-28.79,-22.81,-23.53,-22.37,-19.12,-21.22,-13.3,-0.14,7.43,10.26,11.59,12.5,19.03,22.26,31.75,22.23,15.72,11.67,12.49,16.88,13.77,6.39,-2.87,-7.27,-6.58,-3.94,-2.39,-5.87,-11.13,-11.86,-7.09,-0.45,3.35,1.75,-1.32,-0.5,5.47,12.56,14.36,11.37,7.42,4.98,8.25,13.12,13.74,8.95,3.08,0.72,3.76,7.79,8.42,4.02,-0.95,-2.24,1.29,7.26,8.47,5.12,0.37,0.3,5.13,10.6,11.62,7.62,3.19,2.67,7.04,11.78,12.35,7.63,2.45,1.69,5.96,10.27,10.08,5.21,0.28,-0.18,4.19,8.58,8.58,3.79,-0.98,-0.94,3.66,8.06,7.68,2.84,-1.72,-1.54,3.13,7.35,6.71,1.69,-2.85,-2.46,2.2,6.27,5.43,0.34,-4.03,-3.41,1.42,5.43,4.46,-0.62,-4.76,-3.81,1.17,5.15,4.05,-1.01,-4.92,-3.71,1.43,5.32,4.08,-0.99,-4.69,-3.21,2.02,5.82,4.41,-0.66,-4.17,-2.44,2.89,6.56,4.98,-0.11,-3.43,-1.48,3.91,7.42,5.65,0.52,-2.64,-0.5,4.9,8.23,6.23,1.04,-1.99,0.31,5.69,8.79,6.54,1.28,-1.63,0.79,6.12,8.98,6.47,1.13,-1.67,0.87,6.14,8.74,5.98,0.56,-2.12,0.54,5.73,8.08,5.08,-0.39,-2.94,-0.15,4.98,7.1,3.87,-1.62,-4.01,-1.07,4.02,5.92,2.51,-2.97,-5.16,-2.05,3.02,4.73,1.16,-4.26,-6.22,-2.92,2.15,3.7,0.02,-5.32,-7.03,-3.51,1.57,2.98,-0.8,-6.01,-7.45,-3.71,1.39,2.66,-1.2,-6.29,-7.45,-3.49,1.62,2.75,-1.19,-6.14,-7.03,-2.87,2.23,3.2,-0.83,-5.66,-6.3,-1.96,3.09,3.88,-0.26,-4.99,-5.39,-0.92,4.05,4.62,0.36,-4.29,-4.5,0.07,4.92,5.25,0.84,-3.76,-3.79,0.85,5.54,5.61,1.02,-3.52,-3.41,1.27,5.79,5.57,0.82,-3.69,-3.43,1.28,5.61,5.11,0.19,-4.27,-3.86,0.87,5.02,4.24,-0.83,-5.21,-4.64,0.13,4.1,3.07,-2.11,-6.38,-5.63,-0.8,3.01,1.76,-3.5,-7.63,-6.66,-1.76,1.92,0.48,-4.81,-8.77,-7.56,-2.57,1.01,-0.59,-5.89,-9.65,-8.17,-3.06,0.42,-1.33,-6.6,-10.13,-8.39,-3.17,0.23,-1.65,-6.89,-10.18,-8.17,-2.84,0.45,-1.56,-6.77,-9.83,-7.56,-2.16,1.02,-1.14,-6.33,-9.17,-6.67,-1.22,1.8,-0.53,-5.71,-8.36,-5.66,-0.2,2.64,0.11,-5.08,-7.57,-4.7,0.73,3.34,0.6,-4.63,-6.97,-3.98,1.39,3.76,0.78,-4.5,-6.71,-3.61,1.68,3.78,0.55,-4.77,-6.86,-3.65,1.53,3.37</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B296" t="str">
+        <v>[L_16_标记]</v>
+      </c>
+      <c r="C296" t="str">
+        <v>78.9uv</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B297" t="str">
+        <v>[R_17_名字]</v>
+      </c>
+      <c r="C297" t="str">
+        <v>FERG(17)_dMax</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B298" t="str">
+        <v>[R_17_放大器]</v>
+      </c>
+      <c r="C298" t="str">
+        <v>1-75 Hz</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B299" t="str">
+        <v>[R_17_闪光]</v>
+      </c>
+      <c r="C299" t="str">
+        <v>f白色光:2000.0cd.m-2,5ms</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B300" t="str">
+        <v>[R_17_闪光背景]</v>
+      </c>
+      <c r="C300" t="str">
+        <v>b背景光_关:0.0cd.m-2</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B301" t="str">
+        <v>[R_17_采样]</v>
+      </c>
+      <c r="C301" t="str">
+        <v>刺激间隔:15.0S</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B302" t="str">
+        <v>[R_17_分析时间]</v>
+      </c>
+      <c r="C302" t="str">
+        <v>200ms</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B303" t="str">
+        <v>[R_17_数据长度]</v>
+      </c>
+      <c r="C303" t="str">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B304" t="str">
+        <v>[R_17_详细数据(uv)]</v>
+      </c>
+      <c r="C304" t="str">
+        <v>-8.28,-24.43,-14.17,3.05,-5.92,-22.53,-13.15,4.61,-3.39,-20.45,-12.01,6.21,-0.82,-18.32,-10.87,7.71,1.63,-16.28,-9.88,8.98,3.84,-14.46,-9.16,9.9,5.69,-12.97,-8.81,10.37,7.08,-11.9,-8.9,10.33,7.97,-11.28,-9.46,9.76,8.33,-11.14,-10.49,8.67,8.17,-11.45,-11.97,7.08,7.54,-12.17,-13.87,5.04,6.43,-13.22,-16.13,2.52,4.95,-14.77,-18.88,-0.45,2.51,-17.07,-22.49,-4.45,-0.1,-19.62,-26.95,-10.25,-4.68,-25.43,-31.67,-16.51,-13.51,-30.3,-44.24,-29.42,-23.07,-43.66,-54.38,-42.56,-30.21,-57.6,-71.45,-64.76,-57.99,-82.25,-88.9,-74.65,-79.95,-84.21,-109.4,-106.38,-79.38,-98.1,-125.03,-97.59,-91.51,-118.53,-130.83,-145.83,-97.64,-144.75,-139.26,-131.89,-124.32,-137.07,-133.41,-120.82,-96.1,-98.2,-125.01,-95.25,-62.8,-36.86,-42.43,-19.31,16.35,-12.07,-6,12.83,57.57,56.04,67.15,93.79,96.56,135.07,114.39,150.37,178.56,215.88,219.34,224.22,257.71,276.78,275.79,265.4,363.61,326.36,375.19,370.58,396.5,403.6,421.55,410.95,541.5,559.03,477.14,476.57,548.42,586.55,531.15,545.58,547.29,585.29,596.45,630.86,624.7,641.58,621.24,643.76,773.77,738.52,697.47,608.97,661.67,662.76,663.89,642.25,790.14,650.11,710.9,724.7,635.95,741.6,639.63,700.9,663.99,578.93,620.11,552.61,642.66,660.91,525.74,502.94,518.26,518.74,540.94,488.92,442.3,508.61,433.57,455.27,399.9,440.65,416.9,398.85,331.54,379.42,347.14,331.86,343.88,336.69,275.21,242.39,251.49,293.38,269.58,204.52,271.65,253.24,254.84,177.07,216.97,228.84,203.94,161.69,201.51,214.57,192.87,148.09,179.54,154.42,162.9,167.44,174.45,187.05,167.65,141.08,153.57,147.91,138.63,104.74,153.48,172.35,154.54,137.73,129.66,111.85,95.87,101.22,134.48,103.41,98.61,89.19,76.75,118.15,75.42,90.28,60.14,100.5,93.34,47.17,61.78,76.91,74.92,64.13,38.97,69.55,75.72,37.2,43.68,65.26,46.48,17,35.18,44.78,38.27,24.92,11.86,33.28,28.2,13.14,4.45,30.2,20.07,8.29,-0.23,22.23,24.54,1.03,-1.02,19.71,12.36,-6.8,-4.15,7.21,6.67,-10.17,-14.57,7.11,3.99,-8.05,-16.21,-0.3,8.62,-14.03,-22.21,0.06,3.99,-16.51,-23.89,-7.18,4.45,-13.06,-30.78,-10.87,-1.82,-22.03,-28.57,-13.41,-13.26,-29.22,-39.53,-13.26,-17.38,-25.07,-47.19,-32.64,-17.68,-40.32,-43.89,-22.95,-18.5,-35.52,-47.72,-43.78,-29.35,-45.47,-52.93,-48.11,-37.64,-43.16,-53.1,-38.18,-29.44,-54.82,-56.94,-44.93,-39.95,-56.34,-67.38,-55.16,-45,-45.33,-66.07,-71.74,-33.85,-65.04,-63.56,-54.79,-44.21,-45.88,-67.26,-64.3,-57.08,-57.89,-90.21,-55.95,-52.96,-48.88,-78.73,-56.18,-58.2,-55.59,-64.34,-82.09,-40.22,-68.39,-82.04,-67.03,-39.93,-53.33,-80.15,-90.28,-63.71,-60.76,-92.47,-58.71,-64.29,-44.54,-81.6,-61.74,-53.89,-74.53,-73.4,-73.19,-41.48,-68.03,-85.32,-98.49,-52.87,-66.39,-79.36,-96.31,-71.93,-52.04,-77.89,-87.49,-68.24,-71.19,-72.46,-98.32,-85.53,-67.5,-72.56,-105.41,-54.63,-81.73,-64.6,-102.74,-83.32,-80.94,-83.2,-81.55,-70.19,-65.49,-95.04,-83.4,-61.93,-62.57,-87.64,-92.56,-57.91,-66.94,-100.55,-77.4,-67.82,-70.37,-76.81,-76.14,-58.11,-79.23,-82.35,-86.86,-83.03,-69.66,-81.78,-77.81,-69.94,-39.97,-79.2,-78.24,-74.27,-47.85,-56.02,-81.04,-57.42,-60.2,-47.48,-80.29,-50.93,-31.7,-52.78,-75.69,-62.15,-30.53,-50.31,-68.67,-46.6,-22.38,-58.77,-59.52,-55.65,-25.19,-32.34,-60.17,-41.53,-14.57,-40.05,-55.65,-49.09,-33.34,-40.69,-36.97,-44.07,-23.7,-17.67,-52.46,-30.24,-15.63,-31.27,-39.12,-39.29,-14.8,-17.04,-41,-39.74,-9.57,-23.92,-38.03,-36.53,-12.79,-13.93,-29.69,-27.45,-12.39,-15.45,-32.65,-36,-11.47,-6.44,-35.59,-28.39,-12.96</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B305" t="str">
+        <v>[R_17_标记]</v>
+      </c>
+      <c r="C305" t="str">
+        <v>a: 43.7ms -216.3uv b: 91.4ms 907.3uv</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B306" t="str">
+        <v>[L_17_名字]</v>
+      </c>
+      <c r="C306" t="str">
+        <v>FERG(17)_dMax</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B307" t="str">
+        <v>[L_17_放大器]</v>
+      </c>
+      <c r="C307" t="str">
+        <v>1-75 Hz</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B308" t="str">
+        <v>[L_17_闪光]</v>
+      </c>
+      <c r="C308" t="str">
+        <v>f白色光:2000.0cd.m-2,5ms</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B309" t="str">
+        <v>[L_17_闪光背景]</v>
+      </c>
+      <c r="C309" t="str">
+        <v>b背景光_关:0.0cd.m-2</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B310" t="str">
+        <v>[L_17_采样]</v>
+      </c>
+      <c r="C310" t="str">
+        <v>刺激间隔:15.0S</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B311" t="str">
+        <v>[L_17_分析时间]</v>
+      </c>
+      <c r="C311" t="str">
+        <v>200ms</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B312" t="str">
+        <v>[L_17_数据长度]</v>
+      </c>
+      <c r="C312" t="str">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B313" t="str">
+        <v>[L_17_详细数据(uv)]</v>
+      </c>
+      <c r="C313" t="str">
+        <v>-16.59,-20.52,-6.67,1.69,-9.32,-20.46,-12.26,1.78,-1.8,-16.35,-16.47,-1.4,3.73,-9.26,-17.59,-6.43,5.76,-1.24,-14.92,-11.33,3.9,5.33,-9.01,-14.12,-0.95,8.56,-1.72,-13.72,-7.02,7.19,4.65,-10.11,-12.42,1.77,8.16,-4.78,-15.26,-5.43,6.09,-0.1,-16.36,-14.08,-0.02,-0.64,-14.54,-23.11,-14.05,-5.81,-12.96,-30.92,-26.41,-12.54,-14.31,-36.76,-46.46,-33.4,-20.38,-38,-58.23,-46.21,-39.26,-47.76,-75.1,-74.2,-51.3,-68.72,-85.77,-99.93,-89.25,-76.39,-87.09,-94.42,-87.93,-80.41,-81.16,-109.15,-130.83,-77.26,-89.15,-88.55,-97.11,-92.66,-99.6,-94.28,-91.81,-104.53,-83.37,-81.72,-61.83,-75.89,-44.96,-14.81,-7.54,-25.33,12.39,38.17,30.35,25.8,48.01,62.22,95.66,119.08,125.09,105.43,193.02,136.45,159.73,209,193.24,244.2,264.52,305.65,266.26,319.48,314.91,342.73,396.5,448.19,467.95,377.97,471.17,463.39,520.56,555.31,556.74,577,533.1,538.34,568.82,521.91,556.18,682.26,695.28,552.4,596.65,608.09,652.45,638.43,601.98,731.11,645.74,626.64,747.36,674.82,701.89,753.95,743.66,618.96,633.34,778.54,738.64,763.54,657.83,672.37,685.17,743.51,641.01,705.2,659.45,701.81,649.16,628.64,573.54,602.59,559.12,560.48,635.79,580.2,570.99,525.97,482.59,580.34,478.53,528.48,463.55,452,450,464.22,436.77,466.38,419.07,358.4,400.97,380.16,371.96,408.86,336.36,339.18,386.19,364.09,333.7,333.11,296.64,332.8,305.57,272.72,254.77,257.81,244.02,226.17,210.59,268.42,226.76,204.57,202.09,216.12,234.34,207.68,222.57,171.45,213.97,172.98,148.55,186.04,159.64,168.38,129.91,153.57,145.16,125.58,160.33,111.61,95.81,122.73,115.14,124.18,102.29,108.65,119.99,117.93,80.14,95.49,88.36,94.07,62.41,70.44,71.02,60.66,70.25,48.8,36.2,60.85,60.35,24.33,33.17,32.65,32.09,33.8,20.71,15.18,33.69,21.17,-6.06,-1.23,13.67,13.36,-3.32,-0.96,4.84,10.82,-7.77,-12.64,-9.97,-2.43,-7.67,-23.48,-22.62,-4.33,-7.66,-15.13,-27.14,-12.12,-9.9,-18.44,-32.37,-23.42,-15.1,-11.58,-32.52,-33.09,-20.48,-17.99,-28.6,-41.45,-27.77,-10.76,-25.07,-35.5,-38.11,-26.95,-13.53,-36.37,-34.9,-26.88,-22.18,-22.04,-41.97,-37.17,-28.48,-30.85,-38.07,-41.34,-37.93,-20.24,-40.46,-59.51,-40.16,-28.89,-25.92,-54.98,-45.65,-39.73,-27.54,-47,-60.59,-48.15,-45.66,-39.93,-65.74,-64.89,-44.55,-49.09,-65.98,-68.01,-70.18,-55.75,-61.59,-66.98,-76.74,-65.46,-51.18,-71.64,-73.53,-55.79,-51.49,-82.6,-87.9,-88.42,-61.33,-80.92,-89.36,-87.24,-67,-67.45,-67.72,-106,-64.54,-63.75,-81.91,-93.23,-87.72,-63.09,-67.75,-92.4,-102.42,-74.45,-75.28,-72.26,-114.72,-90.67,-94.4,-74.6,-109.11,-98.52,-88.13,-57.27,-85.91,-98.78,-93.5,-61.91,-84.04,-113.62,-74.78,-66.53,-78.24,-78.9,-113.16,-64.66,-66.04,-92.75,-110.76,-106.4,-66.42,-69.47,-84.65,-87.42,-92.39,-80.31,-80.26,-86.24,-89.53,-92.35,-88.1,-73.68,-77.66,-68.6,-67.14,-97.54,-99.73,-96.57,-88.42,-91.1,-92.83,-97.69,-58.65,-77.52,-97.52,-78.14,-76.55,-69.59,-88.49,-92.3,-89.35,-69.95,-64.6,-82.36,-81.2,-78.97,-81.86,-75.17,-81.43,-80.4,-77.97,-77.89,-85.39,-83.21,-73.04,-59.54,-89.28,-73.02,-82.75,-69.71,-88.48,-93.16,-75.78,-64.87,-68.7,-84.77,-66.69,-70.15,-64.74,-81.47,-89.85,-60.64,-58.64,-71.62,-80.67,-81.29,-62.75,-42.43,-75.27,-62.12,-63.99,-50.92,-56.28,-59.76,-50.78,-41.55,-45.11,-57.53,-53.77,-51.94,-36.14,-45.47,-48.09,-53.07,-23.33,-40.81,-48.48,-54.18,-29.53,-22.22,-36.19,-51.48,-37.98,-19.48,-36.11,-47.35,-42.49,-25.21,-15.83,-41.12,-37.12,-19.96,-18.02,-25.24,-39.55,-34.95,-16.51,-15.73,-33.63,-35.94,-15.53,-11.08,-32.34,-40.62,-22.26,-16.96,-22.59,-39.26</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B314" t="str">
+        <v>[L_17_标记]</v>
+      </c>
+      <c r="C314" t="str">
+        <v>a: 43.7ms -215.2uv b: 91.2ms 970.5uv</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B315" t="str">
+        <v>[R_18_名字]</v>
+      </c>
+      <c r="C315" t="str">
+        <v>FERG(18)_dOps</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B316" t="str">
+        <v>[R_18_放大器]</v>
+      </c>
+      <c r="C316" t="str">
+        <v>1-75 Hz</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B317" t="str">
+        <v>[R_18_闪光]</v>
+      </c>
+      <c r="C317" t="str">
+        <v>f白色光:2000.0cd.m-2,5ms</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B318" t="str">
+        <v>[R_18_闪光背景]</v>
+      </c>
+      <c r="C318" t="str">
+        <v>b背景光_关:0.0cd.m-2</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B319" t="str">
+        <v>[R_18_采样]</v>
+      </c>
+      <c r="C319" t="str">
+        <v>刺激间隔:15.0S</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B320" t="str">
+        <v>[R_18_分析时间]</v>
+      </c>
+      <c r="C320" t="str">
+        <v>200ms</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B321" t="str">
+        <v>[R_18_数据长度]</v>
+      </c>
+      <c r="C321" t="str">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B322" t="str">
+        <v>[R_18_详细数据(uv)]</v>
+      </c>
+      <c r="C322" t="str">
+        <v>-9.97,2.89,3.31,-9.27,-0.44,6.53,-6.77,-3.98,7.75,-2.8,-6.84,6.88,1.75,-8.04,4.21,5.63,-7.54,0.29,7.91,-5.43,-4.18,7.69,-2.65,-8.18,4.99,0.52,-10.39,0.87,2.87,-10.78,-3.77,4.53,-8.3,-7.87,4.96,-4.04,-10.02,4.03,0.79,-10.09,0.84,4.08,-9.38,-4.53,4.14,-8.58,-10.65,1.2,-8.44,-16.96,-5.22,-7.81,-21.75,-12.26,-6.89,-22.73,-15.97,-6.2,-16.71,-17.28,-1.86,-7.65,-12.98,1.46,3.82,-9.55,4.78,9.85,-3.94,-2.63,10.44,-3.81,-10.32,0.35,-9.82,-22.05,-12.1,-15.57,-28.62,-24.67,-16.31,-34.72,-29.81,-16.74,-22.32,-20.06,-1.19,-1.57,-4.89,14.24,22.16,14.03,22.26,36.75,21.37,16.41,25.2,14.29,4.64,9.62,-3.75,-21.35,-21.58,-28.39,-48.35,-40.08,-28.34,-47.37,-49.34,-25.47,-29.94,-26.67,-5.11,1.34,-0.54,23.33,36.21,28.37,43.27,43.78,33.32,32.31,36.23,22.32,5.98,8.65,-4.48,-29.06,-28.73,-36.83,-58.86,-58.88,-51.67,-58.44,-60.31,-47,-44.26,-46.54,-17.85,-7.32,-6.84,18.32,26.44,19.37,34.57,41.75,45.85,26.84,45.12,20.76,4.5,5.7,-5.46,-31.01,-36.5,-32.19,-65.63,-69.34,-61.65,-71.38,-71.32,-47.9,-42.52,-44.88,-19.02,-8.73,-12.29,6.06,22.58,21.46,31.14,34.73,33.32,29.31,36.62,17.75,3.97,6.66,1.18,-19.73,-19.53,-19.65,-35.8,-42.27,-27.11,-39.45,-44.64,-26.12,-24.02,-28.97,-12.04,-3.42,-11.04,1.06,12.45,7.81,5.8,21.82,14.12,8.12,16.78,8.81,-5.79,2.95,1.91,-15.56,-13.7,-7.19,-23.05,-25.32,-11.41,-21.11,-29.89,-15.7,-13.95,-24.64,-13.28,-5.89,-17.44,-11.18,0.64,-9.8,-11.65,1.59,-5.48,-13.43,-2.29,-5.04,-18.72,-10.02,-5.84,-20.67,-18.39,-8.04,-20.8,-24.33,-11.38,-17.37,-26.5,-14.04,-12.18,-25.16,-15.63,-8.11,-20.94,-18.06,-5.61,-15.96,-20.06,-6.22,-11,-20.91,-8.95,-7.32,-20.47,-12.9,-5.08,-18.28,-17.04,-4.71,-14.35,-19.77,-5.83,-9.67,-20.34,-8.37,-5.35,-18.59,-11.52,-2.5,-15.03,-14.61,-1.67,-10.52,-16.74,-3.13,-6.04,-17.37,-6.39,-2.62,-16.2,-10.49,-0.96,-13.43,-14.43,-1.46,-9.74,-17.2,-4.02,-6.09,-18.21,-8.1,-3.48,-17.29,-12.78,-2.67,-14.82,-17.07,-4.01,-11.55,-20.07,-7.32,-8.46,-21.2,-11.97,-6.48,-20.35,-16.97,-6.27,-17.91,-21.28,-8.06,-14.67,-24.01,-11.59,-11.59,-24.66,-16.16,-9.59,-23.21,-20.77,-9.31,-20.15,-24.41,-10.91,-16.34,-26.27,-14.08,-12.77,-25.94,-18.08,-10.37,-23.53,-21.93,-9.7,-19.61,-24.66,-10.92,-15.1,-25.53,-13.65,-11.05,-24.26,-17.12,-8.35,-21.04,-20.38,-7.55,-16.55,-22.48,-8.72,-11.77,-22.78,-11.44,-7.74,-21.08,-14.9,-5.32,-17.65,-18.13,-4.99,-13.24,-20.22,-6.73,-8.84,-20.57,-10.04,-5.46,-19.04,-14.04,-3.9,-15.97,-17.74,-4.54,-12.13,-20.24,-7.24,-8.5,-20.97,-11.4,-6.04,-19.83,-16.1,-5.48,-17.22,-20.28,-7.07,-13.92,-23.07,-10.58,-10.9,-23.94,-15.31,-9.09,-22.86,-20.28,-9.11,-20.28,-24.44,-11.14,-17.02,-26.96,-14.86,-14.05,-27.37,-19.52,-12.27,-25.74,-24.11,-12.25,-22.59,-27.62,-14.12,-18.8,-29.28,-17.48,-15.38,-28.74,-21.57,-13.2,-26.15,-25.38,-12.81,-22.15,-27.95,-14.27,-17.68,-28.61,-17.17,-13.78,-27.11,-20.7,-11.31,-23.72,-23.87,-10.76,-19.15,-25.8,-12.15,-14.41,-25.86,-15,-10.51,-23.9,-18.47,-8.31,-20.29,-21.57,-8.21,-15.8,-23.45,-10.14,-11.42,-23.53,-13.53,-8.18,-21.74,-17.51,-6.83,-18.49,-21.06,-7.68,-14.57,-23.32,-10.55,-10.98,-23.77,-14.79,-8.69,-22.39,-19.44,-8.34,-19.61,-23.46,-10.15,-16.27,-26.02,-13.83,-13.33,-26.64,-18.63,-11.71,-25.34,-23.56,-11.97,-22.64,-27.58,-14.25,-19.38,-29.88,-18.15,-16.53,-30.06,-22.89,-14.97,-28.25,-27.44,-15.23,-25.01,-30.81</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B323" t="str">
+        <v>[R_18_标记]</v>
+      </c>
+      <c r="C323" t="str">
+        <v>80.1uv</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B324" t="str">
+        <v>[L_18_名字]</v>
+      </c>
+      <c r="C324" t="str">
+        <v>FERG(18)_dOps</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B325" t="str">
+        <v>[L_18_放大器]</v>
+      </c>
+      <c r="C325" t="str">
+        <v>1-75 Hz</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B326" t="str">
+        <v>[L_18_闪光]</v>
+      </c>
+      <c r="C326" t="str">
+        <v>f白色光:2000.0cd.m-2,5ms</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B327" t="str">
+        <v>[L_18_闪光背景]</v>
+      </c>
+      <c r="C327" t="str">
+        <v>b背景光_关:0.0cd.m-2</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B328" t="str">
+        <v>[L_18_采样]</v>
+      </c>
+      <c r="C328" t="str">
+        <v>刺激间隔:15.0S</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B329" t="str">
+        <v>[L_18_分析时间]</v>
+      </c>
+      <c r="C329" t="str">
+        <v>200ms</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B330" t="str">
+        <v>[L_18_数据长度]</v>
+      </c>
+      <c r="C330" t="str">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B331" t="str">
+        <v>[L_18_详细数据(uv)]</v>
+      </c>
+      <c r="C331" t="str">
+        <v>7.09,-11.74,-11.69,8.4,1.05,-14.42,1.08,11,-8.3,-8.81,11.22,3.11,-13.07,1.83,11.09,-8.58,-9.92,9.63,1.93,-14.82,0.63,10.46,-8.84,-10.19,10.25,3.42,-12.27,3.36,13.89,-4.16,-4.73,15.6,8.52,-8.25,5.41,15.36,-5.06,-7.81,9.9,0.67,-17.86,-6.02,2.28,-19.77,-21.44,-2.93,-13.09,-27.99,-13.43,-2.79,-21.26,-20.85,1.87,-2.88,-15.8,0.31,13.36,-2.34,-5.8,13.27,7.24,-7.29,0.85,10.12,-13.81,-19.53,-4.76,-15.03,-39.26,-28.96,-22.39,-44.85,-45.4,-24.64,-25.84,-43.55,-23.01,-8.82,-19.9,-14.7,11.48,13.85,-1,25.25,38.42,15.45,10.92,31.51,25.57,3.16,8.57,11.96,-15.4,-28.75,-17.4,-31.23,-49.07,-45.25,-32.31,-46.46,-50.53,-22.45,-27.8,-34,-7.95,14.17,4.69,12.65,38.28,51.87,40.48,48.22,70.34,34,33.83,38.49,22.29,-4.34,-3.93,-5.3,-34.88,-50.83,-44.93,-41.31,-79.63,-51.92,-52.98,-53.44,-49.82,-16.7,-11.35,-18.54,8.91,28.58,19.22,20.23,60.21,40.92,36.87,45.77,46.07,22.71,8.51,14.59,-5.43,-38.06,-34.8,-30.41,-55.03,-63.84,-45.84,-48.49,-76.37,-54.04,-29.18,-45.92,-38.61,-6.1,0.7,-6.21,12.54,36.8,20.76,22.02,30.87,38.15,9.66,15.33,22.04,-4.72,-17.9,-6.49,-16.88,-44.99,-32.64,-24.84,-46.36,-51.86,-31.25,-27.02,-42.3,-22.86,-2.96,-14.09,-13.31,11.54,14.92,-1.05,15.38,33.5,12.67,9.85,24.67,18.71,-3.47,2.54,12.1,-9.76,-18.92,-1.45,-10.3,-26.74,-16.88,-6.45,-19.64,-27.93,-4.48,-5.93,-21.49,-7.63,8.39,-6.5,-11.96,8.99,7.21,-9.75,0.18,11.9,-5.26,-12.76,4.22,-0.26,-20.69,-11.36,0.53,-17.73,-25.45,-6.83,-9.43,-28.81,-18.5,-4.36,-20.87,-26.65,-6.49,-8.4,-26.79,-15.63,-0.95,-17.92,-24.5,-4.32,-6.71,-25.72,-15.03,-1.58,-18.73,-25.55,-6.14,-8.35,-27.58,-17.31,-2.72,-19.48,-26.43,-6.33,-7.81,-26.52,-15.74,-0.66,-16.85,-23.4,-3.03,-4.18,-22.77,-12.16,2.89,-13.28,-20.2,-0.08,-1.13,-20.03,-9.74,5.29,-10.97,-18.17,1.86,0.77,-18.22,-8.2,6.86,-9.33,-16.8,3.12,2.1,-17.05,-7.33,7.71,-8.56,-16.37,3.31,2.29,-17.14,-7.81,7.13,-9.26,-17.46,1.97,0.93,-18.74,-9.74,5.14,-11.3,-19.8,-0.53,-1.51,-21.33,-12.58,2.35,-14.05,-22.76,-3.56,-4.39,-24.26,-15.67,-0.61,-16.87,-25.7,-6.48,-7.06,-26.9,-18.37,-3.1,-19.12,-27.99,-8.67,-8.92,-28.64,-20.1,-4.54,-20.27,-29.11,-9.64,-9.51,-29.07,-20.5,-4.62,-20.04,-28.84,-9.21,-8.71,-28.12,-19.52,-3.36,-18.49,-27.29,-7.55,-6.72,-26.03,-17.48,-1.09,-16.01,-24.88,-5.11,-4.05,-23.35,-14.92,1.59,-13.21,-22.25,-2.55,-1.35,-20.73,-12.54,3.99,-10.78,-20.08,-0.55,0.7,-18.85,-10.97,5.51,-9.31,-18.95,0.35,1.6,-18.17,-10.66,5.73,-9.17,-19.17,-0.12,1.11,-18.89,-11.74,4.56,-10.4,-20.74,-1.91,-0.67,-20.85,-14.02,2.25,-12.72,-23.32,-4.65,-3.32,-23.61,-17,-0.69,-15.57,-26.35,-7.74,-6.23,-26.51,-20.04,-3.58,-18.27,-29.12,-10.48,-8.69,-28.88,-22.45,-5.76,-20.18,-31.03,-12.28,-10.14,-30.17,-23.73,-6.75,-20.84,-31.64,-12.76,-10.23,-30.09,-23.61,-6.34,-20.11,-30.87,-11.86,-8.98,-28.67,-22.2,-4.67,-18.16,-28.94,-9.86,-6.68,-26.29,-19.89,-2.2,-15.49,-26.36,-7.31,-3.93,-23.54,-17.32,0.45,-12.74,-23.81,-4.89,-1.4,-21.11,-15.16,2.59,-10.6,-21.94,-3.23,0.28,-19.6,-14,3.66,-9.58,-21.26,-2.81,0.68,-19.41,-14.18,3.36,-9.94,-21.97,-3.79,-0.31,-20.6,-15.72,1.72,-11.61,-23.94,-5.98,-2.47,-22.9,-18.32,-0.9,-14.19,-26.75,-8.93,-5.3,-25.77,-21.4,-3.91,-17.06,-29.75,-11.98,-8.13,-28.55,-24.28,-6.63,-19.54,-32.26</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B332" t="str">
+        <v>[L_18_标记]</v>
+      </c>
+      <c r="C332" t="str">
+        <v>84.8uv</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B333" t="str">
+        <v>[R_19_名字]</v>
+      </c>
+      <c r="C333" t="str">
+        <v>FERG(19)_lCone</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B334" t="str">
+        <v>[R_19_放大器]</v>
+      </c>
+      <c r="C334" t="str">
+        <v>1-75 Hz</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B335" t="str">
+        <v>[R_19_闪光]</v>
+      </c>
+      <c r="C335" t="str">
+        <v>b白色光:600.0cd.m-2,5ms</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B336" t="str">
+        <v>[R_19_闪光背景]</v>
+      </c>
+      <c r="C336" t="str">
+        <v>b白色光:30.0cd.m-2</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B337" t="str">
+        <v>[R_19_采样]</v>
+      </c>
+      <c r="C337" t="str">
+        <v>刺激间隔:1.0S</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B338" t="str">
+        <v>[R_19_分析时间]</v>
+      </c>
+      <c r="C338" t="str">
+        <v>200ms</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B339" t="str">
+        <v>[R_19_数据长度]</v>
+      </c>
+      <c r="C339" t="str">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B340" t="str">
+        <v>[R_19_详细数据(uv)]</v>
+      </c>
+      <c r="C340" t="str">
+        <v>2.77,-6.18,-1.08,1.08,-6.94,1.47,-1.81,-6.03,2.65,-4.89,-3.83,2,-7.14,-1.2,-0.35,-7.85,0.81,-3.68,-6.88,1.33,-6.92,-4.73,0.04,-9.07,-2.34,-2.77,-9.53,-0.72,-6.27,-8.32,-0.65,-9.37,-6.03,-2.31,-11.16,-3.68,-5.3,-11.11,-2.25,-8.66,-9.44,-2.41,-11.41,-6.88,-4.24,-12.68,-4.53,-7.32,-12.12,-3.41,-10.45,-10.09,-3.91,-12.91,-7.33,-5.9,-14.4,-5.42,-9.68,-13.39,-4.71,-13.75,-11.16,-6.05,-16.09,-10.63,-9.69,-19.44,-10.58,-16.14,-19.22,-11.2,-19.9,-20.24,-16.94,-25.21,-16.17,-19.93,-26.99,-19.95,-27.33,-28.42,-24.17,-33.5,-31.81,-32.98,-32.77,-34.47,-33.31,-36.14,-34.77,-41.87,-46.04,-32.56,-37.53,-44.24,-31.24,-49.07,-33.52,-32.8,-31.55,-26.17,-34.84,-36.82,-23.81,-24.35,-22.86,-20.83,-24.74,-4.56,-16.13,-12,-2.54,-7.77,-4.62,16.69,9.58,4.34,15.02,9.42,38.47,23.5,27.23,55.62,51.87,50.34,66.82,65.31,77.43,69.34,62.18,84.64,91.51,90.47,90.22,103.1,99.71,117.72,97.68,145.35,114.99,120.21,148,119.75,137.45,154.5,127.64,163.65,161.65,179.8,177.98,191.02,170.93,210.79,209.84,161.56,215.92,180.99,213.2,192.21,226.35,192.4,180.32,213.6,222.1,187.86,209.19,212.22,213.04,226.37,207.7,185.35,216.48,217.81,233.67,251.08,220.87,193.14,205.11,232.16,196.78,184.78,174.62,198.79,192.95,214.55,203.09,168.6,175.06,182.84,185.62,197.15,176.64,190.84,185.65,185.95,161.26,175.09,146.68,149.8,152.84,143.41,152.86,139.4,113.11,109.85,113.04,95.6,110.44,102.75,109.27,88.44,85.39,85.45,84.45,74.66,75.67,69.47,74.97,58.99,52.6,60.39,61.39,52.67,54.02,46.1,37.33,44.74,30.38,27.24,33.58,25.72,30.27,23.19,17.33,17.9,15.84,12.26,14.69,4.41,8.07,12.9,3.26,11.36,3.48,-3.63,8.28,-0.24,-2.06,5.21,-7.5,0.87,-3.6,-8.15,0.57,-4.42,-10.2,-3.22,-10.94,-7.62,-3.51,-12.89,-6.69,-7.58,-14.88,-5.55,-13.4,-14.41,-6.11,-17.78,-11.96,-10.6,-17.31,-12.77,-13.06,-21.43,-11.3,-18.51,-20.23,-12.71,-20.82,-16.57,-18.41,-25.14,-13.77,-22.55,-25.15,-18.31,-23.37,-26.78,-21.77,-24.89,-22.45,-21.92,-32.04,-19.83,-27.79,-30.03,-26.33,-32.34,-26.88,-25.41,-36.93,-28.82,-28.92,-32.6,-29.29,-31.51,-40.05,-27.65,-33.69,-38.77,-31,-38.72,-35.7,-33.81,-44.58,-31.53,-41.92,-37.17,-32.21,-48.44,-33.72,-38.23,-42.45,-32.98,-42.74,-40.68,-36.64,-44.75,-47.99,-32.31,-39.71,-47.81,-38.39,-44.33,-41.16,-42.06,-52.01,-31.79,-41.39,-43.82,-41.54,-52.32,-39.58,-43.63,-45.68,-40.78,-39,-47.46,-33.96,-57.76,-38.6,-52.53,-53.62,-48.16,-41.04,-52.24,-41.43,-52.03,-59.82,-48.79,-54.11,-43.57,-49.4,-64.1,-39.13,-48.62,-52.48,-41.39,-62.11,-57.68,-40.88,-61.84,-59.82,-52.27,-66.02,-54.66,-45.26,-58.48,-50.02,-48.83,-63.87,-53.17,-60.17,-61.01,-55.29,-62.15,-43.93,-63.36,-61.73,-41.38,-52.22,-47.43,-51.82,-47.75,-45.34,-43.82,-58.84,-56.56,-53.49,-63.25,-51.1,-61.34,-48.99,-50.18,-63.95,-40.46,-52.61,-55.45,-35.37,-55.23,-52.43,-38.06,-44.11,-43.77,-37.12,-45.89,-37.2,-51.47,-44.55,-45.15,-48.67,-39.51,-42.29,-50.82,-32.33,-42.9,-50.79,-41.75,-38.37,-37.28,-27.61,-43.87,-36.59,-28.4,-38.29,-34.34,-31.41,-36.49,-26.09,-33.35,-30.57,-28.6,-31.48,-27.35,-23.74,-32.85,-25.79,-29.95,-34.81,-27.56,-29.89,-27.28,-20.76,-33.81,-30.63,-26.19,-34.01,-21.08,-24.21,-31.76,-21.84,-26.37,-26.28,-19.01,-27.49,-23.04,-24.93,-30,-21.99,-24.8,-30.87,-20.15,-28.32,-26.04,-19.16,-29.11,-24.18,-20.64,-28.03,-19.24,-24.63,-25.85,-19.74,-28.13,-23.71,-18.7,-27.09,-22.47,-20.89,-27.93,-19.2,-22.68,-26.44,-16.9,-25.66,-21,-17.58,-27.34</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B341" t="str">
+        <v>[R_19_标记]</v>
+      </c>
+      <c r="C341" t="str">
+        <v>a: 47.3ms -37.4uv b: 98.3ms 184.8uv</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B342" t="str">
+        <v>[L_19_名字]</v>
+      </c>
+      <c r="C342" t="str">
+        <v>FERG(19)_lCone</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B343" t="str">
+        <v>[L_19_放大器]</v>
+      </c>
+      <c r="C343" t="str">
+        <v>1-75 Hz</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B344" t="str">
+        <v>[L_19_闪光]</v>
+      </c>
+      <c r="C344" t="str">
+        <v>b白色光:600.0cd.m-2,5ms</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B345" t="str">
+        <v>[L_19_闪光背景]</v>
+      </c>
+      <c r="C345" t="str">
+        <v>b白色光:30.0cd.m-2</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B346" t="str">
+        <v>[L_19_采样]</v>
+      </c>
+      <c r="C346" t="str">
+        <v>刺激间隔:1.0S</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B347" t="str">
+        <v>[L_19_分析时间]</v>
+      </c>
+      <c r="C347" t="str">
+        <v>200ms</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B348" t="str">
+        <v>[L_19_数据长度]</v>
+      </c>
+      <c r="C348" t="str">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B349" t="str">
+        <v>[L_19_详细数据(uv)]</v>
+      </c>
+      <c r="C349" t="str">
+        <v>-3.85,-3.04,-16.22,-1.83,-4.33,-15.58,-0.22,-5.92,-14.75,0.92,-7.73,-13.75,1.54,-9.68,-12.64,1.63,-11.69,-11.45,1.16,-13.66,-10.24,0.18,-15.51,-9.05,-1.28,-17.15,-7.93,-3.14,-18.51,-6.93,-5.33,-19.53,-6.09,-7.75,-20.16,-5.43,-10.28,-20.36,-5,-12.81,-20.13,-4.79,-15.24,-19.48,-4.82,-17.45,-18.42,-5.08,-19.34,-17,-5.56,-20.83,-15.29,-6.25,-21.86,-13.35,-7.1,-22.4,-11.3,-8.09,-22.43,-9.2,-9.2,-21.99,-7.2,-10.43,-21.05,-5.53,-11.7,-19.96,-4.21,-13.2,-18.31,-3.46,-15.11,-16.96,-3.56,-16.47,-16.34,-3.41,-19.93,-15.38,-6.56,-21.33,-16.08,-8.3,-26.02,-17.1,-15.41,-29.64,-19.44,-17.96,-37.35,-20.69,-23.81,-39.66,-28.44,-37.05,-39.12,-30.98,-35.39,-54.36,-29.73,-42.83,-45.15,-33.29,-49.53,-56.21,-41.61,-50.14,-62.72,-37.59,-52.34,-57.09,-39.76,-57.95,-37.42,-30.95,-58.15,-39.6,-36.34,-47.87,-28.79,-24.31,-34.65,-24.75,-20.34,-29.7,-1.5,-10.54,-10.65,6.19,1.74,9.3,25.99,12.13,22.92,38.59,31.55,40.29,59.12,42.35,51.21,58.09,53.34,60.21,78.41,74.24,73.61,97.11,70.64,119.43,116.04,96.65,119.66,136.85,125.2,127.16,129.75,144.58,150.69,142.61,175.3,184.46,171.78,171.56,197.22,173.37,165.61,229.44,211.58,211.75,210.37,217.9,190.65,189.07,208,203.83,252.05,188.4,248.99,213.06,244.96,234.98,235.45,194.74,256.92,225.37,226.58,240.88,202.78,186.37,206.46,188.66,218.67,220.54,169.32,190.4,182.67,147.3,168.39,158.63,143.35,162.42,170.4,126.24,129.24,150.03,135.1,137.68,127.06,115.63,103.58,115.97,76.34,93.77,87.51,77.16,87.6,76.09,60.55,66.4,63.38,45.97,56.89,46.92,34.76,41.28,28.21,29.24,34.26,23.84,21.03,30.99,11.23,15.66,20.71,7.74,13.28,16.52,0.91,11.46,9.21,-4.27,8.61,6.46,-5.56,6.66,0.7,-8.52,5.14,-1.76,-9.73,5.61,-6.5,-8.83,4.62,-8.53,-7.62,4.91,-10.6,-7.18,3.07,-12.33,-5.61,1.32,-14.93,-4.31,1.37,-14.8,-3.76,-2.25,-16.93,-3.29,-4.45,-16.92,-0.95,-6.49,-18.16,-0.86,-8.45,-15.9,-2.87,-11.49,-18.58,-0.49,-14.99,-16.37,-2.03,-17.66,-18.85,-7.86,-22.75,-16.3,-7.43,-21.62,-16.72,-11.59,-27.42,-14.68,-14.76,-25.52,-14,-13.7,-33.82,-19.28,-22.48,-29.7,-19.8,-20.09,-31.32,-16.88,-30.04,-31.23,-22.12,-30.12,-34.05,-23.12,-36.98,-34.37,-16.1,-31.89,-35.09,-24.8,-38.45,-34.84,-27.02,-35.33,-27.14,-27.41,-36.29,-22.44,-22.77,-46.42,-28.22,-36.22,-40.24,-20.75,-30.56,-41.32,-18.41,-32.8,-37.09,-20.5,-39.32,-39.55,-32.15,-37.95,-33.66,-32.68,-36.36,-38.86,-33.62,-33.43,-32.13,-25.12,-44.13,-40.78,-27.83,-51.94,-40.18,-34.02,-38.64,-25.4,-33.69,-51.12,-25.51,-44,-55.83,-36.09,-39.04,-43.85,-27.57,-37.1,-44.37,-41.77,-42.24,-49.23,-34.91,-55.96,-36.5,-40.96,-53.26,-36.66,-34.34,-55.81,-47.13,-27.52,-62.27,-49.33,-31.04,-54.6,-34.24,-40.24,-51.36,-34.42,-48.36,-46.62,-43.48,-53.24,-46.42,-45.96,-44.46,-61.77,-41.63,-51.83,-42.68,-30.61,-51.71,-44.34,-30.29,-57.9,-50.99,-26.88,-53.94,-37.76,-31.64,-51.74,-34.85,-37.35,-40.12,-40.09,-39.83,-42,-32.59,-33.83,-39.01,-27.84,-39.41,-49.14,-18.65,-26.99,-33.66,-22.56,-36.35,-39.01,-25.02,-38.65,-34.61,-19.14,-36.19,-26.32,-20.62,-37.05,-29.93,-18.92,-35.67,-15.83,-12.39,-33.29,-20.14,-16.77,-23.45,-10.51,-10.61,-27.95,-10.1,-16.43,-27.14,-8.81,-18.99,-26.85,-10.52,-18.48,-26.72,-5.1,-18.25,-21.54,-4.29,-17.24,-21.36,-5.41,-21.54,-20.23,-10.38,-23.96,-13.7,-7.61,-25.74,-15.8,-9.87,-22.97,-13.44,-8.27,-22.72,-7.21,-11.39,-22.01,-7.57,-14.1,-22.6,-5.77,-13.86,-20.58,-5.57,-15.62,-17.2,-4.43,-18.17,-17.25</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B350" t="str">
+        <v>[L_19_标记]</v>
+      </c>
+      <c r="C350" t="str">
+        <v>a: 47.2ms -43.5uv b: 98.3ms 162.2uv</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B351" t="str">
+        <v>[R_20_名字]</v>
+      </c>
+      <c r="C351" t="str">
+        <v>FERG(20)_lFlicker</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B352" t="str">
+        <v>[R_20_放大器]</v>
+      </c>
+      <c r="C352" t="str">
+        <v>1-300 Hz</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B353" t="str">
+        <v>[R_20_闪光]</v>
+      </c>
+      <c r="C353" t="str">
+        <v>b白色光:600.0cd.m-2,5ms</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B354" t="str">
+        <v>[R_20_闪光背景]</v>
+      </c>
+      <c r="C354" t="str">
+        <v>b白色光:30.0cd.m-2</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B355" t="str">
+        <v>[R_20_采样]</v>
+      </c>
+      <c r="C355" t="str">
+        <v>刺激频率:20.0Hz</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B356" t="str">
+        <v>[R_20_分析时间]</v>
+      </c>
+      <c r="C356" t="str">
+        <v>200ms</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B357" t="str">
+        <v>[R_20_数据长度]</v>
+      </c>
+      <c r="C357" t="str">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B358" t="str">
+        <v>[R_20_详细数据(uv)]</v>
+      </c>
+      <c r="C358" t="str">
+        <v>-41.26,-50.58,-53.26,-44,-59.06,-30.54,-57.19,-27.95,-35.82,-38.03,-32.28,-40.31,-14.91,-31.47,-11.26,-18.04,-13.87,-1.83,-11.91,10.75,-6.55,12.91,9.92,14.17,28.61,14.17,36.29,19.32,33.54,30.67,30.96,48.82,30.68,53.36,36.89,50.04,47.48,50.29,60.21,43.94,60.65,43.48,55.9,61.21,48.54,61.05,46.04,63.8,53.67,54.17,63.74,50.8,62.97,49.34,67.33,53.18,55.75,49.54,40.09,62.12,47.54,56.91,55.45,51.53,54.67,44.46,55.28,44.02,55.55,50.74,50.76,63.07,35.49,59.18,44.73,54.43,54.89,45.3,57.75,35.88,51.85,39.69,43.42,46.24,36.61,49.31,27.25,45.37,29.53,32.98,32.15,13.36,30.85,13.11,21.23,17.3,12.93,15.6,-6.18,9.91,-9.96,-1.44,-8.2,-23.92,-6.63,-30.76,-12.53,-38.5,-32.5,-29.71,-44.7,-38.6,-60.83,-42.74,-57.89,-54.87,-57.68,-68.56,-52.13,-75.43,-56.34,-72.95,-64.29,-52.47,-72.11,-48.76,-72.5,-51.68,-54.18,-50.33,-46.45,-52.35,-29.69,-54.45,-36.16,-32.03,-33.08,-23.07,-30.39,-8.81,-24.3,-5.93,-7.81,-8.4,11.56,-1.94,19.28,12,22.25,29,21.09,37.33,22.61,47.87,39.65,40.84,52.42,39.97,60.23,43.57,65.69,53.04,50.64,61.8,47.67,74.58,54.55,66.96,62.53,58.65,70.18,49.29,65.65,51.42,68.28,66.64,50.38,71.79,42.97,61.85,50.75,57.16,58.28,49.72,60.61,32.72,63.21,43,44.07,48.67,34.04,54.39,34.86,51.01,35.59,45.22,54.69,37.79,48.32,29.52,44.78,41.59,36.54,47.95,24.4,44.83,30.15,37.84,33.49,22.88,36.09,16.99,32.54,15.41,23.84,22.93,9.12,22.18,4.36,17.41,4.6,7.61,7.6,-10.74,3.11,-19.33,-1.27,-23.89,-20.08,-13.6,-33.37,-16.29,-41.5,-31.69,-31.64,-45.89,-31.13,-45.79,-41.63,-52.19,-45.28,-42.72,-55.33,-44.06,-67.06,-54.33,-61.37,-53.51,-55.59,-62.68,-38.76,-53.76,-40.81,-53.06,-40.77,-41.21,-54.64,-24.28,-48.88,-25.62,-26.46,-23.92,-19.21,-22.45,-2.31,-17.38,3.8,-3.57,-1.52,14.01,-0.04,20.97,5.31,23.03,19.52,18.41,38.4,23.69,43.77,28.03,44.15,40.79,33.63,56.65,39.62,58.28,42.25,49.19,57.08,43.26,55.04,41.54,61.51,49.5,55,59.45,48.27,61.41,37.1,52.51,48.91,50.33,55.86,39.99,60.66,35.34,45.67,45.13,47.09,50.13,30.92,47.45,36.65,39.09,43.92,40.57,47.06,28.38,52.4,42.11,43,46.07,33.74,48.52,31.17,55.33,34.5,42.3,43.64,32.87,48.98,31.74,46.72,36.17,34.87,45.14,28.45,43.98,22.08,33.79,26.86,21.38,33.71,8.04,29.01,7.69,14.86,7.37,-2.93,4.42,-16.31,-1.08,-15.8,-14.77,-12.78,-23.09,-18.48,-37.51,-18.04,-36.62,-38.38,-36.23,-54.4,-34.47,-62.83,-49.82,-59.76,-50.23,-49.27,-64.84,-48.37,-77.38,-64.09,-54.82,-62.3,-60.26,-66.33,-48.78,-68.96,-48.06,-54.02,-52.65,-37.86,-48.25,-28.82,-42.49,-32.19,-28.94,-35.66,-16.1,-28.21,-1.28,-14.6,-6.19,2.26,-7.28,14.06,-1.19,20.61,16.96,20.9,29.64,22.64,45.12,23.01,43.42,39.5,41.03,56.53,36.67,62.69,41.71,53.73,49.98,56.14,64.44,51.13,67.9,44.29,58.02,62.8,58.42,69.11,53.73,65.48,48.4,61.49,66.45,45.67,60.63,38.91,61.64,48.3,48.95,61.03,39.35,60.47,38.56,59.58,47.89,40.4,49.88,31.56,59.75,32.57,49.97,39.51,38.76,54.28,29.35,49.62,30.37,46.27,40.59,30.3,45.14,24.31,42.1,23.88,35.71,33.04,18.93,34.85,9.8,29.79,12.76,18.47,13.7,-2.05,20.91,-7.34,3.79,-6.02,-8.38,-2.78,-19.5,-4.88,-28.07,-13.51,-28.95,-39.46,-24.4,-45.59,-32.82,-55.77,-44.16,-47.09,-55.79,-44.97,-66.74,-53.75,-56.48,-61.06,-49.65,-60.23,-52.77,-65.91,-57.2,-63.34,-56.7</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B359" t="str">
+        <v>[R_20_标记]</v>
+      </c>
+      <c r="C359" t="str">
+        <v>幅值: 53.7uv 相位: 34.6°</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B360" t="str">
+        <v>[L_20_名字]</v>
+      </c>
+      <c r="C360" t="str">
+        <v>FERG(20)_lFlicker</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B361" t="str">
+        <v>[L_20_放大器]</v>
+      </c>
+      <c r="C361" t="str">
+        <v>1-300 Hz</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B362" t="str">
+        <v>[L_20_闪光]</v>
+      </c>
+      <c r="C362" t="str">
+        <v>b白色光:600.0cd.m-2,5ms</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B363" t="str">
+        <v>[L_20_闪光背景]</v>
+      </c>
+      <c r="C363" t="str">
+        <v>b白色光:30.0cd.m-2</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B364" t="str">
+        <v>[L_20_采样]</v>
+      </c>
+      <c r="C364" t="str">
+        <v>刺激频率:20.0Hz</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B365" t="str">
+        <v>[L_20_分析时间]</v>
+      </c>
+      <c r="C365" t="str">
+        <v>200ms</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B366" t="str">
+        <v>[L_20_数据长度]</v>
+      </c>
+      <c r="C366" t="str">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B367" t="str">
+        <v>[L_20_详细数据(uv)]</v>
+      </c>
+      <c r="C367" t="str">
+        <v>-44.2,-53.87,-33.26,-59.51,-39.63,-52.33,-45.92,-33.45,-54.57,-42.52,-42.9,-54.04,-45.19,-57.86,-44.17,-44.8,-56.92,-41.71,-67.56,-47.03,-58.43,-47,-46.28,-67.23,-48.45,-56.66,-55.77,-43.87,-63.62,-38.04,-55.13,-51.5,-46.12,-54.89,-35.46,-51.54,-42.71,-35.99,-46.54,-28.21,-40.05,-32.43,-23.16,-32.37,-13.48,-26.57,-10.29,-8.06,-15.57,6.56,-10.19,12.22,11.55,8.42,21.75,12.38,29.03,25.81,27.48,46.54,23.95,48.65,38.83,40.17,62.74,34.37,58.79,49.24,54.84,69.22,42.15,62.4,52.93,51.6,75.02,41.06,69.88,51,52.43,60.59,36.06,50.92,43.61,41.79,51.89,31.4,37.26,20.35,28.46,25.22,9.01,24.89,6.58,8.33,7.62,-11.99,2.72,-13.45,-14.13,-8.48,-29.4,-9.55,-32.25,-25.9,-29.45,-40.89,-30.31,-49.58,-37.23,-44.71,-47.8,-38.19,-61.06,-42.62,-52.73,-58.77,-42.18,-58.91,-51.03,-53.07,-63.35,-46.57,-60.48,-46.53,-59.49,-61.51,-40.96,-60.9,-41.4,-55.87,-47.29,-48.38,-60.26,-37.95,-49.16,-58,-47.56,-62.92,-41.35,-52.5,-57.36,-38.3,-64.94,-36.08,-52.49,-48.69,-46.07,-59.83,-41.18,-52.22,-49.73,-37.37,-55.96,-33.18,-50.74,-42.31,-38.98,-44.32,-27.5,-46.56,-34.7,-28.7,-35.01,-17.36,-34,-20.99,-16.13,-28.64,-5.64,-20.67,-2.61,-4.11,-11.65,16.4,-2.87,17.18,12.21,6.31,31.03,14.8,30.82,29.31,27.89,43.91,28.97,52.55,47.89,49.63,52.43,49.73,67.37,43.38,49.93,75.89,50.96,71.01,50.62,63.07,62.03,47.35,60.2,54.67,56.98,53.91,30.17,59.09,33.84,36.73,47.91,17.77,43.65,21.07,24.2,23.6,8.63,24.74,-3.86,6.91,5.86,-11.97,-0.21,-15.66,-13.33,-17.18,-28.78,-15.53,-33.79,-26.07,-30.11,-40.46,-28.47,-44.2,-31.5,-40.01,-50.11,-33.65,-48.87,-36.58,-49.47,-54.43,-37.16,-51.36,-36.23,-43.11,-54.14,-38.03,-49.96,-45.63,-44.9,-48.17,-33.32,-61.36,-37.8,-41.48,-53.48,-39.61,-51.82,-31.58,-40.26,-36.37,-30.41,-50.52,-33.14,-55.79,-44.91,-30.94,-53.13,-33.9,-45.69,-42.13,-36.41,-57.93,-35.73,-49.26,-44.74,-36.58,-48.38,-32.61,-47.44,-44.69,-35.94,-47.4,-28.23,-49.55,-38.67,-31.7,-47.13,-21.77,-40.99,-28.93,-23.7,-33.12,-12.19,-25.4,-14.4,-13.44,-20.61,2.69,-14.1,8.69,2.28,1.52,19.96,5.18,22.9,23.33,19.14,34.65,18.76,43.24,44.44,41.65,59.87,39.4,51.19,45.83,54.28,55.11,49.66,57.84,56.76,55.45,64.3,46.63,63.86,47.48,61.9,55.81,39.91,68.64,43.48,52.01,54.21,31.52,54.94,26.46,33.71,36.96,15.7,32.43,16.47,18.73,15.54,-0.45,12.51,-4.02,1.48,-3,-17.6,-1.37,-21.63,-10.62,-14.06,-29.13,-15.43,-39.03,-27.41,-27.57,-41.98,-28.52,-46.44,-34.2,-43.54,-44.31,-34.17,-52.01,-41.46,-45.14,-48.71,-35.24,-58.1,-44.96,-45.15,-52.82,-44.81,-53.92,-39.23,-50.38,-51.47,-35.79,-49.39,-41.56,-52.95,-47.93,-41.06,-48.4,-32.21,-50.96,-53.41,-34.41,-59.21,-42.12,-53.21,-50.14,-35.08,-62.85,-37.02,-52.47,-42.74,-41.3,-58.59,-37.17,-54.37,-46.52,-39.26,-50.91,-31.94,-52.01,-33.79,-34.34,-46.34,-21.22,-41.16,-22.88,-19.99,-26.47,-8.66,-21.12,-9.53,-3.95,-9.92,5.72,-4.92,8.49,12.95,9.81,24.68,8.32,33.3,32.17,28.12,42.44,31.64,50.72,50.2,42.79,59.63,41.19,60.69,56.2,61.24,69.68,49.37,75.56,61.81,60.31,71.62,53.65,78.33,69.31,60.02,64.3,57.84,64.33,54.85,57.38,59.02,33.32,54.45,33.71,32.45,37.03,17.49,36.98,15.43,20.79,13.54,-0.93,17.73,-7.2,0.08,-2.23,-20.96,-4.71,-28.85,-20.57,-20.5,-32.19,-20.09,-42.63,-29.85,-36.7,-43.32,-30.63,-49.68,-39.05,-46.31,-51.16,-40.76,-54.13,-39.71,-47.14,-51.77,-41.92,-55.93,-37.63,-50.14,-47.33,-43.61,-51.47</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B368" t="str">
+        <v>[L_20_标记]</v>
+      </c>
+      <c r="C368" t="str">
+        <v>幅值: 53.1uv 相位: 34°</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B369" t="str">
+        <v>[R_21_名字]</v>
+      </c>
+      <c r="C369" t="str">
+        <v>FERG(21)_lCone</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B370" t="str">
+        <v>[R_21_放大器]</v>
+      </c>
+      <c r="C370" t="str">
+        <v>1-75 Hz</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B371" t="str">
+        <v>[R_21_闪光]</v>
+      </c>
+      <c r="C371" t="str">
+        <v>f白色光:1000.0cd.m-2,5ms</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B372" t="str">
+        <v>[R_21_闪光背景]</v>
+      </c>
+      <c r="C372" t="str">
+        <v>b白色光:30.0cd.m-2</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B373" t="str">
+        <v>[R_21_采样]</v>
+      </c>
+      <c r="C373" t="str">
+        <v>刺激间隔:1.0S</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B374" t="str">
+        <v>[R_21_分析时间]</v>
+      </c>
+      <c r="C374" t="str">
+        <v>200ms</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B375" t="str">
+        <v>[R_21_数据长度]</v>
+      </c>
+      <c r="C375" t="str">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B376" t="str">
+        <v>[R_21_详细数据(uv)]</v>
+      </c>
+      <c r="C376" t="str">
+        <v>-10.83,-8.96,-12.07,-8.22,-13.23,-7.56,-14.24,-7.01,-15.07,-6.6,-15.7,-6.35,-16.09,-6.27,-16.22,-6.36,-16.1,-6.62,-15.72,-7.05,-15.11,-7.61,-14.28,-8.28,-13.27,-9.03,-12.11,-9.81,-10.86,-10.59,-9.56,-11.34,-8.25,-11.99,-6.99,-12.53,-5.83,-12.91,-4.79,-13.12,-3.93,-13.12,-3.26,-12.92,-2.81,-12.51,-2.58,-11.9,-2.58,-11.09,-2.8,-10.14,-3.22,-9.06,-3.82,-7.91,-4.57,-6.72,-5.41,-5.61,-6.34,-4.51,-7.32,-3.57,-8.47,-2.82,-9.53,-2.28,-10.25,-2.39,-11.42,-2.63,-12.74,-3.13,-13.37,-3.98,-13.81,-5.46,-15.75,-7.04,-15.43,-9.4,-19.04,-11.98,-20.51,-17.77,-21.92,-22.51,-25.13,-25.74,-24.66,-25.52,-24.02,-29.78,-25.82,-34.52,-29.46,-39.4,-40.74,-41.44,-35.2,-42.78,-47.24,-55.74,-38.03,-57.45,-45.68,-50.51,-51.89,-51.24,-36.28,-50.6,-42.45,-43.82,-44.05,-38.13,-46.1,-38.66,-36.72,-36.14,-32.34,-28.34,-29.47,-11.03,-15.77,-7.49,-17.34,-5.78,6.87,8.02,11.12,16.6,22.93,26.86,21.58,39.66,37.2,49.31,42.07,60.71,62.38,64.71,60.77,77.78,92.71,89.53,88.81,91.58,113.36,121.41,123.53,107.59,128.99,128.92,135.97,146.07,146.4,156.84,172.3,134.63,191.24,179.31,193.41,192.16,185.76,188.09,186.74,163.89,226.64,196.22,197.66,220.07,244.3,239.61,222.04,189.05,204.91,247.63,228.56,237.14,205.94,203.92,209.51,215.31,246.84,201.74,201.39,197.34,206.67,193.6,226.6,236.97,227.24,184.05,175.34,198.71,211.18,175.1,177,162.27,153.69,170.39,188.24,159.18,157.74,179.56,175.22,158.94,133.21,150.28,140.09,131.99,147.35,133.3,131.19,112.55,98.14,102.62,95.71,83,82.96,75.1,99.89,75.19,75.81,63.82,79.59,65.69,65.05,49.71,64.89,48.89,46.29,41.12,39.95,34.02,39.25,38.77,36,32.15,24.54,23.64,20.56,26.47,18.69,21.97,16.3,20.88,11.46,16.87,5.74,14.52,3.41,13.04,2.13,11.09,2.05,10.09,-2.08,7.55,-1.62,4.32,-2.53,3.64,-2.69,-0.37,-4.14,-2.35,-5.3,-3.3,-4.55,-6.93,-4.73,-6.91,-4.92,-9.88,-3.71,-12.29,-2.6,-13.25,-3.82,-13.44,-4.24,-13.58,-5.42,-14.03,-3.47,-14.96,-8.12,-14.51,-4.74,-15.35,-6.67,-16.6,-11.43,-11.9,-12.06,-11.12,-12.82,-14.22,-11.88,-12.33,-15.49,-10.14,-17.19,-9.62,-16.96,-12.99,-15.81,-13.44,-15.05,-6.3,-23.59,-6.42,-17.09,-9.4,-16.58,-7.92,-25.73,-15.01,-22.84,-11.83,-15.37,-17.53,-22.76,-13,-17.46,-15,-26.1,-16.13,-15.77,-24.91,-13.9,-17.26,-15.46,-27.57,-13.1,-24.31,-18.55,-24.43,-17.18,-30.33,-18.88,-33.48,-15.94,-30.26,-20.71,-37.62,-24.85,-29.08,-32.09,-30.04,-24.1,-25.43,-25.98,-34.2,-31.53,-39.75,-29.83,-27.48,-36.73,-32.68,-30.15,-32.38,-33.64,-42.48,-39.21,-33.38,-35.81,-22.78,-35.05,-29.01,-33.76,-29.1,-42.91,-31.06,-51.62,-33.82,-50.69,-32.77,-38.95,-44.01,-41.33,-27.33,-47.51,-30.17,-45.84,-36.06,-46.7,-41.62,-34.61,-33.11,-26.07,-43.81,-33.68,-30.42,-33.58,-37.14,-35.71,-36.19,-34.24,-44.31,-32.2,-35.1,-32.36,-31.13,-33.22,-32.08,-23.42,-25.52,-29.95,-28.8,-30.11,-33.09,-19.54,-35.18,-25.77,-35.86,-18.56,-27.76,-30.95,-27.49,-31.6,-24.34,-25.32,-19.71,-22.54,-16.53,-31.15,-12.84,-34.33,-10.82,-25.87,-23.77,-21.62,-17.95,-26.29,-19.2,-23.13,-18.15,-29.4,-18.25,-27.37,-18.77,-17.39,-18.9,-21.76,-21.41,-13.88,-19.66,-12.4,-14.03,-17.42,-18.57,-9.11,-20.24,-15.58,-20.55,-7.4,-19.16,-10.62,-14.26,-5.47,-17.52,-9.34,-16.42,-2.1,-13.22,-7.7,-15.07,-6.24,-14.22,-5.68,-9.54,-5.51,-5.99,-1.73,-7.62,-1.97,-7.04,-2.67,-1.99,-6.37,-3.19,-3.28,2.98,-4.38,1.69,-3.82,5.18,-5.21,4.03,-3.6,7.85,-3.61,7.9,-0.93,8.91,-2.5,8.44</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B377" t="str">
+        <v>[R_21_标记]</v>
+      </c>
+      <c r="C377" t="str">
+        <v>a: 50.5ms -43.1uv b: 106.2ms 198.0uv</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B378" t="str">
+        <v>[L_21_名字]</v>
+      </c>
+      <c r="C378" t="str">
+        <v>FERG(21)_lCone</v>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B379" t="str">
+        <v>[L_21_放大器]</v>
+      </c>
+      <c r="C379" t="str">
+        <v>1-75 Hz</v>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B380" t="str">
+        <v>[L_21_闪光]</v>
+      </c>
+      <c r="C380" t="str">
+        <v>f白色光:1000.0cd.m-2,5ms</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B381" t="str">
+        <v>[L_21_闪光背景]</v>
+      </c>
+      <c r="C381" t="str">
+        <v>b白色光:30.0cd.m-2</v>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B382" t="str">
+        <v>[L_21_采样]</v>
+      </c>
+      <c r="C382" t="str">
+        <v>刺激间隔:1.0S</v>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B383" t="str">
+        <v>[L_21_分析时间]</v>
+      </c>
+      <c r="C383" t="str">
+        <v>200ms</v>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B384" t="str">
+        <v>[L_21_数据长度]</v>
+      </c>
+      <c r="C384" t="str">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B385" t="str">
+        <v>[L_21_详细数据(uv)]</v>
+      </c>
+      <c r="C385" t="str">
+        <v>-13.37,-23.86,-14.49,-22.76,-16.61,-20.85,-19.3,-18.61,-22.03,-16.58,-24.24,-15.26,-25.49,-15,-25.54,-15.89,-24.43,-17.76,-22.42,-20.23,-19.98,-22.76,-17.67,-24.81,-16,-25.91,-15.33,-25.81,-15.8,-24.51,-17.28,-22.28,-19.41,-19.56,-21.67,-16.92,-23.51,-14.89,-24.46,-13.85,-24.28,-14.01,-22.9,-15.21,-20.63,-17.17,-17.9,-19.45,-15.31,-21.4,-13.15,-22.76,-12.36,-22.94,-12.98,-22.22,-14.46,-20.56,-17.54,-18.71,-19.62,-16.44,-23.76,-16.43,-25.45,-15.65,-27.95,-19.17,-28.01,-22.19,-28.27,-28.8,-32.16,-31.01,-29.91,-36.06,-30.17,-38.99,-35.18,-51.04,-40.6,-49.65,-46.24,-46.24,-48.85,-51.59,-50.11,-50.58,-60.61,-48.2,-62.08,-56.8,-69.25,-59.05,-70.94,-53.25,-51.78,-48.37,-55.82,-45.3,-43.66,-51.74,-39.48,-44.91,-37.39,-39.85,-27.19,-33.59,-27.87,-26.78,-24.53,-9.81,-16.5,-7.96,-5.01,12.25,1.69,24.55,15.21,31.71,15.27,43.41,41.45,53.1,43.46,51.1,65.22,73.38,69.15,80.01,77.02,92.89,99.65,85.69,122.66,111.68,118.79,120.25,113.99,143.3,142.6,148.01,121,172.75,147.85,170.88,179.85,171.56,183.22,173.14,177.21,184.18,182.37,210.29,198.82,199.76,231.28,170.69,216.37,235.37,201.14,225.97,191.43,186.57,236.54,183.95,214.6,237.7,207.39,218.65,176.78,248.17,211.96,231.87,195.19,194.17,217.27,208.73,176.74,191.4,184.84,177.59,163.15,157.66,150.32,139.87,172.73,174.9,159.41,160.93,164.13,116.6,125.27,130.25,110.36,131.63,124.87,115.28,89.26,109.61,104.01,95.72,93.27,84.25,76.01,59.91,57.05,69.57,66.6,45.21,52.66,40.91,45.92,34.42,34.1,36.98,28.22,22.77,23.56,25.6,17.6,26.5,8.73,21.39,11.36,19.07,8.36,13.84,5.65,8.83,4.81,3.06,1.24,-1.98,5.14,-5.22,0.72,-6.52,1.03,-10.99,-1.87,-9.61,-3.88,-7.88,-7.9,-8.11,-10.43,-6.14,-14.34,-4.79,-16.45,-6.65,-16.23,-8.08,-16.56,-11.05,-15.63,-13.12,-14.4,-17.93,-12.17,-17.87,-11.12,-20.65,-12.09,-22.47,-14.44,-21.14,-13.88,-20.91,-16.72,-19.71,-21.88,-17.04,-24.35,-17.16,-28.66,-16.55,-30.36,-18.75,-25.78,-18.76,-27.04,-23.98,-25.34,-24.53,-25.11,-33.27,-20.85,-34.7,-21.9,-28.78,-26.6,-35.7,-23.21,-28.93,-26.44,-31.61,-27.33,-26.03,-36.85,-30.82,-39.52,-21.19,-34.01,-26.88,-40.69,-24.76,-38.77,-26.8,-32.21,-34.58,-34.95,-42,-29.95,-40.46,-24.85,-36.8,-27.05,-44.34,-27.68,-34.57,-26.18,-40.4,-43.75,-37.36,-43.2,-35.91,-40.29,-33.21,-50.12,-29.75,-41.99,-40.83,-39.83,-31.55,-37.62,-45.17,-45.62,-48.1,-34.04,-44.43,-31.4,-49.56,-28.19,-38.9,-32.8,-45.1,-39.01,-35.61,-45.67,-40.98,-49.79,-36.72,-57.48,-47.79,-47.73,-35.27,-55.27,-41.27,-42.29,-51.68,-50.25,-50.49,-45.58,-53,-46.46,-49.24,-46.92,-55.07,-52.56,-64.42,-44.98,-55.77,-56.43,-46.66,-43.41,-58.16,-45.14,-45.71,-52.91,-53.43,-60.86,-41.05,-43.12,-40.29,-50.16,-46.47,-49,-46.77,-53.35,-39.76,-33.64,-43.28,-37.12,-50.02,-31.2,-43.27,-46.94,-50.41,-37.11,-40.48,-47.25,-37.99,-37.37,-36,-39.42,-35.28,-38.94,-29.89,-39.05,-31.18,-39.44,-31.96,-32.27,-30.39,-26.77,-27.28,-24.8,-32.37,-24.13,-38.81,-26.39,-34.39,-20.75,-38.85,-23.5,-24.4,-30.5,-25.31,-31.45,-22.77,-32.43,-17.52,-28.94,-23.78,-28.86,-20.65,-25.77,-24.57,-22.94,-25.33,-24.79,-20.07,-17.34,-29.1,-17.76,-29.09,-12.99,-27.08,-16.85,-23.21,-13.76,-22.43,-20.45,-18.27,-17.32,-19.06,-19.89,-17.05,-24.72,-10.95,-22.64,-12.01,-23.96,-12.69,-21.23,-13.32,-17.02,-18.01,-14.18,-16.33,-9.47,-20.66,-10.47,-17.52,-9.18,-19.52,-6.95,-16.12,-8.45,-14.35,-12.32,-10.98,-12.53,-6.84,-13.68,-3.45,-14.59,-2.79,-13.51,-2.7,-11.11,-3.63,-9.21,-6.05,-6.12,-8.14,-2.04,-10.07</v>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B386" t="str">
+        <v>[L_21_标记]</v>
+      </c>
+      <c r="C386" t="str">
+        <v>a: 50.5ms -44.5uv b: 106.3ms 143.8uv</v>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B387" t="str">
+        <v>[R_22_名字]</v>
+      </c>
+      <c r="C387" t="str">
+        <v>FERG(22)_lFlicker</v>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B388" t="str">
+        <v>[R_22_放大器]</v>
+      </c>
+      <c r="C388" t="str">
+        <v>1-300 Hz</v>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B389" t="str">
+        <v>[R_22_闪光]</v>
+      </c>
+      <c r="C389" t="str">
+        <v>f白色光:1000.0cd.m-2,5ms</v>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B390" t="str">
+        <v>[R_22_闪光背景]</v>
+      </c>
+      <c r="C390" t="str">
+        <v>b白色光:30.0cd.m-2</v>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B391" t="str">
+        <v>[R_22_采样]</v>
+      </c>
+      <c r="C391" t="str">
+        <v>刺激频率:20.0Hz</v>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B392" t="str">
+        <v>[R_22_分析时间]</v>
+      </c>
+      <c r="C392" t="str">
+        <v>200ms</v>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B393" t="str">
+        <v>[R_22_数据长度]</v>
+      </c>
+      <c r="C393" t="str">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B394" t="str">
+        <v>[R_22_详细数据(uv)]</v>
+      </c>
+      <c r="C394" t="str">
+        <v>-55.47,-40.28,-47.61,-42.07,-42.94,-31.65,-40.55,-39.35,-30.49,-33.65,-37.92,-37.06,-22.68,-41.88,-22.5,-30.19,-16.51,-26.55,-20.62,-24.17,-17.7,-17.56,-24.56,-11.79,-25.98,-10.35,-24.14,-7.48,-19.91,-4.86,-13.72,-8.03,-7.64,-4.13,-3.19,-11.47,3.45,-3.55,10.74,-0.21,14.57,3.6,14.44,10.61,18.83,28.66,16.38,34.99,19.09,35.15,22.56,48.55,37.84,49.24,44.89,44.3,50.23,48.34,64.26,53.38,57.77,43.75,65.41,51.16,68.58,61.15,66.96,61.49,62.62,63.34,53.57,61.86,52.26,65.19,43.47,58.33,48.51,45.82,42.03,37.33,41.36,30.54,34.78,20.66,29.3,10.58,23.29,4.71,11,-2.66,0.52,-8.42,-12.1,-12.51,-24.28,-14.61,-35.81,-21.37,-41.38,-29.91,-45.94,-33.67,-43.49,-47.95,-45.77,-56.23,-46.77,-64.07,-52.04,-69.25,-50.37,-62.42,-52.69,-58.57,-53.23,-52.61,-54.17,-49.08,-56.68,-41.41,-63.1,-46.29,-55.16,-46.4,-55.24,-46.73,-45.36,-49.19,-45.1,-47.02,-24.87,-42.17,-27.68,-46.93,-26.62,-30.48,-26.37,-33.85,-30.13,-20,-32.44,-16.86,-29.72,-16.32,-29.64,-15.36,-29.95,-11.24,-23.31,-16.66,-19.37,-16.86,-13.34,-20.36,-9.37,-22.27,-5.73,-19.28,-1.8,-13.83,-1.44,-7.43,-5.17,0.59,-3.19,9.22,-8.04,10.72,1.95,16.03,-2.83,19.33,8.84,25.28,23.13,26.84,34.74,25.11,38.28,28.23,39.59,31.5,43.38,32.28,53.07,44.87,49.23,49.27,54.04,56.88,39.22,64.99,46.53,64.66,46.8,54.82,46.12,54.63,57.6,45.23,53.99,35.36,46.39,34.26,49.77,25.53,43.48,24.57,24.24,20.56,18.82,14,6.98,12.49,-3.84,5.81,-12.62,-3,-19.23,-12.23,-25.77,-25.63,-28.69,-37.5,-27.27,-45.61,-31.23,-51.97,-36.94,-54.28,-41.92,-59.8,-48.67,-60.09,-51.81,-51.16,-65.26,-46.67,-61.31,-51.96,-67.43,-47.07,-58.33,-51.49,-58.18,-51.36,-57.48,-58.91,-47.89,-56.78,-46.35,-53.03,-37.87,-54.29,-36.3,-55.73,-40.18,-49.24,-50.36,-34.56,-41.7,-29.64,-43.32,-34.32,-39.92,-30.62,-41.51,-32.69,-35.16,-32.62,-31.87,-31.6,-23.4,-38.36,-21.19,-35.15,-19.67,-30.12,-18.78,-26.7,-19.89,-17.92,-20.89,-12.82,-22.69,-9.76,-18.13,-2.04,-16.94,2.86,-4.87,4.09,3.38,2.82,10.26,5.09,14.86,11.16,20.67,14.3,30.3,22.15,31.67,23.76,35.01,36.07,37.73,51.86,46.14,59.96,40.77,61.01,41.36,60.59,50.1,52.61,59.43,58.03,59.5,52.06,66.55,51.33,67.18,47.16,52.67,40.97,48.33,42.18,39.82,37.54,24.11,33.51,14.62,27.1,9.9,18.18,-1.31,7.1,-6.36,-2.64,-9.65,-18.02,-13.58,-28.51,-19.97,-37.45,-30.43,-45.12,-37.61,-47.69,-49.89,-51.14,-60.31,-53.5,-63.26,-54.01,-66.03,-59.97,-69.67,-59.1,-70.7,-66.96,-67.62,-64.92,-62.82,-73.36,-66.85,-77.29,-64.02,-77.59,-53.72,-62.09,-62.27,-70.91,-50.34,-53.4,-59.12,-52.22,-52.23,-44.86,-54.47,-42.28,-49.92,-30.84,-43.4,-36.24,-38.01,-38.58,-29.73,-42.84,-29.32,-38.51,-25.47,-37.36,-20.06,-37.87,-23.89,-33.25,-26.16,-26.74,-27.06,-20.2,-30.01,-16.6,-27.72,-10.84,-26.6,-9.75,-21.97,-10.9,-14.09,-11.19,-10.02,-15.25,-2.25,-9.64,7.19,-1.01,8.35,-0.87,19.06,7.53,13.93,17.09,9.96,29.18,12.31,29.9,23.75,32.11,29.16,34.75,34.62,35.43,33.77,42.67,47.69,35.25,50.01,39.18,53.52,31.99,50.17,39.72,50.43,46.78,46.09,36.68,32.36,38.24,26.73,45.23,19.1,35.34,14.78,25.87,12.3,20.41,8.64,6.37,5.06,-5.25,3.52,-17.23,-3.89,-24.63,-14.32,-30.95,-25.08,-35.24,-34.77,-39.17,-45.69,-37.18,-52.37,-41.56,-55.75,-47.07,-66.21,-54.02,-63.71,-59.28,-62.2,-72.5,-58.22,-69.22,-60.48,-69.09,-61.66,-75.94,-59.23,-66.8,-58.5,-61.83,-68.46,-54.58,-59.2,-61.89,-61.5,-41.5</v>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B395" t="str">
+        <v>[R_22_标记]</v>
+      </c>
+      <c r="C395" t="str">
+        <v>幅值: 52.3uv 相位: 33.2°</v>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B396" t="str">
+        <v>[L_22_名字]</v>
+      </c>
+      <c r="C396" t="str">
+        <v>FERG(22)_lFlicker</v>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B397" t="str">
+        <v>[L_22_放大器]</v>
+      </c>
+      <c r="C397" t="str">
+        <v>1-300 Hz</v>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B398" t="str">
+        <v>[L_22_闪光]</v>
+      </c>
+      <c r="C398" t="str">
+        <v>f白色光:1000.0cd.m-2,5ms</v>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B399" t="str">
+        <v>[L_22_闪光背景]</v>
+      </c>
+      <c r="C399" t="str">
+        <v>b白色光:30.0cd.m-2</v>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B400" t="str">
+        <v>[L_22_采样]</v>
+      </c>
+      <c r="C400" t="str">
+        <v>刺激频率:20.0Hz</v>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B401" t="str">
+        <v>[L_22_分析时间]</v>
+      </c>
+      <c r="C401" t="str">
+        <v>200ms</v>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B402" t="str">
+        <v>[L_22_数据长度]</v>
+      </c>
+      <c r="C402" t="str">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B403" t="str">
+        <v>[L_22_详细数据(uv)]</v>
+      </c>
+      <c r="C403" t="str">
+        <v>-74.35,-54.44,-63.75,-51.14,-71.55,-66.59,-69.24,-59.65,-58.71,-70.09,-56.69,-71.99,-60.35,-70.64,-51.86,-71.77,-49.01,-67.56,-50.09,-63.44,-47.5,-65.91,-41.41,-59.9,-41.61,-50.08,-40.22,-42.76,-32.38,-35.39,-26.98,-25.23,-26.68,-14.94,-17.02,-5.73,-15.71,0.96,-8.56,13,-1.87,18.45,5.8,30.25,13.12,36.13,19.61,38.4,29.97,44.36,39.9,46.59,41.79,47.47,51.98,50.76,44.25,43.24,50.47,44.71,63.63,42.71,52.14,38.4,61.09,40.8,51.1,40.25,41.47,29.46,36.26,17.82,37.22,15.16,24.49,9.11,14.08,3,9.18,0.78,-6.62,-5.49,-11.59,-9.93,-24.45,-12.39,-31.86,-18.78,-37.61,-23.34,-46.83,-30.57,-51.27,-33.73,-48.44,-39.27,-54.77,-45.39,-56.24,-46.92,-54.3,-54.4,-52.27,-50.17,-51.44,-58.64,-52.1,-62.45,-52.55,-61.58,-46.53,-60.79,-48.52,-55.01,-38.3,-63.55,-47.04,-60.45,-41.01,-56.92,-45.75,-53.72,-47.96,-56.47,-55.4,-54.1,-50.56,-45.55,-55.9,-48.03,-61.4,-45.26,-53.67,-45.44,-59.08,-40.69,-56.77,-40.82,-59.99,-43.42,-55.15,-45.96,-55.03,-43.58,-51.78,-38.82,-45.56,-35.1,-38.42,-38.45,-32.91,-31.91,-26.02,-29.21,-19,-27.65,-12.26,-20.79,-2.66,-12.87,4.62,-7.28,11.33,-0.71,16.14,6.68,19.87,11.19,23.77,16.18,32.16,32.33,39.86,43.07,34.15,37.59,42.66,48.92,47.28,55.08,47.79,60.42,48.24,56.91,39.18,54.95,40.11,55.98,34.59,49.07,40.91,47.24,31.98,44.44,37.36,32.1,29.05,23.39,24.54,15.89,25.13,6.82,18.28,-0.21,14.26,-1.8,9.46,-7.83,0.93,-16.57,-6.04,-27,-12.91,-28.52,-19.46,-30.24,-23.33,-32.54,-26.46,-37.39,-34.26,-36.33,-37.88,-36.32,-44.33,-32.62,-43.8,-36,-48,-31.82,-44.8,-35.43,-54.69,-33.2,-50.48,-36.69,-55.31,-31.52,-46.53,-35.41,-48.18,-35.5,-38.09,-42.08,-41.11,-47.61,-48.02,-45.65,-40.52,-49.93,-47.12,-60.41,-36.2,-51.45,-47.1,-61.09,-37.76,-53.45,-46.92,-63.08,-45.73,-53.76,-48.37,-51.78,-43.05,-51.95,-48.89,-49.88,-49.03,-48.17,-48.12,-42.74,-42.68,-34.06,-43.91,-32.3,-40.19,-20.19,-35.24,-13.52,-27.31,-8.92,-25.32,-3.49,-14.58,3.65,-7.92,7.19,0.82,14.28,12.67,18.45,26.85,23.8,29.18,34.26,43.66,42.91,52.2,45.93,60.96,44.62,67.14,52.08,64.56,47.65,59.28,61.04,69.63,56.69,61.76,56.91,62.07,60.38,64.26,58.24,54.62,55.42,53.74,53.96,39.76,44.24,36.63,37.86,29.14,32.93,15,27.56,10.65,17.53,2.17,16.34,-7.85,6.08,-14.43,-0.14,-13.37,-13.37,-18.93,-21.16,-20.1,-28.86,-26.08,-34.83,-26.9,-37.58,-28.33,-44.23,-32.23,-43.9,-31.12,-49.08,-35.66,-49.09,-37.82,-55.65,-39.27,-47.6,-34.59,-52,-43.97,-41.31,-49.92,-38.57,-43.97,-40.21,-50.76,-43.06,-51.02,-39.43,-52.75,-34.71,-53.37,-33.52,-54.45,-36.99,-45.94,-36.16,-54.48,-34.53,-49.78,-40.21,-53.34,-43.96,-52.67,-41.65,-45.93,-42.27,-43.17,-44.73,-36.8,-46.19,-37.57,-40.13,-34.48,-39.92,-21.71,-38.01,-19.97,-34.51,-15.51,-26.6,-10.15,-24.88,-4.17,-14,3.87,-5.25,4.25,4.25,9.04,14.21,18.05,25.43,20.25,34.72,22.32,40.67,28.36,52.8,35.28,60.87,35.88,61.45,45.71,64.87,54.36,62.79,57.19,64.38,52.2,65.52,57.9,69.46,71.12,68.31,66.23,62.71,63.11,53.34,60.36,52.63,51.31,44.71,47.27,28.02,50.07,31.6,42.69,24.17,29.23,17.24,20.02,7.73,16.87,-0.33,4.06,0.89,-0.34,-3.57,-11,-10.56,-20.37,-8.71,-26.68,-17.79,-31.31,-17.07,-34.08,-18.16,-35.05,-23.58,-39.53,-23.27,-39.55,-27.6,-40.42,-28.16,-34.09,-31.26,-33.85,-33.59,-30.45,-32.43,-24.39,-31.75,-34.86,-29.66,-25.28,-36.69,-19.71,-40.99,-23.3,-38.64,-24.96,-42.6,-17.53,-35.52,-29.4,-46.17</v>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B404" t="str">
+        <v>[L_22_标记]</v>
+      </c>
+      <c r="C404" t="str">
+        <v>幅值: 51.8uv 相位: 32.6°</v>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B405" t="str">
+        <v>[R_23_名字]</v>
+      </c>
+      <c r="C405" t="str">
+        <v>FERG(23)_lCone</v>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B406" t="str">
+        <v>[R_23_放大器]</v>
+      </c>
+      <c r="C406" t="str">
+        <v>1-75 Hz</v>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B407" t="str">
+        <v>[R_23_闪光]</v>
+      </c>
+      <c r="C407" t="str">
+        <v>f白色光:2000.0cd.m-2,5ms</v>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B408" t="str">
+        <v>[R_23_闪光背景]</v>
+      </c>
+      <c r="C408" t="str">
+        <v>b白色光:30.0cd.m-2</v>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B409" t="str">
+        <v>[R_23_采样]</v>
+      </c>
+      <c r="C409" t="str">
+        <v>刺激间隔:1.0S</v>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B410" t="str">
+        <v>[R_23_分析时间]</v>
+      </c>
+      <c r="C410" t="str">
+        <v>200ms</v>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B411" t="str">
+        <v>[R_23_数据长度]</v>
+      </c>
+      <c r="C411" t="str">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B412" t="str">
+        <v>[R_23_详细数据(uv)]</v>
+      </c>
+      <c r="C412" t="str">
+        <v>1.48,10.16,1.01,7.54,6.69,2.07,10.92,1.88,8.19,7.7,2.82,11.82,2.88,8.93,8.8,3.63,12.75,3.9,9.68,9.88,4.42,13.62,4.86,10.33,10.84,5.08,14.35,5.66,10.81,11.61,5.54,14.84,6.24,11.04,12.13,5.75,15.06,6.55,10.99,12.37,5.69,15,6.58,10.67,12.33,5.36,14.67,6.37,10.11,12.06,4.82,14.13,5.97,9.37,11.62,4.14,13.44,5.45,8.5,11.07,3.38,12.66,4.86,7.58,10.47,2.55,11.83,4.22,6.63,9.76,1.59,10.75,3.2,5.22,8.4,0.34,9.54,1.92,2.73,6.81,-1.68,5.77,-0.88,-0.43,3.38,-7.15,3.16,-7.53,-6.54,-1.05,-11.83,-5.47,-14.07,-13.42,-8.12,-21.42,-15.11,-23.17,-25.86,-17.04,-28.87,-21.75,-36.54,-26.55,-21.4,-30.83,-33.67,-42.32,-42.72,-37.81,-44.72,-28.79,-40.83,-30.65,-28.85,-35.66,-20.8,-34.06,-17.4,-11.05,-27.62,-10.3,-18.06,-12.04,-5.23,-7.71,7.72,3,12.4,18.12,8.78,28,29.75,30.26,40.76,30.97,45.21,45.03,57.78,64.34,54.04,63.88,81.55,79.45,93.99,86.89,104.11,107.29,93.7,110.6,98.75,115.75,114.93,116.31,136.09,117.9,158.53,153.37,169.06,158.82,160.94,178.06,199.92,166.6,198.58,210.43,191.84,213.53,227.92,220.94,178.69,210.7,193.24,196.53,245.72,251.35,223.24,260.75,243.25,219.1,202.33,209.77,220.48,252.89,231.72,257.93,240.37,209.09,218.34,220.75,215.66,194.7,230.71,195.63,241.16,223.9,179.52,189.44,179.82,179.09,181.03,173.38,163.15,157.59,169.46,145.76,166.04,158.22,134.18,157.33,129.58,137.76,121.12,129.28,109.02,109.1,107.6,108.96,101.39,99.04,76.66,87.83,89.6,69.46,71.58,56.93,65.25,66.29,46.4,54.07,44.63,44.31,45.9,34.95,40.91,36.93,33.65,34.64,26.8,33.46,25.9,24.4,26.12,19.7,25.34,18.06,18.28,21.45,12.28,20.07,13.8,15.23,17.79,9.05,17.9,9.99,12.05,15.3,5.54,14.74,7.84,10.32,14.23,5.19,12.93,7.37,8.74,12.28,4.94,14.12,5.69,8.46,12.62,4.95,12.47,6.28,6.29,11.96,4.63,13.32,5.82,5.16,11.8,2.12,12.99,5.73,4.84,10.35,2.09,12.92,5.04,5.49,9.73,0.19,9.66,2.82,4.48,7.86,3.02,8.78,7.25,5.97,9.18,2.48,7.18,5.36,3.36,8.12,0.49,2.49,-1.34,-0.12,4.53,-4.76,3.28,2.5,-0.04,1.38,-8.86,2.44,-8.37,-9.28,-3,-12.32,0.86,-6.61,-10.08,-7.02,-14.28,-1.7,-13.11,-17.69,-2.91,-14.46,-11.09,-8.62,-21,-1.86,-16.12,-5.61,-19.58,-20.09,-9.64,-11.91,-17.27,-21.03,-21.32,-9.44,-14.27,-17.24,-10.81,-19.41,-6.43,-25.21,-24.63,-19.77,-27.79,-13.93,-14.35,-18.42,-14.7,-16.43,-14.81,-29.17,-8.69,-15.1,-21.04,-21.39,-28.09,-27.88,-9.9,-17.25,-8.18,-26.19,-14.51,-20.75,-27.33,-19.33,-23.35,-11.02,-21.01,-15.17,-11.33,-29.07,-17.98,-20.53,-18.01,-16.38,-26.54,-15.3,-6.74,-29.95,-8.44,-16.97,-17.98,-14.93,-29.01,-11.78,-12.97,-18.33,-6.41,-14.79,-16.89,-21.07,-18.39,-25.01,-31.51,-19.2,-28.56,-16.01,-17.11,-27.9,-20.58,-22.84,-12.55,-21.62,-12.9,-16.37,-25.07,-14.68,-12.54,-15.64,-3.66,-11.09,-12.46,-5.77,-12.99,-12.37,-8.93,-9.63,-7.44,-13.11,-6.78,-12.76,-10.81,-8.47,-12.49,-7.09,-7.33,-16.12,2.31,-10.1,-2.92,-10.19,-8.44,-6.69,-10.62,0.09,-2.6,-3.93,0.03,-3.67,5.96,-3.91,2.2,4.83,-0.25,6.63,2.67,2.27,5.65,-1.3,6.91,4.74,1.5,14.33,1.3,7.27,7.25,7.21,9.53,5.01,15.54,7.26,9,15.98,8.93,15.6,12.42,9.25,15.91,7.25,16.43,14.98,12.82,19.53,9.52,18.36,13.16,12.11,20.58,8.31,16.43,13.96,12.08,20.48,11.61,19.06,14.02,11.73</v>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B413" t="str">
+        <v>[R_23_标记]</v>
+      </c>
+      <c r="C413" t="str">
+        <v>a: 53.9ms -52.3uv b: 113.0ms 184.2uv</v>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B414" t="str">
+        <v>[L_23_名字]</v>
+      </c>
+      <c r="C414" t="str">
+        <v>FERG(23)_lCone</v>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B415" t="str">
+        <v>[L_23_放大器]</v>
+      </c>
+      <c r="C415" t="str">
+        <v>1-75 Hz</v>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B416" t="str">
+        <v>[L_23_闪光]</v>
+      </c>
+      <c r="C416" t="str">
+        <v>f白色光:2000.0cd.m-2,5ms</v>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B417" t="str">
+        <v>[L_23_闪光背景]</v>
+      </c>
+      <c r="C417" t="str">
+        <v>b白色光:30.0cd.m-2</v>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B418" t="str">
+        <v>[L_23_采样]</v>
+      </c>
+      <c r="C418" t="str">
+        <v>刺激间隔:1.0S</v>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B419" t="str">
+        <v>[L_23_分析时间]</v>
+      </c>
+      <c r="C419" t="str">
+        <v>200ms</v>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B420" t="str">
+        <v>[L_23_数据长度]</v>
+      </c>
+      <c r="C420" t="str">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B421" t="str">
+        <v>[L_23_详细数据(uv)]</v>
+      </c>
+      <c r="C421" t="str">
+        <v>15.63,-6.24,10.98,3.22,0.25,13.96,-6.28,16.38,-2.13,8.71,9.33,-1.43,18.04,-4.05,16.52,3.91,6.84,15.72,-1.36,21.14,0.22,15.81,10.81,5.38,21.26,0.18,22.55,5.67,14.08,17.33,4.27,24.87,2.67,21.74,11.22,11.17,22.28,3.34,25.81,5.35,18.51,15.61,7.31,24.55,2.17,23.47,7.55,12.74,17.68,1.91,23.35,-0.22,16.75,7.9,5,16.8,-4.61,16.47,-3.76,8.03,6.99,-7,9.96,-13.54,8.91,-9.91,-4.89,-1.69,-15.92,2.36,-22.84,-9.56,-17.66,-18.24,-11.64,-25.74,-14.63,-28.43,-16.09,-16.06,-33.87,-18.72,-42,-21.35,-28.1,-24.54,-15.56,-46.33,-8.18,-33.28,-30.74,-28.49,-25.44,-15.2,-31.09,-6.55,-27.75,-17.29,-0.67,-17.09,12.97,-8.06,0.82,4.2,-3.7,20.15,5.98,34.63,18.04,28.07,35.01,33.09,49.56,35.63,60.1,58.51,72.74,74.32,64.93,96.13,75.28,91.35,88.89,88.49,129.11,96.25,124.6,118.27,128.58,146.75,142.93,171.78,145.06,154.2,177.72,142.36,197.26,162.7,201.95,169.09,190.64,179.96,189.94,204.63,174.14,232.37,202.59,237.91,219.05,185.11,254.64,234.23,247.65,194.07,213.99,230.87,208.71,241,220.7,215.93,261.98,210.65,236.33,243.88,244.42,217.53,253.06,225.12,232.95,257.26,231.45,259.98,238.92,200.98,203.23,235.8,217.5,209.51,220.9,187.87,199.98,200.69,179.97,181.67,177.64,184.48,181.34,175.84,188.74,161.18,174.21,188.15,173.98,191.69,158.55,180.65,154.65,150.19,157.04,119.5,149.18,118.78,126.61,105.82,117.33,116.74,104.21,109.61,101.5,107.38,90.87,76.91,109.28,77.18,90.24,70.56,86.29,77.55,63.74,82.75,51.21,73.4,54.86,55.19,61.3,45.63,66.37,37.04,43.94,50.21,37.13,50.57,28.43,44.41,31.45,27.47,39.69,20.8,39.78,14.05,27.02,21.98,15.78,31.25,4.75,28.91,9,16.58,19.71,1.57,21.97,-1.65,17.29,6.88,5.72,16.05,-4.72,17.87,-3.16,9.65,5.9,-4.3,14.63,-8.58,11.89,-1.53,1.61,8.92,-9.4,14.07,-8.65,9.13,0.99,-5.72,8.4,-8.96,8.61,-9.78,2.97,4.39,-5.78,10.7,-8.21,6.07,-6.52,-2.56,6.92,-8.84,14.97,-12.59,2.69,-0.1,-1.86,13.23,-9.29,11.72,-3.91,2.15,0.18,-13.25,14.66,-15.29,8.34,-3.69,-7.79,6.06,-11.47,7.97,-12.65,1.17,3.1,-8.86,2.97,-22.15,7.89,-9.36,-10.85,-1.85,-20.64,-3.7,-20.26,-9.62,-15.41,-20.06,-11.89,-21.83,-8.9,-22.67,-11.67,-19.74,-19.09,-10.67,-35.43,-14.38,-31.44,-21.83,-16,-31.19,-16.6,-39.58,-18.41,-21.64,-23.89,-16.56,-38.5,-16.84,-35.14,-31.42,-28.42,-38.1,-10.34,-30.53,-19.22,-39.39,-31.79,-22.04,-31.68,-22.73,-39.45,-31.56,-23.01,-39.47,-16.57,-34.87,-11.61,-25.59,-23.85,-18.21,-38.23,-13.78,-27.22,-11.27,-27.34,-32.25,-22.66,-25.96,-22.41,-24.17,-16.98,-14.68,-22.07,-13.78,-33.1,-7.88,-18.99,-20.49,-15.86,-21.83,-3.95,-18.79,-20.8,-8.76,-27.39,-11.97,-24.33,-9.38,-26.81,-9.51,-13.01,-29.77,-9.55,-29.2,-9.77,-18.71,-12.77,-12.04,-18.92,-4.95,-15.02,-12.43,-15.25,-20.07,5.32,-31.23,-10.17,-22.13,-8.85,-4.09,-28.14,2.1,-21.35,-10.36,-8.54,-13.38,-2.78,-26.2,-3.54,-23.37,-8.23,-12.68,-21.11,-1.46,-26.22,-4.58,-12.14,-11.7,-5.12,-22.8,5.91,-22.44,-0.21,-7.04,-10.94,0.16,-18.09,5.1,-14,-5.76,1.39,-10.34,12.19,-14.13,3.67,-0.84,-1.72,9.18,-9.72,15.92,-4.59,10.14,7.89,0.94,18.05,-5.28,19.15,-0.39,6.66,13.01,-1.83,22.58,1.26,17.94,10.98,9.95,22.01,1.14,24.81,7.16,16.77,17.21,5.81,26.64,3.44,23.85,11.57,15.53,23.79,6.66,27.28,7.11,22.53,15.95,11.61,26.37,4.94,25.81,8.92,16.04,18.18,5.05</v>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B422" t="str">
+        <v>[L_23_标记]</v>
+      </c>
+      <c r="C422" t="str">
+        <v>a: 53.9ms -57.1uv b: 113.2ms 185.7uv</v>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B423" t="str">
+        <v>[R_24_名字]</v>
+      </c>
+      <c r="C423" t="str">
+        <v>FERG(24)_lFlicker</v>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B424" t="str">
+        <v>[R_24_放大器]</v>
+      </c>
+      <c r="C424" t="str">
+        <v>1-300 Hz</v>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B425" t="str">
+        <v>[R_24_闪光]</v>
+      </c>
+      <c r="C425" t="str">
+        <v>f白色光:2000.0cd.m-2,5ms</v>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B426" t="str">
+        <v>[R_24_闪光背景]</v>
+      </c>
+      <c r="C426" t="str">
+        <v>b白色光:30.0cd.m-2</v>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B427" t="str">
+        <v>[R_24_采样]</v>
+      </c>
+      <c r="C427" t="str">
+        <v>刺激频率:20.0Hz</v>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B428" t="str">
+        <v>[R_24_分析时间]</v>
+      </c>
+      <c r="C428" t="str">
+        <v>200ms</v>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B429" t="str">
+        <v>[R_24_数据长度]</v>
+      </c>
+      <c r="C429" t="str">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B430" t="str">
+        <v>[R_24_详细数据(uv)]</v>
+      </c>
+      <c r="C430" t="str">
+        <v>-47.77,-49.77,-45.02,-40.15,-52.97,-38.09,-44.52,-46.5,-34.32,-37.74,-45.74,-29.4,-37.73,-40.86,-28.94,-37.36,-33.44,-21.14,-30.72,-26.27,-14.12,-25.78,-20.5,-4.46,-17.27,-13.14,0.9,-5.18,-0.62,12.02,-3.68,8.89,16.37,10.54,13.34,25.66,21.98,23.2,35.32,25.14,42.65,41.42,35.12,49.96,51.06,39.23,51.49,59.53,46.42,55.99,49.79,49.08,58.18,46.16,38.19,56.86,51.07,38.45,47.33,38.04,38.13,41.25,29.23,21.31,28.45,19.18,15.58,17.71,4.05,-0.74,11.45,-3.44,-9.65,-1.76,-19.65,-18.58,-13.7,-27.51,-29.05,-23.37,-36.94,-37.11,-34.8,-45.69,-43.89,-41.38,-53.34,-49,-50.41,-63.68,-54.72,-54.6,-68.37,-56.33,-58.37,-65.72,-58.52,-52.1,-60.77,-48.72,-58.84,-66.02,-44.67,-49.09,-68.65,-50.88,-52.88,-64.31,-51.77,-55.81,-58.45,-40.01,-52.01,-60.35,-48.56,-53.94,-50.12,-34.87,-46.43,-48.07,-38.13,-49.55,-46.15,-37.16,-54.5,-47.42,-36.81,-53.37,-44.38,-30.77,-50.4,-41.08,-35.88,-49.63,-38.61,-35.01,-44.76,-38.55,-30.72,-43.32,-32.3,-25.56,-39.28,-23.97,-22.61,-30.63,-18.51,-17.55,-22.87,-12.62,-14.92,-16.28,1.93,0.99,-6.71,4.47,6.19,3.76,20.51,13.88,16.47,32.79,28.32,21.4,42.92,32.11,30.96,44.79,43.09,32,56.12,45.53,45.47,55.41,40.27,52.32,63.35,50.77,51.98,55.36,40.12,54.92,53.33,36.22,51.4,42.82,33.69,40.38,46.11,20.68,31.82,33.75,18.05,20.48,22.3,2.54,8.47,3.33,-5.5,-0.41,-6.67,-22.49,-13.09,-16.09,-29.85,-20.47,-28.29,-43.15,-31.62,-43.82,-49.58,-38.22,-50.69,-57.96,-43.29,-58.23,-58.11,-47.3,-53.62,-63.18,-54.72,-61.99,-61.82,-51.35,-60.33,-56.87,-54.97,-68.06,-58.23,-53.16,-59.67,-59.65,-50.04,-55.58,-49.5,-41.13,-67.39,-44.4,-45.15,-59.08,-43.3,-43.14,-54.82,-56.84,-42.96,-50.45,-49.76,-46.64,-55.92,-42.48,-44.71,-46.65,-43.43,-44.35,-50.31,-37.22,-41.52,-52.02,-31.72,-40.78,-44.86,-33.27,-35.73,-42.39,-27.62,-31.22,-36.55,-19.23,-24.96,-24.37,-8.89,-20.68,-16.3,-4,-10.68,-8.39,8.53,-5.92,-0.15,10.97,5.86,8.28,30.2,11.35,21.58,38.16,19.1,38.7,46.18,38.56,38.26,50.02,40.21,50.55,52.19,51.54,57.88,63.5,44.75,56.34,62.39,54.2,66.26,63.33,43.66,51.82,51.56,39.26,51.4,43.86,41.18,49.2,39.53,24.01,33.13,28.59,18.82,27.14,11.81,2.12,9.78,-1,-8.36,1.9,-12.48,-18.15,-12.8,-30.59,-28.33,-24.31,-40.85,-35.28,-33.73,-48.95,-47.01,-39.95,-54.49,-53.25,-43.43,-59.03,-51.4,-53.83,-64.16,-61.02,-49.66,-62.46,-58.54,-50.87,-67.45,-54.36,-52.77,-68.22,-46.63,-48.34,-55.7,-51.6,-52.38,-57.39,-42.55,-43.74,-60.44,-46.81,-56.34,-57.45,-35.24,-41.14,-42.75,-27.2,-52.47,-44.78,-33.67,-46.64,-47.93,-32.04,-41.78,-44.17,-34.39,-43.6,-35.62,-32.67,-40.76,-36.79,-27.63,-38.43,-35.9,-24.37,-40.96,-31.6,-21.23,-38.93,-27.77,-18.04,-28.2,-22.68,-12.53,-24.88,-11.27,-8.35,-17.94,-4.05,-3.05,-11.83,1.12,6.89,-1.09,10.58,18.18,10.9,30.6,24.16,20.8,36.66,23.96,21.55,39.68,32.23,42.62,54.4,42.96,38.07,58.75,40.43,53.43,62.9,47.56,42.91,57.48,53.28,56.65,55.97,49.42,47.72,50.62,44.93,42.01,53.44,36.06,39.54,39.93,22.29,31.23,30.3,12.56,21.77,20.85,-1.43,9.68,7.26,-10.2,-0.81,-3.95,-17.71,-9.23,-19.21,-27.86,-19.83,-27.12,-43.18,-27.98,-38.68,-47.59,-38.38,-43.18,-50.05,-40.01,-51.43,-52.23,-41.72,-56.38,-53.62,-48.67,-53.18,-56.56,-47.49,-59.91,-58.16,-40.2,-50.86,-48.96,-48.37,-60.87,-47.06,-48.34,-49.18,-44.76,-36.15,-47.42,-42.77,-41.95,-51.11,-46.6,-35.72,-51.3,-33.74,-40.16,-53.81,-41.76,-39.87,-57.96,-42.17</v>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B431" t="str">
+        <v>[R_24_标记]</v>
+      </c>
+      <c r="C431" t="str">
+        <v>幅值: 53.6uv 相位: 33.6°</v>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B432" t="str">
+        <v>[L_24_名字]</v>
+      </c>
+      <c r="C432" t="str">
+        <v>FERG(24)_lFlicker</v>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B433" t="str">
+        <v>[L_24_放大器]</v>
+      </c>
+      <c r="C433" t="str">
+        <v>1-300 Hz</v>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B434" t="str">
+        <v>[L_24_闪光]</v>
+      </c>
+      <c r="C434" t="str">
+        <v>f白色光:2000.0cd.m-2,5ms</v>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B435" t="str">
+        <v>[L_24_闪光背景]</v>
+      </c>
+      <c r="C435" t="str">
+        <v>b白色光:30.0cd.m-2</v>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B436" t="str">
+        <v>[L_24_采样]</v>
+      </c>
+      <c r="C436" t="str">
+        <v>刺激频率:20.0Hz</v>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B437" t="str">
+        <v>[L_24_分析时间]</v>
+      </c>
+      <c r="C437" t="str">
+        <v>200ms</v>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B438" t="str">
+        <v>[L_24_数据长度]</v>
+      </c>
+      <c r="C438" t="str">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B439" t="str">
+        <v>[L_24_详细数据(uv)]</v>
+      </c>
+      <c r="C439" t="str">
+        <v>-38.3,-28.95,-35.89,-20.04,-22.37,-17.78,-7.91,-12.67,-8.15,2.92,-4.84,7.88,13.37,9.65,23.8,22.29,25.06,36.01,35.41,39.98,49.8,45.31,57.94,55.44,55.09,63.67,67.8,58.72,78.33,70.98,66.05,82.51,65.32,68.65,76.45,61.06,72.38,80,68.21,84.78,69.91,65.95,72.51,61.06,63.19,65.97,56.41,58.43,52.1,43.74,57.05,53.07,39.91,48.81,45.39,36.75,41.56,23.43,28.68,29.23,18,26.41,22.76,16.24,18.81,17.2,10.43,21.67,7.58,9.33,15.03,1.27,7.61,7.03,0.43,8.14,1.68,-1.02,7.36,-4.54,0.21,3.01,-4.34,-0.16,-5.82,-12.81,-2.73,-5.76,-19.49,-6.56,-21.04,-10.71,-11.39,-24.24,-17.88,-11.43,-27.86,-19.72,-25.24,-26.85,-16.05,-39.16,-33.22,-36.45,-40.34,-33.63,-33.02,-41.26,-43.97,-45,-51.91,-34.1,-39.77,-55.77,-40.34,-53,-39.03,-38.83,-48.19,-43.78,-41.46,-48.72,-32.06,-39.6,-38.52,-22.23,-31.23,-26.81,-14.59,-24.84,-15.49,-10.35,-16.87,-3.39,-2.23,-3.3,10.05,7.24,11.02,22.19,17.86,24.89,34.96,28.55,39.2,46.59,40.98,52.77,55.81,54.75,68.92,57.6,59.93,65.51,58.74,63.66,70.29,65.04,76.26,78.01,64.18,68.56,71.25,67.58,71.15,60.59,67.51,68.14,52.74,67.41,56.51,52.6,67.29,49.67,50.57,60.29,36.75,53.3,47.98,39.79,42.9,34.73,32.41,35.65,27.67,22.05,32.44,20.3,20.53,24.67,16.49,15.34,14.44,8.44,19.86,10.56,7.31,14.29,6.74,6.46,12.13,1.11,6.4,8.35,-1.54,4.79,4.86,-8.2,3.2,-4.63,-7.22,-5.18,-4.93,-9.71,-3.6,-20.28,-8.83,-12.92,-20.35,-12.48,-22.33,-23.87,-18.44,-34.05,-24.77,-31.74,-44.55,-27.6,-33.79,-50.32,-31.87,-40.76,-41.62,-34.59,-48.78,-47.87,-47.68,-59.36,-48.91,-47.8,-61.2,-44.29,-54.73,-48.87,-44.67,-42.88,-52.98,-34.35,-43.23,-36.98,-29.23,-43.24,-24.18,-27.04,-26.46,-17.02,-15.18,-18.62,-3.05,-7.51,-0.39,8.14,3.15,15.53,19.44,16.81,30.8,32.15,31,41.53,39.1,42.29,56.09,49.3,54.39,66.44,62.46,65.74,67.94,65.31,77.23,74.45,69.13,86.3,69.05,75.33,77.84,74.2,76.07,79.19,64.59,70.57,66.96,69.38,73.15,65.8,62.34,66.9,57.36,63.85,57.2,44.54,51.02,46.25,34.13,40.02,36.05,37.31,34.31,25.14,22.95,24.67,20.45,24.61,16.76,7.97,16.81,12.73,7.15,12.23,4.3,7.07,10.68,-0.63,5.81,3.45,-4.73,4.26,-3.58,-6.71,0.68,-10.85,-3.47,-1.59,-10.53,-2.6,-7.81,-14.11,-11.3,-19.16,-19.55,-10.81,-18.95,-18.71,-15.52,-37.84,-33.33,-28.22,-34.84,-33.89,-33.29,-33.77,-32.5,-42.39,-36.57,-30.63,-48.84,-41.2,-42,-54.54,-49.74,-49.34,-60.1,-39.19,-53.63,-46,-41.87,-44.6,-45.39,-46.08,-45.41,-37.17,-37.84,-44.57,-31.1,-33.6,-34.7,-21.21,-27.41,-19.27,-11.76,-20.69,-9.55,-2.33,-5.13,6.95,8.63,7.49,21.32,16.89,21.54,34.64,29.63,36.4,44.07,37,51.03,50.6,51.02,55.82,57.2,62.84,73.51,63.8,72.46,68.51,61.83,73.65,66.03,61.95,68.97,75.15,68.43,72.82,70.71,58.45,72.11,58.57,64.18,63.24,54.76,54.51,52.37,45.97,51.92,43.03,39.55,49.75,35.5,43.14,38.06,28.65,27.69,27.77,14.73,27.7,24.59,18.84,29.02,12.68,8.82,15.48,4.17,13.57,11.81,0.61,9.86,4.79,0.4,9.51,0.08,1.51,6.81,-2.5,4.21,1.96,-3.89,-1.44,0.13,-3.36,-6.38,-11.2,-5.99,-9.08,-16.52,-6.4,-3.36,-24.55,-21.41,-17.9,-27.8,-18.52,-26.24,-25.5,-25.31,-41.83,-32.94,-36.4,-35.49,-35.52,-38.27,-53.5,-34.21,-46.05,-45.09,-39.04,-50.81,-55.19,-53.08,-53.38,-43.33,-43.51,-47.73,-52.59,-40.02,-47.79,-37.73,-43.59,-45.89,-33.9</v>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="str">
+        <v>FERG</v>
+      </c>
+      <c r="B440" t="str">
+        <v>[L_24_标记]</v>
+      </c>
+      <c r="C440" t="str">
+        <v>幅值: 52.6uv 相位: 33.8°</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:C98"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:C440"/>
   </ignoredErrors>
 </worksheet>
 </file>